--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F2" t="n">
         <v>51</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="D3" t="n">
         <v>48.9</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="D4" t="n">
         <v>51.3</v>
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D5" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E5" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F5" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D6" t="n">
         <v>49.2</v>
@@ -644,10 +644,10 @@
         <v>50.8</v>
       </c>
       <c r="F6" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D7" t="n">
         <v>47.6</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="D8" t="n">
         <v>48.8</v>
@@ -716,10 +716,10 @@
         <v>51.2</v>
       </c>
       <c r="F8" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D9" t="n">
         <v>48.2</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="D10" t="n">
         <v>51.5</v>
@@ -788,10 +788,10 @@
         <v>48.5</v>
       </c>
       <c r="F10" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="G10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E11" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F11" t="n">
         <v>41.4</v>
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="D12" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E12" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F12" t="n">
         <v>39.5</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="D13" t="n">
         <v>49.8</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="D14" t="n">
         <v>50.3</v>
@@ -932,10 +932,10 @@
         <v>49.7</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="D15" t="n">
         <v>49.8</v>
@@ -968,10 +968,10 @@
         <v>50.2</v>
       </c>
       <c r="F15" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="D16" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E16" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F16" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G16" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1027,23 +1027,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1434</v>
+        <v>1480</v>
       </c>
       <c r="D17" t="n">
-        <v>49.2</v>
+        <v>47.2</v>
       </c>
       <c r="E17" t="n">
-        <v>50.8</v>
+        <v>52.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1063,17 +1063,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1475</v>
+        <v>1439</v>
       </c>
       <c r="D18" t="n">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="E18" t="n">
-        <v>52.7</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
         <v>49.7</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1424</v>
+        <v>1429</v>
       </c>
       <c r="D19" t="n">
         <v>49.8</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="D20" t="n">
         <v>49.4</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1211,19 +1211,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D22" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E22" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F22" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1247,19 +1247,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="D23" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E23" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F23" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="G23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="D24" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
         <v>54.8</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1445</v>
+        <v>1450</v>
       </c>
       <c r="D25" t="n">
         <v>51.5</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="D26" t="n">
         <v>50.8</v>
@@ -1387,20 +1387,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1438</v>
+        <v>1480</v>
       </c>
       <c r="D27" t="n">
-        <v>45.8</v>
+        <v>48.2</v>
       </c>
       <c r="E27" t="n">
-        <v>54.2</v>
+        <v>51.8</v>
       </c>
       <c r="F27" t="n">
-        <v>55.8</v>
+        <v>44.2</v>
       </c>
       <c r="G27" t="n">
         <v>5.8</v>
@@ -1423,23 +1423,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1475</v>
+        <v>1443</v>
       </c>
       <c r="D28" t="n">
-        <v>48.3</v>
+        <v>45.7</v>
       </c>
       <c r="E28" t="n">
-        <v>51.7</v>
+        <v>54.3</v>
       </c>
       <c r="F28" t="n">
-        <v>44.2</v>
+        <v>55.9</v>
       </c>
       <c r="G28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1459,17 +1459,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1464</v>
+        <v>1474</v>
       </c>
       <c r="D29" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
       <c r="E29" t="n">
-        <v>51.2</v>
+        <v>52.4</v>
       </c>
       <c r="F29" t="n">
         <v>43.6</v>
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1469</v>
       </c>
       <c r="D30" t="n">
-        <v>47.7</v>
+        <v>48.8</v>
       </c>
       <c r="E30" t="n">
-        <v>52.3</v>
+        <v>51.2</v>
       </c>
       <c r="F30" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1535,19 +1535,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1463</v>
+        <v>1468</v>
       </c>
       <c r="D31" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E31" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F31" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="G31" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1456</v>
+        <v>1461</v>
       </c>
       <c r="D32" t="n">
         <v>47.6</v>
@@ -1580,10 +1580,10 @@
         <v>52.4</v>
       </c>
       <c r="F32" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="G32" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="D33" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E33" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F33" t="n">
         <v>42.2</v>
@@ -1639,20 +1639,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EURAUD</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D34" t="n">
-        <v>48.2</v>
+        <v>46.8</v>
       </c>
       <c r="E34" t="n">
-        <v>51.8</v>
+        <v>53.2</v>
       </c>
       <c r="F34" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G34" t="n">
         <v>9</v>
@@ -1675,20 +1675,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D35" t="n">
-        <v>46.8</v>
+        <v>48.1</v>
       </c>
       <c r="E35" t="n">
-        <v>53.2</v>
+        <v>51.9</v>
       </c>
       <c r="F35" t="n">
-        <v>59.1</v>
+        <v>40.9</v>
       </c>
       <c r="G35" t="n">
         <v>9.1</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D36" t="n">
         <v>48</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1448</v>
+        <v>1322</v>
       </c>
       <c r="D37" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="E37" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="F37" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="G37" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1783,17 +1783,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1318</v>
+        <v>1453</v>
       </c>
       <c r="D38" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="E38" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="F38" t="n">
         <v>60.4</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="D39" t="n">
         <v>48.2</v>
@@ -1855,20 +1855,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1440</v>
+        <v>1485</v>
       </c>
       <c r="D40" t="n">
-        <v>51</v>
+        <v>49.8</v>
       </c>
       <c r="E40" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="F40" t="n">
-        <v>61.8</v>
+        <v>38.2</v>
       </c>
       <c r="G40" t="n">
         <v>11.8</v>
@@ -1891,23 +1891,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1480</v>
+        <v>1445</v>
       </c>
       <c r="D41" t="n">
-        <v>49.9</v>
+        <v>50.9</v>
       </c>
       <c r="E41" t="n">
-        <v>50.1</v>
+        <v>49.1</v>
       </c>
       <c r="F41" t="n">
-        <v>38.2</v>
+        <v>61.9</v>
       </c>
       <c r="G41" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D42" t="n">
         <v>49.9</v>
@@ -1940,10 +1940,10 @@
         <v>50.1</v>
       </c>
       <c r="F42" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="G42" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D43" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E43" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F43" t="n">
         <v>37.5</v>
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D44" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E44" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
         <v>37</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D45" t="n">
         <v>49.8</v>
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1478</v>
+        <v>1483</v>
       </c>
       <c r="D46" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E46" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F46" t="n">
         <v>36.2</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="D47" t="n">
         <v>49.3</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
@@ -2147,13 +2147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="D48" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E48" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F48" t="n">
         <v>35.5</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="D49" t="n">
         <v>47.9</v>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="D50" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E50" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F50" t="n">
         <v>66</v>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D51" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E51" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F51" t="n">
         <v>33.9</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="D52" t="n">
         <v>48.8</v>
@@ -2300,10 +2300,10 @@
         <v>51.2</v>
       </c>
       <c r="F52" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="G52" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2327,19 +2327,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D53" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E53" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F53" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="G53" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D55" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E55" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F55" t="n">
         <v>70.09999999999999</v>
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1459</v>
+        <v>1464</v>
       </c>
       <c r="D56" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E56" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F56" t="n">
         <v>75.2</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D57" t="n">
         <v>49.7</v>
@@ -2480,10 +2480,10 @@
         <v>50.3</v>
       </c>
       <c r="F57" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D58" t="n">
         <v>49.5</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="D59" t="n">
         <v>48.9</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="D61" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E61" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F61" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="G61" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2651,19 +2651,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D62" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="E62" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="F62" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D63" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E63" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F63" t="n">
         <v>58.2</v>
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="D64" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E64" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F64" t="n">
         <v>59.2</v>
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E65" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F65" t="n">
         <v>59.8</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D66" t="n">
         <v>48.5</v>
@@ -2804,10 +2804,10 @@
         <v>51.5</v>
       </c>
       <c r="F66" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G66" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -2831,19 +2831,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="D67" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="E67" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="G67" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="D68" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E68" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F68" t="n">
         <v>61.3</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D69" t="n">
         <v>48.1</v>
@@ -2912,10 +2912,10 @@
         <v>51.9</v>
       </c>
       <c r="F69" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="G69" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D70" t="n">
         <v>50</v>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71">
@@ -3047,13 +3047,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D73" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E73" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F73" t="n">
         <v>65.7</v>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="D78" t="n">
         <v>48.6</v>
@@ -3299,13 +3299,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D80" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F80" t="n">
         <v>60.6</v>
@@ -3335,19 +3335,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D81" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="E81" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="F81" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="G81" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82">
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D82" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E82" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F82" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3407,19 +3407,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D83" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="E83" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="F83" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3443,19 +3443,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D84" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E84" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F84" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="G84" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -3479,19 +3479,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D85" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E85" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F85" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D86" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E86" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F86" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G86" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
@@ -3551,19 +3551,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D87" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E87" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F87" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G87" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D88" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E88" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="F88" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="G88" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89">
@@ -3623,19 +3623,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D89" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="E89" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="F89" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="G89" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3659,19 +3659,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D90" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E90" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F90" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="G90" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91">
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D91" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E91" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F91" t="n">
         <v>62.7</v>
@@ -3731,19 +3731,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D92" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="E92" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="F92" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="G92" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -3767,19 +3767,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D93" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="E93" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="F93" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="G93" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="D94" t="n">
         <v>52</v>
@@ -3812,10 +3812,10 @@
         <v>48</v>
       </c>
       <c r="F94" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="G94" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="D95" t="n">
         <v>51.5</v>
@@ -3875,19 +3875,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="D96" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E96" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F96" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -3911,19 +3911,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="D97" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E97" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F97" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -3947,19 +3947,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D98" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E98" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G98" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D100" t="n">
         <v>50</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="D101" t="n">
         <v>50.3</v>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102">
@@ -4087,23 +4087,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2</v>
+        <v>50.5</v>
       </c>
       <c r="E102" t="n">
-        <v>50.8</v>
+        <v>49.5</v>
       </c>
       <c r="F102" t="n">
-        <v>60.1</v>
+        <v>60.2</v>
       </c>
       <c r="G102" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4123,17 +4123,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6</v>
+        <v>49.1</v>
       </c>
       <c r="E103" t="n">
-        <v>49.4</v>
+        <v>50.9</v>
       </c>
       <c r="F103" t="n">
         <v>60.2</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37346</v>
+        <v>37351</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37067</v>
+        <v>37072</v>
       </c>
       <c r="D3" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E3" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F3" t="n">
         <v>49.1</v>
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36892</v>
+        <v>36897</v>
       </c>
       <c r="D4" t="n">
         <v>48.9</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37618</v>
+        <v>37622</v>
       </c>
       <c r="D5" t="n">
         <v>51</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37669</v>
+        <v>37674</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37533</v>
+        <v>37538</v>
       </c>
       <c r="D7" t="n">
         <v>50.6</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37682</v>
+        <v>37687</v>
       </c>
       <c r="D8" t="n">
         <v>51.3</v>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37078</v>
+        <v>37083</v>
       </c>
       <c r="D9" t="n">
         <v>49.5</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37510</v>
+        <v>37515</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37568</v>
+        <v>37573</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37593</v>
+        <v>37597</v>
       </c>
       <c r="D12" t="n">
         <v>51.1</v>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37399</v>
+        <v>37404</v>
       </c>
       <c r="D13" t="n">
         <v>50.2</v>
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37351</v>
+        <v>37355</v>
       </c>
       <c r="D14" t="n">
         <v>49.9</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37478</v>
+        <v>37482</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37494</v>
+        <v>37499</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37620</v>
+        <v>37625</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37292</v>
+        <v>37297</v>
       </c>
       <c r="D19" t="n">
         <v>49.9</v>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36833</v>
+        <v>36838</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37454</v>
+        <v>37459</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34514</v>
+        <v>34519</v>
       </c>
       <c r="D22" t="n">
         <v>49.9</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37619</v>
+        <v>37624</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37386</v>
+        <v>37391</v>
       </c>
       <c r="D24" t="n">
         <v>48.9</v>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37358</v>
+        <v>37363</v>
       </c>
       <c r="D25" t="n">
         <v>49.8</v>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37630</v>
+        <v>37635</v>
       </c>
       <c r="D26" t="n">
         <v>49.1</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37312</v>
+        <v>37317</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>36981</v>
+        <v>36986</v>
       </c>
       <c r="D28" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E28" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F28" t="n">
         <v>54.5</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37124</v>
+        <v>37129</v>
       </c>
       <c r="D29" t="n">
         <v>49.9</v>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37676</v>
+        <v>37681</v>
       </c>
       <c r="D30" t="n">
         <v>49.5</v>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37489</v>
+        <v>37494</v>
       </c>
       <c r="D31" t="n">
         <v>50.5</v>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37534</v>
+        <v>37539</v>
       </c>
       <c r="D32" t="n">
         <v>51</v>
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37650</v>
+        <v>37655</v>
       </c>
       <c r="D33" t="n">
         <v>49.3</v>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37650</v>
+        <v>37655</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37616</v>
+        <v>37621</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37897</v>
+        <v>37902</v>
       </c>
       <c r="D36" t="n">
         <v>48.9</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37887</v>
+        <v>37892</v>
       </c>
       <c r="D37" t="n">
         <v>49</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34974</v>
+        <v>34978</v>
       </c>
       <c r="D38" t="n">
         <v>50.2</v>
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34627</v>
+        <v>34632</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -5593,17 +5593,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37248</v>
+        <v>37380</v>
       </c>
       <c r="D40" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="E40" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F40" t="n">
         <v>58.3</v>
@@ -5629,23 +5629,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37375</v>
+        <v>37253</v>
       </c>
       <c r="D41" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="E41" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="F41" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G41" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37421</v>
+        <v>37426</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37809</v>
+        <v>37814</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37863</v>
+        <v>37868</v>
       </c>
       <c r="D44" t="n">
         <v>49.1</v>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37857</v>
+        <v>37862</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37680</v>
+        <v>37685</v>
       </c>
       <c r="D46" t="n">
         <v>49.5</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37631</v>
+        <v>37636</v>
       </c>
       <c r="D47" t="n">
         <v>49.4</v>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37805</v>
+        <v>37810</v>
       </c>
       <c r="D48" t="n">
         <v>49.8</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34461</v>
+        <v>34466</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37291</v>
+        <v>37296</v>
       </c>
       <c r="D50" t="n">
         <v>49.5</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37333</v>
+        <v>37338</v>
       </c>
       <c r="D51" t="n">
         <v>49.9</v>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37290</v>
+        <v>37295</v>
       </c>
       <c r="D52" t="n">
         <v>50.3</v>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37754</v>
+        <v>37759</v>
       </c>
       <c r="D53" t="n">
         <v>49</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35801</v>
+        <v>35805</v>
       </c>
       <c r="D54" t="n">
         <v>48.8</v>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37508</v>
+        <v>37513</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37219</v>
+        <v>37224</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37571</v>
+        <v>37576</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37644</v>
+        <v>37649</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37847</v>
+        <v>37852</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34685</v>
+        <v>34690</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36673</v>
+        <v>36678</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23186</v>
+        <v>23187</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23612</v>
+        <v>23613</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23561</v>
+        <v>23562</v>
       </c>
       <c r="D65" t="n">
         <v>51.1</v>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37553</v>
+        <v>37558</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -6569,7 +6569,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20929</v>
+        <v>20930</v>
       </c>
       <c r="D67" t="n">
         <v>51.9</v>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37061</v>
+        <v>37066</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30157</v>
+        <v>30158</v>
       </c>
       <c r="D69" t="n">
         <v>50.9</v>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35422</v>
+        <v>35427</v>
       </c>
       <c r="D70" t="n">
         <v>50.4</v>
@@ -6749,7 +6749,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32799</v>
+        <v>32800</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35097</v>
+        <v>35102</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28338</v>
+        <v>28339</v>
       </c>
       <c r="D79" t="n">
         <v>49.4</v>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27199</v>
+        <v>27203</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10322</v>
+        <v>10323</v>
       </c>
       <c r="D82" t="n">
         <v>51.6</v>
@@ -7118,10 +7118,10 @@
         <v>48.4</v>
       </c>
       <c r="F82" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10325</v>
+        <v>10326</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10106</v>
+        <v>10107</v>
       </c>
       <c r="D84" t="n">
         <v>50.8</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10620</v>
+        <v>10621</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10108</v>
+        <v>10109</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10576</v>
+        <v>10577</v>
       </c>
       <c r="D87" t="n">
         <v>50.9</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10682</v>
+        <v>10683</v>
       </c>
       <c r="D88" t="n">
         <v>51.7</v>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10814</v>
+        <v>10815</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10818</v>
+        <v>10819</v>
       </c>
       <c r="D90" t="n">
         <v>51.6</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10746</v>
+        <v>10747</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10171</v>
+        <v>10172</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10102</v>
+        <v>10103</v>
       </c>
       <c r="D93" t="n">
         <v>51.4</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37097</v>
+        <v>37102</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37689</v>
+        <v>37694</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35347</v>
+        <v>35352</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37032</v>
+        <v>37037</v>
       </c>
       <c r="D97" t="n">
         <v>49.2</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37806</v>
+        <v>37811</v>
       </c>
       <c r="D98" t="n">
         <v>50.3</v>
@@ -7717,23 +7717,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37603</v>
+        <v>37208</v>
       </c>
       <c r="D99" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E99" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F99" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
@@ -7753,17 +7753,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37203</v>
+        <v>37608</v>
       </c>
       <c r="D100" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F100" t="n">
         <v>54.3</v>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37468</v>
+        <v>37473</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37883</v>
+        <v>37888</v>
       </c>
       <c r="D102" t="n">
         <v>50</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="D2" t="n">
         <v>50.3</v>
@@ -7976,10 +7976,10 @@
         <v>49.7</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="D3" t="n">
         <v>49.8</v>
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="D4" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E4" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F4" t="n">
         <v>39.5</v>
@@ -8075,13 +8075,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="D5" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E5" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F5" t="n">
         <v>41.4</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="D6" t="n">
         <v>51.5</v>
@@ -8120,10 +8120,10 @@
         <v>48.5</v>
       </c>
       <c r="F6" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="G6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8147,19 +8147,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D7" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E7" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F7" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D8" t="n">
         <v>49.2</v>
@@ -8192,10 +8192,10 @@
         <v>50.8</v>
       </c>
       <c r="F8" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="D9" t="n">
         <v>51.3</v>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="D10" t="n">
         <v>48.9</v>
@@ -8291,13 +8291,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F11" t="n">
         <v>51</v>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D12" t="n">
         <v>47.6</v>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="D13" t="n">
         <v>48.8</v>
@@ -8372,10 +8372,10 @@
         <v>51.2</v>
       </c>
       <c r="F13" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D14" t="n">
         <v>48.2</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="D15" t="n">
         <v>49.8</v>
@@ -8444,10 +8444,10 @@
         <v>50.2</v>
       </c>
       <c r="F15" t="n">
-        <v>65.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -8471,19 +8471,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="D16" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E16" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F16" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G16" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -8543,19 +8543,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D18" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E18" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -8579,13 +8579,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D19" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E19" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F19" t="n">
         <v>33.9</v>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="D20" t="n">
         <v>47.9</v>
@@ -8651,13 +8651,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="D21" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E21" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F21" t="n">
         <v>35.5</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="D22" t="n">
         <v>49.3</v>
@@ -8723,13 +8723,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1478</v>
+        <v>1483</v>
       </c>
       <c r="D23" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E23" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F23" t="n">
         <v>36.2</v>
@@ -8759,13 +8759,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D24" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
         <v>37</v>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D25" t="n">
         <v>49.8</v>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D26" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F26" t="n">
         <v>37.5</v>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -8876,10 +8876,10 @@
         <v>50.1</v>
       </c>
       <c r="F27" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="G27" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -8903,13 +8903,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="D28" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E28" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F28" t="n">
         <v>38.2</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D29" t="n">
         <v>48</v>
@@ -8975,19 +8975,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D30" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E30" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9011,13 +9011,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="D31" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E31" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F31" t="n">
         <v>42.2</v>
@@ -9047,19 +9047,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D32" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="E32" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="F32" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="G32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D33" t="n">
         <v>48.8</v>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="D34" t="n">
         <v>50.8</v>
@@ -9155,13 +9155,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D35" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E35" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F35" t="n">
         <v>44.2</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1445</v>
+        <v>1450</v>
       </c>
       <c r="D36" t="n">
         <v>51.5</v>
@@ -9227,19 +9227,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="D37" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E37" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F37" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="G37" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="D38" t="n">
         <v>49.4</v>
@@ -9299,13 +9299,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="D39" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="F39" t="n">
         <v>49.7</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D40" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="E40" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="F40" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1424</v>
+        <v>1429</v>
       </c>
       <c r="D41" t="n">
         <v>49.8</v>
@@ -9443,19 +9443,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="D43" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E43" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F43" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="G43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="D44" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E44" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
         <v>54.8</v>
@@ -9515,19 +9515,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="D45" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="E45" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="F45" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="G45" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -9551,19 +9551,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1463</v>
+        <v>1468</v>
       </c>
       <c r="D46" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E46" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F46" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="G46" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1456</v>
+        <v>1461</v>
       </c>
       <c r="D47" t="n">
         <v>47.6</v>
@@ -9596,10 +9596,10 @@
         <v>52.4</v>
       </c>
       <c r="F47" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="G47" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="D48" t="n">
         <v>46.8</v>
@@ -9632,10 +9632,10 @@
         <v>53.2</v>
       </c>
       <c r="F48" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="G48" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -9655,23 +9655,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1448</v>
+        <v>1322</v>
       </c>
       <c r="D49" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="E49" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="F49" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="G49" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -9691,17 +9691,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1318</v>
+        <v>1453</v>
       </c>
       <c r="D50" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="E50" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="F50" t="n">
         <v>60.4</v>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="D51" t="n">
         <v>48.2</v>
@@ -9767,19 +9767,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E52" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F52" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="D53" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E53" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F53" t="n">
         <v>66</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="D54" t="n">
         <v>48.8</v>
@@ -9848,10 +9848,10 @@
         <v>51.2</v>
       </c>
       <c r="F54" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="G54" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -9875,13 +9875,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D55" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E55" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F55" t="n">
         <v>70.09999999999999</v>
@@ -9911,13 +9911,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1459</v>
+        <v>1464</v>
       </c>
       <c r="D56" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E56" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F56" t="n">
         <v>75.2</v>
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D57" t="n">
         <v>49.7</v>
@@ -9956,10 +9956,10 @@
         <v>50.3</v>
       </c>
       <c r="F57" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D58" t="n">
         <v>49.5</v>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="D59" t="n">
         <v>48.9</v>
@@ -10055,19 +10055,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="D60" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E60" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F60" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="G60" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10127,19 +10127,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D62" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="E62" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="F62" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D63" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E63" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F63" t="n">
         <v>58.2</v>
@@ -10199,13 +10199,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="D64" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E64" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F64" t="n">
         <v>59.2</v>
@@ -10235,13 +10235,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E65" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F65" t="n">
         <v>59.8</v>
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D66" t="n">
         <v>48.5</v>
@@ -10280,10 +10280,10 @@
         <v>51.5</v>
       </c>
       <c r="F66" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G66" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -10307,19 +10307,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="D67" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="E67" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="G67" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -10343,13 +10343,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="D68" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E68" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F68" t="n">
         <v>61.3</v>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D69" t="n">
         <v>48.1</v>
@@ -10388,10 +10388,10 @@
         <v>51.9</v>
       </c>
       <c r="F69" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="G69" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D70" t="n">
         <v>50</v>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71">
@@ -10523,13 +10523,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D73" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E73" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F73" t="n">
         <v>65.7</v>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="D78" t="n">
         <v>48.6</v>
@@ -10775,13 +10775,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D80" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F80" t="n">
         <v>60.6</v>
@@ -10811,19 +10811,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D81" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="E81" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="F81" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="G81" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -10847,19 +10847,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D82" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E82" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F82" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="G82" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -10883,19 +10883,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D83" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="E83" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="F83" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -10919,19 +10919,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D84" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E84" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F84" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -10955,19 +10955,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D85" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E85" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F85" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -10991,19 +10991,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D86" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E86" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F86" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G86" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87">
@@ -11027,19 +11027,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D87" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E87" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F87" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G87" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11063,19 +11063,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D88" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E88" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="F88" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="G88" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -11099,19 +11099,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D89" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="E89" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="F89" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="G89" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -11135,19 +11135,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D90" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E90" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F90" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="G90" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91">
@@ -11171,13 +11171,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D91" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E91" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F91" t="n">
         <v>62.7</v>
@@ -11207,19 +11207,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D92" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="E92" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="F92" t="n">
-        <v>63.1</v>
+        <v>63.2</v>
       </c>
       <c r="G92" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -11243,19 +11243,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D93" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="E93" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="F93" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="G93" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="D94" t="n">
         <v>52</v>
@@ -11288,10 +11288,10 @@
         <v>48</v>
       </c>
       <c r="F94" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="G94" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="D95" t="n">
         <v>51.5</v>
@@ -11351,19 +11351,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="D96" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E96" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F96" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -11387,19 +11387,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="D97" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E97" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F97" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -11423,19 +11423,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D98" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E98" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G98" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="D100" t="n">
         <v>50</v>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="D101" t="n">
         <v>50.3</v>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102">
@@ -11563,23 +11563,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2</v>
+        <v>50.5</v>
       </c>
       <c r="E102" t="n">
-        <v>50.8</v>
+        <v>49.5</v>
       </c>
       <c r="F102" t="n">
-        <v>60.1</v>
+        <v>60.2</v>
       </c>
       <c r="G102" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -11599,17 +11599,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6</v>
+        <v>49.1</v>
       </c>
       <c r="E103" t="n">
-        <v>49.4</v>
+        <v>50.9</v>
       </c>
       <c r="F103" t="n">
         <v>60.2</v>
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37351</v>
+        <v>37355</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37399</v>
+        <v>37404</v>
       </c>
       <c r="D3" t="n">
         <v>50.2</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37593</v>
+        <v>37597</v>
       </c>
       <c r="D4" t="n">
         <v>51.1</v>
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37078</v>
+        <v>37083</v>
       </c>
       <c r="D5" t="n">
         <v>49.5</v>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37533</v>
+        <v>37538</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -11885,13 +11885,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37067</v>
+        <v>37072</v>
       </c>
       <c r="D7" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E7" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F7" t="n">
         <v>49.1</v>
@@ -11921,7 +11921,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36892</v>
+        <v>36897</v>
       </c>
       <c r="D8" t="n">
         <v>48.9</v>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37346</v>
+        <v>37351</v>
       </c>
       <c r="D9" t="n">
         <v>49.9</v>
@@ -11993,7 +11993,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37618</v>
+        <v>37622</v>
       </c>
       <c r="D10" t="n">
         <v>51</v>
@@ -12029,7 +12029,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37669</v>
+        <v>37674</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37682</v>
+        <v>37687</v>
       </c>
       <c r="D12" t="n">
         <v>51.3</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37510</v>
+        <v>37515</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37568</v>
+        <v>37573</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37478</v>
+        <v>37482</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37494</v>
+        <v>37499</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35801</v>
+        <v>35805</v>
       </c>
       <c r="D17" t="n">
         <v>48.8</v>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37754</v>
+        <v>37759</v>
       </c>
       <c r="D18" t="n">
         <v>49</v>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37290</v>
+        <v>37295</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34461</v>
+        <v>34466</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37805</v>
+        <v>37810</v>
       </c>
       <c r="D21" t="n">
         <v>49.8</v>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37631</v>
+        <v>37636</v>
       </c>
       <c r="D22" t="n">
         <v>49.4</v>
@@ -12461,7 +12461,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37680</v>
+        <v>37685</v>
       </c>
       <c r="D23" t="n">
         <v>49.5</v>
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37857</v>
+        <v>37862</v>
       </c>
       <c r="D24" t="n">
         <v>49.3</v>
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37809</v>
+        <v>37814</v>
       </c>
       <c r="D25" t="n">
         <v>49.9</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37863</v>
+        <v>37868</v>
       </c>
       <c r="D26" t="n">
         <v>49.1</v>
@@ -12605,7 +12605,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34627</v>
+        <v>34632</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37887</v>
+        <v>37892</v>
       </c>
       <c r="D28" t="n">
         <v>49</v>
@@ -12677,7 +12677,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37897</v>
+        <v>37902</v>
       </c>
       <c r="D29" t="n">
         <v>48.9</v>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37616</v>
+        <v>37621</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37650</v>
+        <v>37655</v>
       </c>
       <c r="D31" t="n">
         <v>49.2</v>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37650</v>
+        <v>37655</v>
       </c>
       <c r="D32" t="n">
         <v>49.3</v>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37676</v>
+        <v>37681</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37630</v>
+        <v>37635</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -12893,7 +12893,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37619</v>
+        <v>37624</v>
       </c>
       <c r="D35" t="n">
         <v>49.6</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34514</v>
+        <v>34519</v>
       </c>
       <c r="D36" t="n">
         <v>49.9</v>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37454</v>
+        <v>37459</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36833</v>
+        <v>36838</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37620</v>
+        <v>37625</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -13109,7 +13109,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37292</v>
+        <v>37297</v>
       </c>
       <c r="D41" t="n">
         <v>49.9</v>
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37386</v>
+        <v>37391</v>
       </c>
       <c r="D42" t="n">
         <v>48.9</v>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37358</v>
+        <v>37363</v>
       </c>
       <c r="D43" t="n">
         <v>49.8</v>
@@ -13217,7 +13217,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37312</v>
+        <v>37317</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -13253,13 +13253,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>36981</v>
+        <v>36986</v>
       </c>
       <c r="D45" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E45" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F45" t="n">
         <v>54.5</v>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37124</v>
+        <v>37129</v>
       </c>
       <c r="D46" t="n">
         <v>49.9</v>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37489</v>
+        <v>37494</v>
       </c>
       <c r="D47" t="n">
         <v>50.5</v>
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37534</v>
+        <v>37539</v>
       </c>
       <c r="D48" t="n">
         <v>51</v>
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34974</v>
+        <v>34978</v>
       </c>
       <c r="D49" t="n">
         <v>50.2</v>
@@ -13429,17 +13429,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37248</v>
+        <v>37380</v>
       </c>
       <c r="D50" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="E50" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F50" t="n">
         <v>58.3</v>
@@ -13465,23 +13465,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37375</v>
+        <v>37253</v>
       </c>
       <c r="D51" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="E51" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="F51" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G51" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37421</v>
+        <v>37426</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -13541,7 +13541,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37291</v>
+        <v>37296</v>
       </c>
       <c r="D53" t="n">
         <v>49.5</v>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37333</v>
+        <v>37338</v>
       </c>
       <c r="D54" t="n">
         <v>49.9</v>
@@ -13613,7 +13613,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37508</v>
+        <v>37513</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37219</v>
+        <v>37224</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37571</v>
+        <v>37576</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37644</v>
+        <v>37649</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37847</v>
+        <v>37852</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34685</v>
+        <v>34690</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36673</v>
+        <v>36678</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -13901,7 +13901,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23186</v>
+        <v>23187</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -13937,7 +13937,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23612</v>
+        <v>23613</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23561</v>
+        <v>23562</v>
       </c>
       <c r="D65" t="n">
         <v>51.1</v>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37553</v>
+        <v>37558</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -14045,7 +14045,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20929</v>
+        <v>20930</v>
       </c>
       <c r="D67" t="n">
         <v>51.9</v>
@@ -14081,7 +14081,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37061</v>
+        <v>37066</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30157</v>
+        <v>30158</v>
       </c>
       <c r="D69" t="n">
         <v>50.9</v>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35422</v>
+        <v>35427</v>
       </c>
       <c r="D70" t="n">
         <v>50.4</v>
@@ -14225,7 +14225,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32799</v>
+        <v>32800</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35097</v>
+        <v>35102</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28338</v>
+        <v>28339</v>
       </c>
       <c r="D79" t="n">
         <v>49.4</v>
@@ -14549,7 +14549,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27199</v>
+        <v>27203</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10322</v>
+        <v>10323</v>
       </c>
       <c r="D82" t="n">
         <v>51.6</v>
@@ -14594,10 +14594,10 @@
         <v>48.4</v>
       </c>
       <c r="F82" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
@@ -14621,7 +14621,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10325</v>
+        <v>10326</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10106</v>
+        <v>10107</v>
       </c>
       <c r="D84" t="n">
         <v>50.8</v>
@@ -14693,7 +14693,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10620</v>
+        <v>10621</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10108</v>
+        <v>10109</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -14765,7 +14765,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10576</v>
+        <v>10577</v>
       </c>
       <c r="D87" t="n">
         <v>50.9</v>
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10682</v>
+        <v>10683</v>
       </c>
       <c r="D88" t="n">
         <v>51.7</v>
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10814</v>
+        <v>10815</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90">
@@ -14873,7 +14873,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10818</v>
+        <v>10819</v>
       </c>
       <c r="D90" t="n">
         <v>51.6</v>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10746</v>
+        <v>10747</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -14945,7 +14945,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10171</v>
+        <v>10172</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -14981,7 +14981,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10102</v>
+        <v>10103</v>
       </c>
       <c r="D93" t="n">
         <v>51.4</v>
@@ -15017,7 +15017,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37097</v>
+        <v>37102</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37689</v>
+        <v>37694</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -15089,7 +15089,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35347</v>
+        <v>35352</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37032</v>
+        <v>37037</v>
       </c>
       <c r="D97" t="n">
         <v>49.2</v>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37806</v>
+        <v>37811</v>
       </c>
       <c r="D98" t="n">
         <v>50.3</v>
@@ -15193,23 +15193,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37603</v>
+        <v>37208</v>
       </c>
       <c r="D99" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E99" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F99" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -15229,17 +15229,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37203</v>
+        <v>37608</v>
       </c>
       <c r="D100" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F100" t="n">
         <v>54.3</v>
@@ -15269,7 +15269,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37468</v>
+        <v>37473</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37883</v>
+        <v>37888</v>
       </c>
       <c r="D102" t="n">
         <v>50</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>usd_linked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>overall_rank</t>
         </is>
       </c>
@@ -513,7 +518,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -549,7 +557,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -585,7 +596,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>14</v>
       </c>
     </row>
@@ -621,7 +635,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -657,7 +674,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>17</v>
       </c>
     </row>
@@ -693,7 +713,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -729,7 +752,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>23</v>
       </c>
     </row>
@@ -765,7 +791,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>35</v>
       </c>
     </row>
@@ -801,7 +830,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>41</v>
       </c>
     </row>
@@ -837,7 +869,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>47</v>
       </c>
     </row>
@@ -873,7 +908,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>62</v>
       </c>
     </row>
@@ -909,7 +947,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>81</v>
       </c>
     </row>
@@ -945,7 +986,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>85</v>
       </c>
     </row>
@@ -981,7 +1025,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1017,7 +1064,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1053,7 +1103,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1089,7 +1142,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1125,7 +1181,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1161,7 +1220,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1197,7 +1259,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1233,7 +1298,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1269,7 +1337,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1305,7 +1376,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1341,7 +1415,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1377,7 +1454,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1413,7 +1493,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1449,7 +1532,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1485,7 +1571,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1521,7 +1610,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1557,7 +1649,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1593,7 +1688,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>37</v>
       </c>
     </row>
@@ -1629,7 +1727,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1665,7 +1766,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>49</v>
       </c>
     </row>
@@ -1701,7 +1805,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1737,7 +1844,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>53</v>
       </c>
     </row>
@@ -1773,7 +1883,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1809,7 +1922,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>61</v>
       </c>
     </row>
@@ -1845,7 +1961,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>64</v>
       </c>
     </row>
@@ -1881,7 +2000,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>69</v>
       </c>
     </row>
@@ -1917,7 +2039,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1953,7 +2078,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
         <v>71</v>
       </c>
     </row>
@@ -1989,7 +2117,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
         <v>74</v>
       </c>
     </row>
@@ -2025,7 +2156,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>77</v>
       </c>
     </row>
@@ -2061,7 +2195,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>78</v>
       </c>
     </row>
@@ -2097,7 +2234,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2133,7 +2273,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
         <v>83</v>
       </c>
     </row>
@@ -2169,7 +2312,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
         <v>86</v>
       </c>
     </row>
@@ -2205,7 +2351,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
         <v>87</v>
       </c>
     </row>
@@ -2241,7 +2390,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>91</v>
       </c>
     </row>
@@ -2277,7 +2429,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
         <v>92</v>
       </c>
     </row>
@@ -2313,7 +2468,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>93</v>
       </c>
     </row>
@@ -2349,7 +2507,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>94</v>
       </c>
     </row>
@@ -2385,7 +2546,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
         <v>96</v>
       </c>
     </row>
@@ -2421,7 +2585,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>95</v>
       </c>
     </row>
@@ -2457,7 +2624,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>99</v>
       </c>
     </row>
@@ -2493,7 +2663,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2529,7 +2702,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>101</v>
       </c>
     </row>
@@ -2565,7 +2741,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>102</v>
       </c>
     </row>
@@ -2601,7 +2780,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2637,7 +2819,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>33</v>
       </c>
     </row>
@@ -2673,7 +2858,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>42</v>
       </c>
     </row>
@@ -2709,7 +2897,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>43</v>
       </c>
     </row>
@@ -2745,7 +2936,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>51</v>
       </c>
     </row>
@@ -2781,7 +2975,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2817,7 +3014,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2853,7 +3053,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>66</v>
       </c>
     </row>
@@ -2889,7 +3092,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>67</v>
       </c>
     </row>
@@ -2925,7 +3131,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
         <v>68</v>
       </c>
     </row>
@@ -2961,7 +3170,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>72</v>
       </c>
     </row>
@@ -2997,7 +3209,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>75</v>
       </c>
     </row>
@@ -3033,7 +3248,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>79</v>
       </c>
     </row>
@@ -3069,7 +3287,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>90</v>
       </c>
     </row>
@@ -3105,7 +3326,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3141,7 +3365,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3177,7 +3404,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3213,7 +3443,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>24</v>
       </c>
     </row>
@@ -3249,7 +3482,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>97</v>
       </c>
     </row>
@@ -3285,7 +3521,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>36</v>
       </c>
     </row>
@@ -3321,7 +3560,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>63</v>
       </c>
     </row>
@@ -3357,7 +3599,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3393,7 +3638,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3429,7 +3677,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3465,7 +3716,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3501,7 +3755,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3537,7 +3794,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3573,7 +3833,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3609,7 +3872,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
         <v>57</v>
       </c>
     </row>
@@ -3645,7 +3911,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
         <v>65</v>
       </c>
     </row>
@@ -3681,7 +3950,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>73</v>
       </c>
     </row>
@@ -3717,7 +3989,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>76</v>
       </c>
     </row>
@@ -3753,7 +4028,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>80</v>
       </c>
     </row>
@@ -3789,7 +4067,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>98</v>
       </c>
     </row>
@@ -3825,7 +4106,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>38</v>
       </c>
     </row>
@@ -3861,7 +4145,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>40</v>
       </c>
     </row>
@@ -3897,7 +4184,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
         <v>44</v>
       </c>
     </row>
@@ -3933,7 +4223,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3969,7 +4262,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
         <v>46</v>
       </c>
     </row>
@@ -4005,7 +4301,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>48</v>
       </c>
     </row>
@@ -4041,7 +4340,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>52</v>
       </c>
     </row>
@@ -4077,7 +4379,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4113,7 +4418,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>58</v>
       </c>
     </row>
@@ -4149,7 +4457,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>59</v>
       </c>
     </row>
@@ -4164,7 +4475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4215,6 +4526,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>usd_linked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>overall_rank</t>
         </is>
       </c>
@@ -4251,7 +4567,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4287,7 +4606,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4323,7 +4645,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4359,7 +4684,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4395,7 +4723,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4431,7 +4762,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4467,7 +4801,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4503,7 +4840,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4539,7 +4879,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -4575,7 +4918,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>46</v>
       </c>
     </row>
@@ -4611,7 +4957,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>70</v>
       </c>
     </row>
@@ -4647,7 +4996,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4683,7 +5035,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>85</v>
       </c>
     </row>
@@ -4719,7 +5074,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>89</v>
       </c>
     </row>
@@ -4755,7 +5113,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>90</v>
       </c>
     </row>
@@ -4791,7 +5152,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4827,7 +5191,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4863,7 +5230,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4899,7 +5269,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4935,7 +5308,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4971,7 +5347,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5007,7 +5386,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5043,7 +5425,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>26</v>
       </c>
     </row>
@@ -5079,7 +5464,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>27</v>
       </c>
     </row>
@@ -5115,7 +5503,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>32</v>
       </c>
     </row>
@@ -5151,7 +5542,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>37</v>
       </c>
     </row>
@@ -5187,7 +5581,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>38</v>
       </c>
     </row>
@@ -5223,7 +5620,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5259,7 +5659,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>45</v>
       </c>
     </row>
@@ -5295,7 +5698,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>47</v>
       </c>
     </row>
@@ -5331,7 +5737,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>48</v>
       </c>
     </row>
@@ -5367,7 +5776,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>49</v>
       </c>
     </row>
@@ -5403,7 +5815,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>52</v>
       </c>
     </row>
@@ -5439,7 +5854,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>56</v>
       </c>
     </row>
@@ -5475,7 +5893,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>62</v>
       </c>
     </row>
@@ -5511,7 +5932,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>65</v>
       </c>
     </row>
@@ -5547,7 +5971,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>66</v>
       </c>
     </row>
@@ -5583,7 +6010,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
         <v>69</v>
       </c>
     </row>
@@ -5619,7 +6049,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>71</v>
       </c>
     </row>
@@ -5655,7 +6088,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>73</v>
       </c>
     </row>
@@ -5691,7 +6127,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>75</v>
       </c>
     </row>
@@ -5727,7 +6166,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5763,7 +6205,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
         <v>77</v>
       </c>
     </row>
@@ -5799,7 +6244,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>82</v>
       </c>
     </row>
@@ -5835,7 +6283,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
         <v>83</v>
       </c>
     </row>
@@ -5871,7 +6322,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
         <v>86</v>
       </c>
     </row>
@@ -5907,7 +6361,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
         <v>87</v>
       </c>
     </row>
@@ -5943,7 +6400,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
         <v>88</v>
       </c>
     </row>
@@ -5979,7 +6439,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>91</v>
       </c>
     </row>
@@ -6015,7 +6478,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>92</v>
       </c>
     </row>
@@ -6051,7 +6517,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
         <v>93</v>
       </c>
     </row>
@@ -6087,7 +6556,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>94</v>
       </c>
     </row>
@@ -6123,7 +6595,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
         <v>98</v>
       </c>
     </row>
@@ -6159,7 +6634,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>97</v>
       </c>
     </row>
@@ -6195,7 +6673,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>99</v>
       </c>
     </row>
@@ -6231,7 +6712,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>100</v>
       </c>
     </row>
@@ -6267,7 +6751,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>101</v>
       </c>
     </row>
@@ -6303,7 +6790,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>102</v>
       </c>
     </row>
@@ -6339,7 +6829,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6375,7 +6868,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6411,7 +6907,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>41</v>
       </c>
     </row>
@@ -6447,7 +6946,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>44</v>
       </c>
     </row>
@@ -6483,7 +6985,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6519,7 +7024,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>53</v>
       </c>
     </row>
@@ -6555,7 +7063,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>54</v>
       </c>
     </row>
@@ -6591,7 +7102,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>57</v>
       </c>
     </row>
@@ -6627,7 +7141,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>58</v>
       </c>
     </row>
@@ -6663,7 +7180,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6699,7 +7219,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>61</v>
       </c>
     </row>
@@ -6735,7 +7258,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6771,7 +7297,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>74</v>
       </c>
     </row>
@@ -6807,7 +7336,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>78</v>
       </c>
     </row>
@@ -6843,7 +7375,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6879,7 +7414,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6915,7 +7453,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>20</v>
       </c>
     </row>
@@ -6951,7 +7492,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>21</v>
       </c>
     </row>
@@ -6987,7 +7531,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>95</v>
       </c>
     </row>
@@ -7023,7 +7570,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>51</v>
       </c>
     </row>
@@ -7059,7 +7609,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>55</v>
       </c>
     </row>
@@ -7095,7 +7648,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>64</v>
       </c>
     </row>
@@ -7131,7 +7687,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>17</v>
       </c>
     </row>
@@ -7167,7 +7726,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7203,7 +7765,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7239,7 +7804,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>42</v>
       </c>
     </row>
@@ -7275,7 +7843,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>59</v>
       </c>
     </row>
@@ -7311,7 +7882,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
         <v>67</v>
       </c>
     </row>
@@ -7347,7 +7921,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
         <v>68</v>
       </c>
     </row>
@@ -7383,7 +7960,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
         <v>72</v>
       </c>
     </row>
@@ -7419,7 +7999,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>79</v>
       </c>
     </row>
@@ -7455,7 +8038,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>81</v>
       </c>
     </row>
@@ -7491,7 +8077,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>84</v>
       </c>
     </row>
@@ -7527,7 +8116,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>96</v>
       </c>
     </row>
@@ -7563,7 +8155,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>23</v>
       </c>
     </row>
@@ -7599,7 +8194,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>24</v>
       </c>
     </row>
@@ -7635,7 +8233,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
         <v>25</v>
       </c>
     </row>
@@ -7671,7 +8272,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>28</v>
       </c>
     </row>
@@ -7707,7 +8311,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
         <v>29</v>
       </c>
     </row>
@@ -7743,7 +8350,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>33</v>
       </c>
     </row>
@@ -7779,7 +8389,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>34</v>
       </c>
     </row>
@@ -7815,7 +8428,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>36</v>
       </c>
     </row>
@@ -7851,7 +8467,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>39</v>
       </c>
     </row>
@@ -7887,7 +8506,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>43</v>
       </c>
     </row>
@@ -7902,7 +8524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7953,6 +8575,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>usd_linked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>overall_rank</t>
         </is>
       </c>
@@ -7989,7 +8616,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8025,7 +8655,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8061,7 +8694,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -8097,7 +8733,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -8133,7 +8772,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>19</v>
       </c>
     </row>
@@ -8169,7 +8811,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>29</v>
       </c>
     </row>
@@ -8205,7 +8850,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -8241,7 +8889,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>31</v>
       </c>
     </row>
@@ -8277,7 +8928,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>33</v>
       </c>
     </row>
@@ -8313,7 +8967,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>39</v>
       </c>
     </row>
@@ -8349,7 +9006,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>47</v>
       </c>
     </row>
@@ -8385,7 +9045,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>49</v>
       </c>
     </row>
@@ -8421,7 +9084,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>55</v>
       </c>
     </row>
@@ -8457,7 +9123,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>91</v>
       </c>
     </row>
@@ -8493,7 +9162,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>92</v>
       </c>
     </row>
@@ -8529,7 +9201,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8565,7 +9240,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8601,7 +9279,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8637,7 +9318,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8673,7 +9357,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8709,7 +9396,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8745,7 +9435,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8781,7 +9474,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8817,7 +9513,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>11</v>
       </c>
     </row>
@@ -8853,7 +9552,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8889,7 +9591,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
         <v>13</v>
       </c>
     </row>
@@ -8925,7 +9630,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>14</v>
       </c>
     </row>
@@ -8961,7 +9669,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>16</v>
       </c>
     </row>
@@ -8997,7 +9708,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>17</v>
       </c>
     </row>
@@ -9033,7 +9747,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
         <v>20</v>
       </c>
     </row>
@@ -9069,7 +9786,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>22</v>
       </c>
     </row>
@@ -9105,7 +9825,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>23</v>
       </c>
     </row>
@@ -9141,7 +9864,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>25</v>
       </c>
     </row>
@@ -9177,7 +9903,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>26</v>
       </c>
     </row>
@@ -9213,7 +9942,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>27</v>
       </c>
     </row>
@@ -9249,7 +9981,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>28</v>
       </c>
     </row>
@@ -9285,7 +10020,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>34</v>
       </c>
     </row>
@@ -9321,7 +10059,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
         <v>36</v>
       </c>
     </row>
@@ -9357,7 +10098,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
         <v>37</v>
       </c>
     </row>
@@ -9393,7 +10137,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>40</v>
       </c>
     </row>
@@ -9429,7 +10176,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
         <v>41</v>
       </c>
     </row>
@@ -9465,7 +10215,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>46</v>
       </c>
     </row>
@@ -9501,7 +10254,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9537,7 +10293,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>52</v>
       </c>
     </row>
@@ -9573,7 +10332,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>54</v>
       </c>
     </row>
@@ -9609,7 +10371,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>57</v>
       </c>
     </row>
@@ -9645,7 +10410,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>66</v>
       </c>
     </row>
@@ -9681,7 +10449,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>75</v>
       </c>
     </row>
@@ -9717,7 +10488,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>76</v>
       </c>
     </row>
@@ -9753,7 +10527,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>78</v>
       </c>
     </row>
@@ -9789,7 +10566,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>83</v>
       </c>
     </row>
@@ -9825,7 +10605,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>94</v>
       </c>
     </row>
@@ -9861,7 +10644,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>95</v>
       </c>
     </row>
@@ -9897,7 +10683,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9933,7 +10722,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>99</v>
       </c>
     </row>
@@ -9969,7 +10761,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>100</v>
       </c>
     </row>
@@ -10005,7 +10800,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>101</v>
       </c>
     </row>
@@ -10041,7 +10839,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>102</v>
       </c>
     </row>
@@ -10077,7 +10878,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>21</v>
       </c>
     </row>
@@ -10113,7 +10917,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>24</v>
       </c>
     </row>
@@ -10149,7 +10956,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>60</v>
       </c>
     </row>
@@ -10185,7 +10995,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>61</v>
       </c>
     </row>
@@ -10221,7 +11034,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>67</v>
       </c>
     </row>
@@ -10257,7 +11073,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>69</v>
       </c>
     </row>
@@ -10293,7 +11112,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>71</v>
       </c>
     </row>
@@ -10329,7 +11151,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>80</v>
       </c>
     </row>
@@ -10365,7 +11190,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>81</v>
       </c>
     </row>
@@ -10401,7 +11229,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
         <v>82</v>
       </c>
     </row>
@@ -10437,7 +11268,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>84</v>
       </c>
     </row>
@@ -10473,7 +11307,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>86</v>
       </c>
     </row>
@@ -10509,7 +11346,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>88</v>
       </c>
     </row>
@@ -10545,7 +11385,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>93</v>
       </c>
     </row>
@@ -10581,7 +11424,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>42</v>
       </c>
     </row>
@@ -10617,7 +11463,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>43</v>
       </c>
     </row>
@@ -10653,7 +11502,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>45</v>
       </c>
     </row>
@@ -10689,7 +11541,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>50</v>
       </c>
     </row>
@@ -10725,7 +11580,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>97</v>
       </c>
     </row>
@@ -10761,7 +11619,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>56</v>
       </c>
     </row>
@@ -10797,7 +11658,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>77</v>
       </c>
     </row>
@@ -10833,7 +11697,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>90</v>
       </c>
     </row>
@@ -10869,7 +11736,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>32</v>
       </c>
     </row>
@@ -10905,7 +11775,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>35</v>
       </c>
     </row>
@@ -10941,7 +11814,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>38</v>
       </c>
     </row>
@@ -10977,7 +11853,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>44</v>
       </c>
     </row>
@@ -11013,7 +11892,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>51</v>
       </c>
     </row>
@@ -11049,7 +11931,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
         <v>53</v>
       </c>
     </row>
@@ -11085,7 +11970,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
         <v>72</v>
       </c>
     </row>
@@ -11121,7 +12009,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
         <v>79</v>
       </c>
     </row>
@@ -11157,7 +12048,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>85</v>
       </c>
     </row>
@@ -11193,7 +12087,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>87</v>
       </c>
     </row>
@@ -11229,7 +12126,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>89</v>
       </c>
     </row>
@@ -11265,7 +12165,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>98</v>
       </c>
     </row>
@@ -11301,7 +12204,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>58</v>
       </c>
     </row>
@@ -11337,7 +12243,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>59</v>
       </c>
     </row>
@@ -11373,7 +12282,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
         <v>62</v>
       </c>
     </row>
@@ -11409,7 +12321,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>63</v>
       </c>
     </row>
@@ -11445,7 +12360,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
         <v>64</v>
       </c>
     </row>
@@ -11481,7 +12399,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>65</v>
       </c>
     </row>
@@ -11517,7 +12438,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>68</v>
       </c>
     </row>
@@ -11553,7 +12477,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>70</v>
       </c>
     </row>
@@ -11589,7 +12516,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>73</v>
       </c>
     </row>
@@ -11625,7 +12555,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>74</v>
       </c>
     </row>
@@ -11640,7 +12573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11691,6 +12624,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>usd_linked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>overall_rank</t>
         </is>
       </c>
@@ -11727,7 +12665,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11763,7 +12704,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11799,7 +12743,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>13</v>
       </c>
     </row>
@@ -11835,7 +12782,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>22</v>
       </c>
     </row>
@@ -11871,7 +12821,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -11907,7 +12860,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>27</v>
       </c>
     </row>
@@ -11943,7 +12899,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>28</v>
       </c>
     </row>
@@ -11979,7 +12938,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>32</v>
       </c>
     </row>
@@ -12015,7 +12977,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>38</v>
       </c>
     </row>
@@ -12051,7 +13016,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>39</v>
       </c>
     </row>
@@ -12087,7 +13055,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>40</v>
       </c>
     </row>
@@ -12123,7 +13094,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>55</v>
       </c>
     </row>
@@ -12159,7 +13133,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>65</v>
       </c>
     </row>
@@ -12195,7 +13172,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>92</v>
       </c>
     </row>
@@ -12231,7 +13211,10 @@
           <t>Forex Major</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>93</v>
       </c>
     </row>
@@ -12267,7 +13250,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12303,7 +13289,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12339,7 +13328,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12375,7 +13367,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -12411,7 +13406,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12447,7 +13445,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12483,7 +13484,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>8</v>
       </c>
     </row>
@@ -12519,7 +13523,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
         <v>9</v>
       </c>
     </row>
@@ -12555,7 +13562,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>11</v>
       </c>
     </row>
@@ -12591,7 +13601,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
         <v>12</v>
       </c>
     </row>
@@ -12627,7 +13640,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
         <v>14</v>
       </c>
     </row>
@@ -12663,7 +13679,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>15</v>
       </c>
     </row>
@@ -12699,7 +13718,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>16</v>
       </c>
     </row>
@@ -12735,7 +13757,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>17</v>
       </c>
     </row>
@@ -12771,7 +13796,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>18</v>
       </c>
     </row>
@@ -12807,7 +13835,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>19</v>
       </c>
     </row>
@@ -12843,7 +13874,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>20</v>
       </c>
     </row>
@@ -12879,7 +13913,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>21</v>
       </c>
     </row>
@@ -12915,7 +13952,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>23</v>
       </c>
     </row>
@@ -12951,7 +13991,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>24</v>
       </c>
     </row>
@@ -12987,7 +14030,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>26</v>
       </c>
     </row>
@@ -13023,7 +14069,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
         <v>29</v>
       </c>
     </row>
@@ -13059,7 +14108,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
         <v>30</v>
       </c>
     </row>
@@ -13095,7 +14147,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
         <v>34</v>
       </c>
     </row>
@@ -13131,7 +14186,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>35</v>
       </c>
     </row>
@@ -13167,7 +14225,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>48</v>
       </c>
     </row>
@@ -13203,7 +14264,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>49</v>
       </c>
     </row>
@@ -13239,7 +14303,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>57</v>
       </c>
     </row>
@@ -13275,7 +14342,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>58</v>
       </c>
     </row>
@@ -13311,7 +14381,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>60</v>
       </c>
     </row>
@@ -13347,7 +14420,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>66</v>
       </c>
     </row>
@@ -13383,7 +14459,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>67</v>
       </c>
     </row>
@@ -13419,7 +14498,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>80</v>
       </c>
     </row>
@@ -13455,7 +14537,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>83</v>
       </c>
     </row>
@@ -13491,7 +14576,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>85</v>
       </c>
     </row>
@@ -13527,7 +14615,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>87</v>
       </c>
     </row>
@@ -13563,7 +14654,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>94</v>
       </c>
     </row>
@@ -13599,7 +14693,10 @@
           <t>Forex Minor</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>95</v>
       </c>
     </row>
@@ -13635,7 +14732,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>98</v>
       </c>
     </row>
@@ -13671,7 +14771,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>99</v>
       </c>
     </row>
@@ -13707,7 +14810,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>100</v>
       </c>
     </row>
@@ -13743,7 +14849,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>101</v>
       </c>
     </row>
@@ -13779,7 +14888,10 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>102</v>
       </c>
     </row>
@@ -13815,7 +14927,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>31</v>
       </c>
     </row>
@@ -13851,7 +14966,10 @@
           <t>Energies</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>33</v>
       </c>
     </row>
@@ -13887,7 +15005,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
         <v>61</v>
       </c>
     </row>
@@ -13923,7 +15044,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>64</v>
       </c>
     </row>
@@ -13959,7 +15083,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>68</v>
       </c>
     </row>
@@ -13995,7 +15122,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>70</v>
       </c>
     </row>
@@ -14031,7 +15161,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>71</v>
       </c>
     </row>
@@ -14067,7 +15200,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>73</v>
       </c>
     </row>
@@ -14103,7 +15239,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>74</v>
       </c>
     </row>
@@ -14139,7 +15278,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
         <v>76</v>
       </c>
     </row>
@@ -14175,7 +15317,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>77</v>
       </c>
     </row>
@@ -14211,7 +15356,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>78</v>
       </c>
     </row>
@@ -14247,7 +15395,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>86</v>
       </c>
     </row>
@@ -14283,7 +15434,10 @@
           <t>Indices</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>88</v>
       </c>
     </row>
@@ -14319,7 +15473,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>36</v>
       </c>
     </row>
@@ -14355,7 +15512,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>37</v>
       </c>
     </row>
@@ -14391,7 +15551,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>43</v>
       </c>
     </row>
@@ -14427,7 +15590,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>44</v>
       </c>
     </row>
@@ -14463,7 +15629,10 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>96</v>
       </c>
     </row>
@@ -14499,7 +15668,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>69</v>
       </c>
     </row>
@@ -14535,7 +15707,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>72</v>
       </c>
     </row>
@@ -14571,7 +15746,10 @@
           <t>Bond</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>79</v>
       </c>
     </row>
@@ -14607,7 +15785,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>41</v>
       </c>
     </row>
@@ -14643,7 +15824,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>42</v>
       </c>
     </row>
@@ -14679,7 +15863,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>52</v>
       </c>
     </row>
@@ -14715,7 +15902,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>62</v>
       </c>
     </row>
@@ -14751,7 +15941,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>75</v>
       </c>
     </row>
@@ -14787,7 +15980,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J87" t="n">
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
         <v>81</v>
       </c>
     </row>
@@ -14823,7 +16019,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
         <v>82</v>
       </c>
     </row>
@@ -14859,7 +16058,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
         <v>84</v>
       </c>
     </row>
@@ -14895,7 +16097,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>89</v>
       </c>
     </row>
@@ -14931,7 +16136,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>90</v>
       </c>
     </row>
@@ -14967,7 +16175,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>91</v>
       </c>
     </row>
@@ -15003,7 +16214,10 @@
           <t>ETF</t>
         </is>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>97</v>
       </c>
     </row>
@@ -15039,7 +16253,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>45</v>
       </c>
     </row>
@@ -15075,7 +16292,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>46</v>
       </c>
     </row>
@@ -15111,7 +16331,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
         <v>47</v>
       </c>
     </row>
@@ -15147,7 +16370,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>50</v>
       </c>
     </row>
@@ -15183,7 +16409,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
         <v>51</v>
       </c>
     </row>
@@ -15219,7 +16448,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>53</v>
       </c>
     </row>
@@ -15255,7 +16487,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>54</v>
       </c>
     </row>
@@ -15291,7 +16526,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>56</v>
       </c>
     </row>
@@ -15327,7 +16565,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>59</v>
       </c>
     </row>
@@ -15363,7 +16604,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>63</v>
       </c>
     </row>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1477</v>
+        <v>1531</v>
       </c>
       <c r="D2" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D3" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E3" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1414</v>
+        <v>1467</v>
       </c>
       <c r="D4" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E4" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F4" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -609,17 +609,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1474</v>
+        <v>1517</v>
       </c>
       <c r="D5" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E5" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F5" t="n">
         <v>45.7</v>
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1465</v>
+        <v>1528</v>
       </c>
       <c r="D6" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E6" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F6" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1477</v>
+        <v>1531</v>
       </c>
       <c r="D7" t="n">
         <v>47.6</v>
@@ -700,10 +700,10 @@
         <v>52.4</v>
       </c>
       <c r="F7" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1445</v>
+        <v>1497</v>
       </c>
       <c r="D8" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E8" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F8" t="n">
         <v>55.2</v>
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D9" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E9" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F9" t="n">
         <v>57.5</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1448</v>
+        <v>1500</v>
       </c>
       <c r="D10" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E10" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F10" t="n">
         <v>41.9</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1453</v>
+        <v>1503</v>
       </c>
       <c r="D11" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E11" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F11" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="G11" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1454</v>
+        <v>1508</v>
       </c>
       <c r="D12" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E12" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F12" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="G12" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1473</v>
+        <v>1527</v>
       </c>
       <c r="D13" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E13" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="F13" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="G13" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1458</v>
+        <v>1511</v>
       </c>
       <c r="D14" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E14" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F14" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1457</v>
+        <v>1511</v>
       </c>
       <c r="D15" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="G15" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1454</v>
+        <v>1506</v>
       </c>
       <c r="D16" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E16" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F16" t="n">
-        <v>65.5</v>
+        <v>65.3</v>
       </c>
       <c r="G16" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1077,20 +1077,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1480</v>
+        <v>1491</v>
       </c>
       <c r="D17" t="n">
-        <v>47.2</v>
+        <v>49.2</v>
       </c>
       <c r="E17" t="n">
-        <v>52.8</v>
+        <v>50.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="G17" t="n">
         <v>0.2</v>
@@ -1116,20 +1116,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1439</v>
+        <v>1534</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>47.1</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>52.9</v>
       </c>
       <c r="F18" t="n">
-        <v>49.7</v>
+        <v>50.3</v>
       </c>
       <c r="G18" t="n">
         <v>0.3</v>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1429</v>
+        <v>1482</v>
       </c>
       <c r="D19" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E19" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F19" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1346</v>
+        <v>1391</v>
       </c>
       <c r="D20" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E20" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="D21" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="E21" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="F21" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1469</v>
+        <v>1523</v>
       </c>
       <c r="D22" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="E22" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="F22" t="n">
-        <v>54.7</v>
+        <v>54.3</v>
       </c>
       <c r="G22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1462</v>
+        <v>1504</v>
       </c>
       <c r="D23" t="n">
-        <v>49.7</v>
+        <v>51.7</v>
       </c>
       <c r="E23" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="F23" t="n">
         <v>45.3</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1448</v>
+        <v>1499</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F24" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1389,17 +1389,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1450</v>
+        <v>1516</v>
       </c>
       <c r="D25" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="E25" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="F25" t="n">
         <v>45.1</v>
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1472</v>
+        <v>1534</v>
       </c>
       <c r="D26" t="n">
-        <v>50.8</v>
+        <v>48.2</v>
       </c>
       <c r="E26" t="n">
-        <v>49.2</v>
+        <v>51.8</v>
       </c>
       <c r="F26" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="G26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1467,23 +1467,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1480</v>
+        <v>1524</v>
       </c>
       <c r="D27" t="n">
-        <v>48.2</v>
+        <v>50.9</v>
       </c>
       <c r="E27" t="n">
-        <v>51.8</v>
+        <v>49.1</v>
       </c>
       <c r="F27" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="G27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1443</v>
+        <v>1497</v>
       </c>
       <c r="D28" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="F28" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1474</v>
+        <v>1527</v>
       </c>
       <c r="D29" t="n">
         <v>47.6</v>
@@ -1558,10 +1558,10 @@
         <v>52.4</v>
       </c>
       <c r="F29" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="G29" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1469</v>
+        <v>1523</v>
       </c>
       <c r="D30" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E30" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F30" t="n">
         <v>43.6</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1468</v>
+        <v>1522</v>
       </c>
       <c r="D31" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="E31" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="F31" t="n">
-        <v>57.4</v>
+        <v>57</v>
       </c>
       <c r="G31" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1461</v>
+        <v>1514</v>
       </c>
       <c r="D32" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="E32" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="F32" t="n">
         <v>57.6</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1347</v>
+        <v>1393</v>
       </c>
       <c r="D33" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F33" t="n">
         <v>42.2</v>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -1740,20 +1740,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1465</v>
+        <v>1519</v>
       </c>
       <c r="D34" t="n">
-        <v>46.8</v>
+        <v>48.3</v>
       </c>
       <c r="E34" t="n">
-        <v>53.2</v>
+        <v>51.7</v>
       </c>
       <c r="F34" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="G34" t="n">
         <v>9</v>
@@ -1779,23 +1779,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EURAUD</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1465</v>
+        <v>1519</v>
       </c>
       <c r="D35" t="n">
-        <v>48.1</v>
+        <v>46.9</v>
       </c>
       <c r="E35" t="n">
-        <v>51.9</v>
+        <v>53.1</v>
       </c>
       <c r="F35" t="n">
-        <v>40.9</v>
+        <v>59.2</v>
       </c>
       <c r="G35" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1474</v>
+        <v>1527</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="E36" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F36" t="n">
         <v>40.2</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1322</v>
+        <v>1373</v>
       </c>
       <c r="D37" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="E37" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="F37" t="n">
-        <v>60.3</v>
+        <v>59.8</v>
       </c>
       <c r="G37" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38">
@@ -1900,19 +1900,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1453</v>
+        <v>1505</v>
       </c>
       <c r="D38" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E38" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="G38" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1459</v>
+        <v>1511</v>
       </c>
       <c r="D39" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="E39" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="F39" t="n">
         <v>61</v>
@@ -1974,23 +1974,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1485</v>
+        <v>1496</v>
       </c>
       <c r="D40" t="n">
-        <v>49.8</v>
+        <v>50.9</v>
       </c>
       <c r="E40" t="n">
-        <v>50.2</v>
+        <v>49.1</v>
       </c>
       <c r="F40" t="n">
-        <v>38.2</v>
+        <v>61.6</v>
       </c>
       <c r="G40" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1445</v>
+        <v>1533</v>
       </c>
       <c r="D41" t="n">
-        <v>50.9</v>
+        <v>49.7</v>
       </c>
       <c r="E41" t="n">
-        <v>49.1</v>
+        <v>50.3</v>
       </c>
       <c r="F41" t="n">
-        <v>61.9</v>
+        <v>38.4</v>
       </c>
       <c r="G41" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>70</v>
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1479</v>
+        <v>1539</v>
       </c>
       <c r="D42" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E42" t="n">
         <v>49.9</v>
       </c>
-      <c r="E42" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F42" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="G42" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>71</v>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1469</v>
+        <v>1523</v>
       </c>
       <c r="D43" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="E43" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F43" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="G43" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1484</v>
+        <v>1538</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E44" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F44" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1480</v>
+        <v>1533</v>
       </c>
       <c r="D45" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E45" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="G45" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1483</v>
+        <v>1537</v>
       </c>
       <c r="D46" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E46" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F46" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="G46" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1471</v>
+        <v>1525</v>
       </c>
       <c r="D47" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E47" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F47" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="G47" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48">
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1342</v>
+        <v>1388</v>
       </c>
       <c r="D48" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E48" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F48" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="G48" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1452</v>
+        <v>1505</v>
       </c>
       <c r="D49" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E49" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F49" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="G49" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1457</v>
+        <v>1510</v>
       </c>
       <c r="D50" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E50" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F50" t="n">
         <v>66</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1484</v>
+        <v>1537</v>
       </c>
       <c r="D51" t="n">
         <v>48.2</v>
@@ -2416,10 +2416,10 @@
         <v>51.8</v>
       </c>
       <c r="F51" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="G51" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1457</v>
+        <v>1511</v>
       </c>
       <c r="D52" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="E52" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1484</v>
+        <v>1538</v>
       </c>
       <c r="D53" t="n">
         <v>49.8</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1372</v>
+        <v>1426</v>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F54" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="G54" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1477</v>
+        <v>1531</v>
       </c>
       <c r="D55" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E55" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F55" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="G55" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1464</v>
+        <v>1517</v>
       </c>
       <c r="D56" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="E56" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="F56" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="G56" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1479</v>
+        <v>1533</v>
       </c>
       <c r="D57" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E57" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F57" t="n">
         <v>81.90000000000001</v>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1479</v>
+        <v>1533</v>
       </c>
       <c r="D58" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="F58" t="n">
         <v>83.2</v>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1481</v>
+        <v>1534</v>
       </c>
       <c r="D59" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E59" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F59" t="n">
         <v>93.90000000000001</v>
@@ -2758,19 +2758,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1441</v>
+        <v>1528</v>
       </c>
       <c r="D60" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E60" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="G60" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1363</v>
+        <v>1411</v>
       </c>
       <c r="D61" t="n">
         <v>51.4</v>
@@ -2806,10 +2806,10 @@
         <v>48.6</v>
       </c>
       <c r="F61" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="G61" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62">
@@ -2832,23 +2832,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="D62" t="n">
-        <v>52.4</v>
+        <v>48.4</v>
       </c>
       <c r="E62" t="n">
-        <v>47.6</v>
+        <v>51.6</v>
       </c>
       <c r="F62" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
@@ -2871,23 +2871,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>924</v>
+        <v>966</v>
       </c>
       <c r="D63" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="E63" t="n">
-        <v>51</v>
+        <v>48.2</v>
       </c>
       <c r="F63" t="n">
-        <v>58.2</v>
+        <v>57.8</v>
       </c>
       <c r="G63" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1336</v>
+        <v>1387</v>
       </c>
       <c r="D64" t="n">
-        <v>49.6</v>
+        <v>49</v>
       </c>
       <c r="E64" t="n">
-        <v>50.4</v>
+        <v>51</v>
       </c>
       <c r="F64" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G64" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
@@ -2953,19 +2953,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>921</v>
+        <v>946</v>
       </c>
       <c r="D65" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="E65" t="n">
-        <v>48.9</v>
+        <v>49.5</v>
       </c>
       <c r="F65" t="n">
-        <v>59.8</v>
+        <v>59.3</v>
       </c>
       <c r="G65" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
@@ -2992,19 +2992,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>922</v>
+        <v>948</v>
       </c>
       <c r="D66" t="n">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="E66" t="n">
-        <v>51.5</v>
+        <v>52.3</v>
       </c>
       <c r="F66" t="n">
-        <v>60.1</v>
+        <v>59.7</v>
       </c>
       <c r="G66" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1459</v>
+        <v>1497</v>
       </c>
       <c r="D67" t="n">
-        <v>47.6</v>
+        <v>48.6</v>
       </c>
       <c r="E67" t="n">
-        <v>52.4</v>
+        <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
       <c r="G67" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1443</v>
+        <v>1512</v>
       </c>
       <c r="D68" t="n">
-        <v>48.8</v>
+        <v>47.4</v>
       </c>
       <c r="E68" t="n">
-        <v>51.2</v>
+        <v>52.6</v>
       </c>
       <c r="F68" t="n">
         <v>61.3</v>
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1283</v>
+        <v>1331</v>
       </c>
       <c r="D69" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E69" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F69" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
       <c r="G69" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D70" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E70" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F70" t="n">
         <v>62.2</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1442</v>
+        <v>1112</v>
       </c>
       <c r="D71" t="n">
-        <v>48.1</v>
+        <v>49.6</v>
       </c>
       <c r="E71" t="n">
-        <v>51.9</v>
+        <v>50.4</v>
       </c>
       <c r="F71" t="n">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
       <c r="G71" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1074</v>
+        <v>1528</v>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="E72" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="F72" t="n">
-        <v>63</v>
+        <v>62.8</v>
       </c>
       <c r="G72" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1290</v>
+        <v>1339</v>
       </c>
       <c r="D73" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="E73" t="n">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
       <c r="F73" t="n">
-        <v>65.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="D74" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E74" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F74" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
       <c r="G74" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="D75" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="E75" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="F75" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="G75" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="D76" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="E76" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="F76" t="n">
-        <v>53.3</v>
+        <v>53</v>
       </c>
       <c r="G76" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1086</v>
+        <v>1128</v>
       </c>
       <c r="D77" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="E77" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="F77" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="G77" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1384</v>
+        <v>1434</v>
       </c>
       <c r="D78" t="n">
         <v>48.6</v>
@@ -3469,10 +3469,10 @@
         <v>51.4</v>
       </c>
       <c r="F78" t="n">
-        <v>70.8</v>
+        <v>70.5</v>
       </c>
       <c r="G78" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="D79" t="n">
-        <v>48.5</v>
+        <v>47.9</v>
       </c>
       <c r="E79" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="F79" t="n">
-        <v>57.5</v>
+        <v>57.1</v>
       </c>
       <c r="G79" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1110</v>
+        <v>1152</v>
       </c>
       <c r="D80" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="E80" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="F80" t="n">
-        <v>60.6</v>
+        <v>60.2</v>
       </c>
       <c r="G80" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1039</v>
+        <v>1078</v>
       </c>
       <c r="D81" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="E81" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F81" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="G81" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82">
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90">
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1430</v>
+        <v>1483</v>
       </c>
       <c r="D94" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="E94" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="F94" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="G94" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1270</v>
+        <v>1321</v>
       </c>
       <c r="D95" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E95" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F95" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="G95" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1412</v>
+        <v>1534</v>
       </c>
       <c r="D96" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E96" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F96" t="n">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
       <c r="G96" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1485</v>
+        <v>1465</v>
       </c>
       <c r="D97" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="E97" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="F97" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="G97" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1480</v>
+        <v>1539</v>
       </c>
       <c r="D98" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="E98" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F98" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1485</v>
+        <v>1539</v>
       </c>
       <c r="D99" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F99" t="n">
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="G99" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1484</v>
+        <v>1538</v>
       </c>
       <c r="D100" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E100" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F100" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="G100" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1476</v>
+        <v>1530</v>
       </c>
       <c r="D101" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="E101" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="G101" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102">
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1464</v>
+        <v>1519</v>
       </c>
       <c r="D102" t="n">
-        <v>50.5</v>
+        <v>49.2</v>
       </c>
       <c r="E102" t="n">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
       <c r="F102" t="n">
-        <v>60.2</v>
+        <v>59.7</v>
       </c>
       <c r="G102" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103">
@@ -4431,23 +4431,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1465</v>
+        <v>1517</v>
       </c>
       <c r="D103" t="n">
-        <v>49.1</v>
+        <v>50.6</v>
       </c>
       <c r="E103" t="n">
-        <v>50.9</v>
+        <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G103" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37351</v>
+        <v>37403</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -4580,17 +4580,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37072</v>
+        <v>36950</v>
       </c>
       <c r="D3" t="n">
-        <v>49.8</v>
+        <v>48.9</v>
       </c>
       <c r="E3" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
       <c r="F3" t="n">
         <v>49.1</v>
@@ -4619,23 +4619,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36897</v>
+        <v>37122</v>
       </c>
       <c r="D4" t="n">
-        <v>48.9</v>
+        <v>49.9</v>
       </c>
       <c r="E4" t="n">
-        <v>51.1</v>
+        <v>50.1</v>
       </c>
       <c r="F4" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37622</v>
+        <v>37676</v>
       </c>
       <c r="D5" t="n">
         <v>51</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37674</v>
+        <v>37728</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37538</v>
+        <v>37592</v>
       </c>
       <c r="D7" t="n">
         <v>50.6</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37687</v>
+        <v>37741</v>
       </c>
       <c r="D8" t="n">
         <v>51.3</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37083</v>
+        <v>37135</v>
       </c>
       <c r="D9" t="n">
         <v>49.5</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37515</v>
+        <v>37567</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37573</v>
+        <v>37627</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37597</v>
+        <v>37651</v>
       </c>
       <c r="D12" t="n">
         <v>51.1</v>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37404</v>
+        <v>37458</v>
       </c>
       <c r="D13" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E13" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F13" t="n">
         <v>40.6</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37355</v>
+        <v>37408</v>
       </c>
       <c r="D14" t="n">
         <v>49.9</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37482</v>
+        <v>37536</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5061,10 +5061,10 @@
         <v>50.5</v>
       </c>
       <c r="F15" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37499</v>
+        <v>37551</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37625</v>
+        <v>37679</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8305</v>
+        <v>8320</v>
       </c>
       <c r="D18" t="n">
         <v>51</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37297</v>
+        <v>37351</v>
       </c>
       <c r="D19" t="n">
         <v>49.9</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36838</v>
+        <v>36890</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37459</v>
+        <v>37513</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34519</v>
+        <v>34564</v>
       </c>
       <c r="D22" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E22" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F22" t="n">
         <v>47.6</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37624</v>
+        <v>37676</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -5399,17 +5399,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37391</v>
+        <v>37417</v>
       </c>
       <c r="D24" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
       <c r="E24" t="n">
-        <v>51.1</v>
+        <v>50.2</v>
       </c>
       <c r="F24" t="n">
         <v>53.8</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -5438,23 +5438,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37363</v>
+        <v>37445</v>
       </c>
       <c r="D25" t="n">
-        <v>49.8</v>
+        <v>48.9</v>
       </c>
       <c r="E25" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
       <c r="F25" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="G25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37635</v>
+        <v>37688</v>
       </c>
       <c r="D26" t="n">
         <v>49.1</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37317</v>
+        <v>37370</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>36986</v>
+        <v>37037</v>
       </c>
       <c r="D28" t="n">
         <v>49.2</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37129</v>
+        <v>37182</v>
       </c>
       <c r="D29" t="n">
         <v>49.9</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37681</v>
+        <v>37735</v>
       </c>
       <c r="D30" t="n">
         <v>49.5</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37494</v>
+        <v>37548</v>
       </c>
       <c r="D31" t="n">
         <v>50.5</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37539</v>
+        <v>37593</v>
       </c>
       <c r="D32" t="n">
         <v>51</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37655</v>
+        <v>37708</v>
       </c>
       <c r="D33" t="n">
         <v>49.3</v>
@@ -5793,13 +5793,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37655</v>
+        <v>37709</v>
       </c>
       <c r="D34" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E34" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F34" t="n">
         <v>44.5</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37621</v>
+        <v>37675</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37902</v>
+        <v>37956</v>
       </c>
       <c r="D36" t="n">
         <v>48.9</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37892</v>
+        <v>37946</v>
       </c>
       <c r="D37" t="n">
         <v>49</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34978</v>
+        <v>35029</v>
       </c>
       <c r="D38" t="n">
         <v>50.2</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34632</v>
+        <v>34678</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37380</v>
+        <v>37304</v>
       </c>
       <c r="D40" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="E40" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="F40" t="n">
         <v>58.3</v>
@@ -6062,23 +6062,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37253</v>
+        <v>37432</v>
       </c>
       <c r="D41" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="E41" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F41" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="G41" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37426</v>
+        <v>37478</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37814</v>
+        <v>37868</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37868</v>
+        <v>37921</v>
       </c>
       <c r="D44" t="n">
         <v>49.1</v>
@@ -6192,10 +6192,10 @@
         <v>50.9</v>
       </c>
       <c r="F44" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37862</v>
+        <v>37916</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -6231,10 +6231,10 @@
         <v>50.7</v>
       </c>
       <c r="F45" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="G45" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37685</v>
+        <v>37739</v>
       </c>
       <c r="D46" t="n">
         <v>49.5</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37636</v>
+        <v>37690</v>
       </c>
       <c r="D47" t="n">
         <v>49.4</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37810</v>
+        <v>37863</v>
       </c>
       <c r="D48" t="n">
         <v>49.8</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34466</v>
+        <v>34512</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37296</v>
+        <v>37350</v>
       </c>
       <c r="D50" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E50" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F50" t="n">
         <v>61.5</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37338</v>
+        <v>37391</v>
       </c>
       <c r="D51" t="n">
         <v>49.9</v>
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37295</v>
+        <v>37348</v>
       </c>
       <c r="D52" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E52" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F52" t="n">
         <v>37.9</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37759</v>
+        <v>37813</v>
       </c>
       <c r="D53" t="n">
         <v>49</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35805</v>
+        <v>35859</v>
       </c>
       <c r="D54" t="n">
         <v>48.8</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37513</v>
+        <v>37567</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37224</v>
+        <v>37277</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37576</v>
+        <v>37630</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37649</v>
+        <v>37703</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37852</v>
+        <v>37905</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36182</v>
+        <v>36269</v>
       </c>
       <c r="D60" t="n">
         <v>50.3</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34690</v>
+        <v>34738</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36678</v>
+        <v>36732</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23187</v>
+        <v>23213</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23613</v>
+        <v>23638</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,13 +7002,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23562</v>
+        <v>23588</v>
       </c>
       <c r="D65" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E65" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
         <v>55.9</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37558</v>
+        <v>37612</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -7080,13 +7080,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20930</v>
+        <v>20956</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="E67" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="F67" t="n">
         <v>56</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37066</v>
+        <v>37119</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30158</v>
+        <v>30206</v>
       </c>
       <c r="D69" t="n">
         <v>50.9</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35427</v>
+        <v>35478</v>
       </c>
       <c r="D70" t="n">
         <v>50.4</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36696</v>
+        <v>36782</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32800</v>
+        <v>32849</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25730</v>
+        <v>25768</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14099</v>
+        <v>14114</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13904</v>
+        <v>13922</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7401,10 +7401,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="G75" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -7431,19 +7431,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14960</v>
+        <v>14976</v>
       </c>
       <c r="D76" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E76" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F76" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="G76" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26304</v>
+        <v>26346</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35102</v>
+        <v>35152</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28339</v>
+        <v>28381</v>
       </c>
       <c r="D79" t="n">
         <v>49.4</v>
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15568</v>
+        <v>15589</v>
       </c>
       <c r="D80" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E80" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F80" t="n">
         <v>55.9</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27203</v>
+        <v>27242</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37102</v>
+        <v>37155</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37694</v>
+        <v>37748</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35352</v>
+        <v>35403</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -8220,10 +8220,10 @@
         <v>51.2</v>
       </c>
       <c r="F96" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G96" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -8237,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37037</v>
+        <v>37090</v>
       </c>
       <c r="D97" t="n">
         <v>49.2</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37811</v>
+        <v>37865</v>
       </c>
       <c r="D98" t="n">
         <v>50.3</v>
@@ -8324,23 +8324,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37208</v>
+        <v>37662</v>
       </c>
       <c r="D99" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
@@ -8363,17 +8363,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37608</v>
+        <v>37262</v>
       </c>
       <c r="D100" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E100" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F100" t="n">
         <v>54.3</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37473</v>
+        <v>37526</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37888</v>
+        <v>37942</v>
       </c>
       <c r="D102" t="n">
         <v>50</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>37908</v>
+        <v>37962</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1458</v>
+        <v>1511</v>
       </c>
       <c r="D2" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E2" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F2" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1473</v>
+        <v>1527</v>
       </c>
       <c r="D3" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="E3" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="F3" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1454</v>
+        <v>1508</v>
       </c>
       <c r="D4" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E4" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F4" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1453</v>
+        <v>1503</v>
       </c>
       <c r="D5" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E5" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F5" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,13 +8750,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1448</v>
+        <v>1500</v>
       </c>
       <c r="D6" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E6" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F6" t="n">
         <v>41.9</v>
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D7" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F7" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1465</v>
+        <v>1517</v>
       </c>
       <c r="D8" t="n">
         <v>49.2</v>
@@ -8867,19 +8867,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1414</v>
+        <v>1467</v>
       </c>
       <c r="D9" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E9" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F9" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,19 +8906,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E10" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1477</v>
+        <v>1531</v>
       </c>
       <c r="D11" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1477</v>
+        <v>1531</v>
       </c>
       <c r="D12" t="n">
         <v>47.6</v>
@@ -8993,10 +8993,10 @@
         <v>52.4</v>
       </c>
       <c r="F12" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1445</v>
+        <v>1497</v>
       </c>
       <c r="D13" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E13" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F13" t="n">
         <v>55.2</v>
@@ -9062,13 +9062,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D14" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E14" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F14" t="n">
         <v>57.5</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1457</v>
+        <v>1511</v>
       </c>
       <c r="D15" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="G15" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1454</v>
+        <v>1506</v>
       </c>
       <c r="D16" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E16" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F16" t="n">
-        <v>65.5</v>
+        <v>65.3</v>
       </c>
       <c r="G16" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1372</v>
+        <v>1426</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F17" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1484</v>
+        <v>1538</v>
       </c>
       <c r="D18" t="n">
         <v>49.8</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1484</v>
+        <v>1537</v>
       </c>
       <c r="D19" t="n">
         <v>48.2</v>
@@ -9266,10 +9266,10 @@
         <v>51.8</v>
       </c>
       <c r="F19" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="G19" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1452</v>
+        <v>1505</v>
       </c>
       <c r="D20" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E20" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F20" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1342</v>
+        <v>1388</v>
       </c>
       <c r="D21" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1471</v>
+        <v>1525</v>
       </c>
       <c r="D22" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E22" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9400,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -9413,19 +9413,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1483</v>
+        <v>1537</v>
       </c>
       <c r="D23" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E23" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F23" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9448,23 +9448,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1484</v>
+        <v>1533</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>49.6</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>50.4</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="G24" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>10</v>
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1480</v>
+        <v>1538</v>
       </c>
       <c r="D25" t="n">
-        <v>49.8</v>
+        <v>51.2</v>
       </c>
       <c r="E25" t="n">
-        <v>50.2</v>
+        <v>48.8</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>11</v>
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1469</v>
+        <v>1523</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="E26" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F26" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="G26" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9565,23 +9565,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1479</v>
+        <v>1539</v>
       </c>
       <c r="D27" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E27" t="n">
         <v>49.9</v>
       </c>
-      <c r="E27" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F27" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="G27" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>13</v>
@@ -9604,23 +9604,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1485</v>
+        <v>1533</v>
       </c>
       <c r="D28" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E28" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F28" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>14</v>
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1474</v>
+        <v>1527</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="E29" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F29" t="n">
         <v>40.2</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1465</v>
+        <v>1519</v>
       </c>
       <c r="D30" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="E30" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="F30" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,13 +9725,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1347</v>
+        <v>1393</v>
       </c>
       <c r="D31" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F31" t="n">
         <v>42.2</v>
@@ -9760,17 +9760,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1474</v>
+        <v>1523</v>
       </c>
       <c r="D32" t="n">
-        <v>47.6</v>
+        <v>49.1</v>
       </c>
       <c r="E32" t="n">
-        <v>52.4</v>
+        <v>50.9</v>
       </c>
       <c r="F32" t="n">
         <v>43.6</v>
@@ -9790,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -9799,23 +9799,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1469</v>
+        <v>1527</v>
       </c>
       <c r="D33" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
       <c r="E33" t="n">
-        <v>51.2</v>
+        <v>52.4</v>
       </c>
       <c r="F33" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="G33" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1472</v>
+        <v>1524</v>
       </c>
       <c r="D34" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E34" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F34" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="G34" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1480</v>
+        <v>1534</v>
       </c>
       <c r="D35" t="n">
         <v>48.2</v>
@@ -9890,10 +9890,10 @@
         <v>51.8</v>
       </c>
       <c r="F35" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="G35" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9916,17 +9916,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1450</v>
+        <v>1516</v>
       </c>
       <c r="D36" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="E36" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="F36" t="n">
         <v>45.1</v>
@@ -9955,17 +9955,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1462</v>
+        <v>1504</v>
       </c>
       <c r="D37" t="n">
-        <v>49.7</v>
+        <v>51.7</v>
       </c>
       <c r="E37" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="F37" t="n">
         <v>45.3</v>
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1346</v>
+        <v>1391</v>
       </c>
       <c r="D38" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E38" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F38" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="G38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1439</v>
+        <v>1491</v>
       </c>
       <c r="D39" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="E39" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="F39" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10063,7 +10063,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -10076,19 +10076,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1480</v>
+        <v>1534</v>
       </c>
       <c r="D40" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="E40" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="F40" t="n">
-        <v>49.8</v>
+        <v>50.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10102,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -10115,19 +10115,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1429</v>
+        <v>1482</v>
       </c>
       <c r="D41" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E41" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F41" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="D42" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="E42" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="F42" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="G42" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10180,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -10193,19 +10193,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1469</v>
+        <v>1523</v>
       </c>
       <c r="D43" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="E43" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="F43" t="n">
-        <v>54.7</v>
+        <v>54.3</v>
       </c>
       <c r="G43" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10232,19 +10232,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1448</v>
+        <v>1499</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E44" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F44" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="G44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1443</v>
+        <v>1497</v>
       </c>
       <c r="D45" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="F45" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="G45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46">
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1468</v>
+        <v>1522</v>
       </c>
       <c r="D46" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="E46" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="F46" t="n">
-        <v>57.4</v>
+        <v>57</v>
       </c>
       <c r="G46" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10349,13 +10349,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1461</v>
+        <v>1514</v>
       </c>
       <c r="D47" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="E47" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="F47" t="n">
         <v>57.6</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48">
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1465</v>
+        <v>1519</v>
       </c>
       <c r="D48" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="E48" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="F48" t="n">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49">
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1322</v>
+        <v>1373</v>
       </c>
       <c r="D49" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="E49" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="F49" t="n">
-        <v>60.3</v>
+        <v>59.8</v>
       </c>
       <c r="G49" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50">
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1453</v>
+        <v>1505</v>
       </c>
       <c r="D50" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E50" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F50" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="G50" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51">
@@ -10505,13 +10505,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1459</v>
+        <v>1511</v>
       </c>
       <c r="D51" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="E51" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="F51" t="n">
         <v>61</v>
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1445</v>
+        <v>1496</v>
       </c>
       <c r="D52" t="n">
         <v>50.9</v>
@@ -10553,10 +10553,10 @@
         <v>49.1</v>
       </c>
       <c r="F52" t="n">
-        <v>61.9</v>
+        <v>61.6</v>
       </c>
       <c r="G52" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1457</v>
+        <v>1510</v>
       </c>
       <c r="D53" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E53" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F53" t="n">
         <v>66</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1457</v>
+        <v>1511</v>
       </c>
       <c r="D54" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="E54" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="G54" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1477</v>
+        <v>1531</v>
       </c>
       <c r="D55" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E55" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F55" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="G55" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,19 +10700,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1464</v>
+        <v>1517</v>
       </c>
       <c r="D56" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="E56" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="F56" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="G56" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1479</v>
+        <v>1533</v>
       </c>
       <c r="D57" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E57" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F57" t="n">
         <v>81.90000000000001</v>
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1479</v>
+        <v>1533</v>
       </c>
       <c r="D58" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="F58" t="n">
         <v>83.2</v>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1481</v>
+        <v>1534</v>
       </c>
       <c r="D59" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E59" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F59" t="n">
         <v>93.90000000000001</v>
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1363</v>
+        <v>1411</v>
       </c>
       <c r="D60" t="n">
         <v>51.4</v>
@@ -10865,10 +10865,10 @@
         <v>48.6</v>
       </c>
       <c r="F60" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="G60" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10895,19 +10895,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1441</v>
+        <v>1528</v>
       </c>
       <c r="D61" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E61" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="G61" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -10930,23 +10930,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="D62" t="n">
-        <v>52.4</v>
+        <v>48.4</v>
       </c>
       <c r="E62" t="n">
-        <v>47.6</v>
+        <v>51.6</v>
       </c>
       <c r="F62" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
@@ -10969,23 +10969,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>924</v>
+        <v>966</v>
       </c>
       <c r="D63" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="E63" t="n">
-        <v>51</v>
+        <v>48.2</v>
       </c>
       <c r="F63" t="n">
-        <v>58.2</v>
+        <v>57.8</v>
       </c>
       <c r="G63" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
@@ -11012,19 +11012,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1336</v>
+        <v>1387</v>
       </c>
       <c r="D64" t="n">
-        <v>49.6</v>
+        <v>49</v>
       </c>
       <c r="E64" t="n">
-        <v>50.4</v>
+        <v>51</v>
       </c>
       <c r="F64" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G64" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
@@ -11051,19 +11051,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>921</v>
+        <v>946</v>
       </c>
       <c r="D65" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="E65" t="n">
-        <v>48.9</v>
+        <v>49.5</v>
       </c>
       <c r="F65" t="n">
-        <v>59.8</v>
+        <v>59.3</v>
       </c>
       <c r="G65" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>922</v>
+        <v>948</v>
       </c>
       <c r="D66" t="n">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="E66" t="n">
-        <v>51.5</v>
+        <v>52.3</v>
       </c>
       <c r="F66" t="n">
-        <v>60.1</v>
+        <v>59.7</v>
       </c>
       <c r="G66" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11125,23 +11125,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1459</v>
+        <v>1497</v>
       </c>
       <c r="D67" t="n">
-        <v>47.6</v>
+        <v>48.6</v>
       </c>
       <c r="E67" t="n">
-        <v>52.4</v>
+        <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
       <c r="G67" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68">
@@ -11164,17 +11164,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1443</v>
+        <v>1512</v>
       </c>
       <c r="D68" t="n">
-        <v>48.8</v>
+        <v>47.4</v>
       </c>
       <c r="E68" t="n">
-        <v>51.2</v>
+        <v>52.6</v>
       </c>
       <c r="F68" t="n">
         <v>61.3</v>
@@ -11207,19 +11207,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1283</v>
+        <v>1331</v>
       </c>
       <c r="D69" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E69" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F69" t="n">
-        <v>61.6</v>
+        <v>61.4</v>
       </c>
       <c r="G69" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11246,13 +11246,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1474</v>
+        <v>1528</v>
       </c>
       <c r="D70" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E70" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F70" t="n">
         <v>62.2</v>
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1442</v>
+        <v>1112</v>
       </c>
       <c r="D71" t="n">
-        <v>48.1</v>
+        <v>49.6</v>
       </c>
       <c r="E71" t="n">
-        <v>51.9</v>
+        <v>50.4</v>
       </c>
       <c r="F71" t="n">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
       <c r="G71" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11320,23 +11320,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1074</v>
+        <v>1528</v>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="E72" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="F72" t="n">
-        <v>63</v>
+        <v>62.8</v>
       </c>
       <c r="G72" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1290</v>
+        <v>1339</v>
       </c>
       <c r="D73" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="E73" t="n">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
       <c r="F73" t="n">
-        <v>65.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="D74" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E74" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F74" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
       <c r="G74" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75">
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="D75" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="E75" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="F75" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="G75" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="D76" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="E76" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="F76" t="n">
-        <v>53.3</v>
+        <v>53</v>
       </c>
       <c r="G76" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77">
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1086</v>
+        <v>1128</v>
       </c>
       <c r="D77" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="E77" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="F77" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="G77" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1384</v>
+        <v>1434</v>
       </c>
       <c r="D78" t="n">
         <v>48.6</v>
@@ -11567,10 +11567,10 @@
         <v>51.4</v>
       </c>
       <c r="F78" t="n">
-        <v>70.8</v>
+        <v>70.5</v>
       </c>
       <c r="G78" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="D79" t="n">
-        <v>48.5</v>
+        <v>47.9</v>
       </c>
       <c r="E79" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="F79" t="n">
-        <v>57.5</v>
+        <v>57.1</v>
       </c>
       <c r="G79" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1110</v>
+        <v>1152</v>
       </c>
       <c r="D80" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="E80" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="F80" t="n">
-        <v>60.6</v>
+        <v>60.2</v>
       </c>
       <c r="G80" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1039</v>
+        <v>1078</v>
       </c>
       <c r="D81" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="E81" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F81" t="n">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="G81" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85">
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86">
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87">
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
@@ -12182,19 +12182,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1430</v>
+        <v>1483</v>
       </c>
       <c r="D94" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="E94" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="F94" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="G94" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12221,19 +12221,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1270</v>
+        <v>1321</v>
       </c>
       <c r="D95" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E95" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F95" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="G95" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1412</v>
+        <v>1534</v>
       </c>
       <c r="D96" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E96" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F96" t="n">
-        <v>58.3</v>
+        <v>58.1</v>
       </c>
       <c r="G96" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1485</v>
+        <v>1465</v>
       </c>
       <c r="D97" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="E97" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="F97" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="G97" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1480</v>
+        <v>1539</v>
       </c>
       <c r="D98" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="E98" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F98" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12377,19 +12377,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1485</v>
+        <v>1539</v>
       </c>
       <c r="D99" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F99" t="n">
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="G99" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12416,19 +12416,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1484</v>
+        <v>1538</v>
       </c>
       <c r="D100" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E100" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F100" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="G100" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12455,19 +12455,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1476</v>
+        <v>1530</v>
       </c>
       <c r="D101" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="E101" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="G101" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12490,23 +12490,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1464</v>
+        <v>1519</v>
       </c>
       <c r="D102" t="n">
-        <v>50.5</v>
+        <v>49.2</v>
       </c>
       <c r="E102" t="n">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
       <c r="F102" t="n">
-        <v>60.2</v>
+        <v>59.7</v>
       </c>
       <c r="G102" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103">
@@ -12529,23 +12529,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1465</v>
+        <v>1517</v>
       </c>
       <c r="D103" t="n">
-        <v>49.1</v>
+        <v>50.6</v>
       </c>
       <c r="E103" t="n">
-        <v>50.9</v>
+        <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G103" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37355</v>
+        <v>37408</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -12682,13 +12682,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37404</v>
+        <v>37458</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E3" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F3" t="n">
         <v>40.6</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37597</v>
+        <v>37651</v>
       </c>
       <c r="D4" t="n">
         <v>51.1</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37083</v>
+        <v>37135</v>
       </c>
       <c r="D5" t="n">
         <v>49.5</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37538</v>
+        <v>37592</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37072</v>
+        <v>37122</v>
       </c>
       <c r="D7" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E7" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F7" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36897</v>
+        <v>36950</v>
       </c>
       <c r="D8" t="n">
         <v>48.9</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37351</v>
+        <v>37403</v>
       </c>
       <c r="D9" t="n">
         <v>49.9</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37622</v>
+        <v>37676</v>
       </c>
       <c r="D10" t="n">
         <v>51</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37674</v>
+        <v>37728</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37687</v>
+        <v>37741</v>
       </c>
       <c r="D12" t="n">
         <v>51.3</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37515</v>
+        <v>37567</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37573</v>
+        <v>37627</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37482</v>
+        <v>37536</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13159,10 +13159,10 @@
         <v>50.5</v>
       </c>
       <c r="F15" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37499</v>
+        <v>37551</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35805</v>
+        <v>35859</v>
       </c>
       <c r="D17" t="n">
         <v>48.8</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37759</v>
+        <v>37813</v>
       </c>
       <c r="D18" t="n">
         <v>49</v>
@@ -13306,13 +13306,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37295</v>
+        <v>37348</v>
       </c>
       <c r="D19" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E19" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F19" t="n">
         <v>37.9</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34466</v>
+        <v>34512</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37810</v>
+        <v>37863</v>
       </c>
       <c r="D21" t="n">
         <v>49.8</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37636</v>
+        <v>37690</v>
       </c>
       <c r="D22" t="n">
         <v>49.4</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37685</v>
+        <v>37739</v>
       </c>
       <c r="D23" t="n">
         <v>49.5</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37862</v>
+        <v>37916</v>
       </c>
       <c r="D24" t="n">
         <v>49.3</v>
@@ -13510,10 +13510,10 @@
         <v>50.7</v>
       </c>
       <c r="F24" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="G24" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -13536,23 +13536,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37814</v>
+        <v>37921</v>
       </c>
       <c r="D25" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="E25" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="F25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G25" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -13575,17 +13575,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>37868</v>
       </c>
       <c r="D26" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="E26" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="F26" t="n">
         <v>40.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34632</v>
+        <v>34678</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37892</v>
+        <v>37946</v>
       </c>
       <c r="D28" t="n">
         <v>49</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37902</v>
+        <v>37956</v>
       </c>
       <c r="D29" t="n">
         <v>48.9</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37621</v>
+        <v>37675</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,13 +13774,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37655</v>
+        <v>37709</v>
       </c>
       <c r="D31" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E31" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F31" t="n">
         <v>44.5</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37655</v>
+        <v>37708</v>
       </c>
       <c r="D32" t="n">
         <v>49.3</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37681</v>
+        <v>37735</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37635</v>
+        <v>37688</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37624</v>
+        <v>37676</v>
       </c>
       <c r="D35" t="n">
         <v>49.6</v>
@@ -13969,13 +13969,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34519</v>
+        <v>34564</v>
       </c>
       <c r="D36" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E36" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F36" t="n">
         <v>47.6</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37459</v>
+        <v>37513</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36838</v>
+        <v>36890</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37625</v>
+        <v>37679</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8305</v>
+        <v>8320</v>
       </c>
       <c r="D40" t="n">
         <v>51</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37297</v>
+        <v>37351</v>
       </c>
       <c r="D41" t="n">
         <v>49.9</v>
@@ -14199,17 +14199,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37391</v>
+        <v>37417</v>
       </c>
       <c r="D42" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
       <c r="E42" t="n">
-        <v>51.1</v>
+        <v>50.2</v>
       </c>
       <c r="F42" t="n">
         <v>53.8</v>
@@ -14229,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43">
@@ -14238,23 +14238,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37363</v>
+        <v>37445</v>
       </c>
       <c r="D43" t="n">
-        <v>49.8</v>
+        <v>48.9</v>
       </c>
       <c r="E43" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
       <c r="F43" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="G43" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37317</v>
+        <v>37370</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>36986</v>
+        <v>37037</v>
       </c>
       <c r="D45" t="n">
         <v>49.2</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37129</v>
+        <v>37182</v>
       </c>
       <c r="D46" t="n">
         <v>49.9</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37494</v>
+        <v>37548</v>
       </c>
       <c r="D47" t="n">
         <v>50.5</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37539</v>
+        <v>37593</v>
       </c>
       <c r="D48" t="n">
         <v>51</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34978</v>
+        <v>35029</v>
       </c>
       <c r="D49" t="n">
         <v>50.2</v>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37380</v>
+        <v>37304</v>
       </c>
       <c r="D50" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="E50" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="F50" t="n">
         <v>58.3</v>
@@ -14550,23 +14550,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37253</v>
+        <v>37432</v>
       </c>
       <c r="D51" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="E51" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F51" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="G51" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -14580,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37426</v>
+        <v>37478</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37296</v>
+        <v>37350</v>
       </c>
       <c r="D53" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F53" t="n">
         <v>61.5</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37338</v>
+        <v>37391</v>
       </c>
       <c r="D54" t="n">
         <v>49.9</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37513</v>
+        <v>37567</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37224</v>
+        <v>37277</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37576</v>
+        <v>37630</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37649</v>
+        <v>37703</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37852</v>
+        <v>37905</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34690</v>
+        <v>34738</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36182</v>
+        <v>36269</v>
       </c>
       <c r="D61" t="n">
         <v>50.3</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36678</v>
+        <v>36732</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23187</v>
+        <v>23213</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23613</v>
+        <v>23638</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,13 +15100,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23562</v>
+        <v>23588</v>
       </c>
       <c r="D65" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E65" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
         <v>55.9</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37558</v>
+        <v>37612</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -15178,13 +15178,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20930</v>
+        <v>20956</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="E67" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="F67" t="n">
         <v>56</v>
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37066</v>
+        <v>37119</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30158</v>
+        <v>30206</v>
       </c>
       <c r="D69" t="n">
         <v>50.9</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35427</v>
+        <v>35478</v>
       </c>
       <c r="D70" t="n">
         <v>50.4</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36696</v>
+        <v>36782</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32800</v>
+        <v>32849</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25730</v>
+        <v>25768</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14099</v>
+        <v>14114</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13904</v>
+        <v>13922</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15499,10 +15499,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="G75" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -15529,19 +15529,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14960</v>
+        <v>14976</v>
       </c>
       <c r="D76" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E76" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F76" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="G76" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26304</v>
+        <v>26346</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35102</v>
+        <v>35152</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28339</v>
+        <v>28381</v>
       </c>
       <c r="D79" t="n">
         <v>49.4</v>
@@ -15685,13 +15685,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15568</v>
+        <v>15589</v>
       </c>
       <c r="D80" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E80" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F80" t="n">
         <v>55.9</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27203</v>
+        <v>27242</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -16062,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90">
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37102</v>
+        <v>37155</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37694</v>
+        <v>37748</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35352</v>
+        <v>35403</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -16318,10 +16318,10 @@
         <v>51.2</v>
       </c>
       <c r="F96" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G96" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -16335,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97">
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37037</v>
+        <v>37090</v>
       </c>
       <c r="D97" t="n">
         <v>49.2</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37811</v>
+        <v>37865</v>
       </c>
       <c r="D98" t="n">
         <v>50.3</v>
@@ -16422,23 +16422,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37208</v>
+        <v>37662</v>
       </c>
       <c r="D99" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -16461,17 +16461,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37608</v>
+        <v>37262</v>
       </c>
       <c r="D100" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E100" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F100" t="n">
         <v>54.3</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37473</v>
+        <v>37526</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37888</v>
+        <v>37942</v>
       </c>
       <c r="D102" t="n">
         <v>50</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>37908</v>
+        <v>37962</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1531</v>
+        <v>1574</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="F2" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1528</v>
+        <v>1570</v>
       </c>
       <c r="D3" t="n">
         <v>48.8</v>
@@ -544,10 +544,10 @@
         <v>51.2</v>
       </c>
       <c r="F3" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1467</v>
+        <v>1510</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -583,10 +583,10 @@
         <v>48.8</v>
       </c>
       <c r="F4" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1517</v>
+        <v>1574</v>
       </c>
       <c r="D5" t="n">
-        <v>49.2</v>
+        <v>47.5</v>
       </c>
       <c r="E5" t="n">
-        <v>50.8</v>
+        <v>52.5</v>
       </c>
       <c r="F5" t="n">
-        <v>45.7</v>
+        <v>54.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -648,17 +648,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1528</v>
+        <v>1560</v>
       </c>
       <c r="D6" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E6" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F6" t="n">
         <v>45.5</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -687,20 +687,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1531</v>
+        <v>1570</v>
       </c>
       <c r="D7" t="n">
-        <v>47.6</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>52.4</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>54.6</v>
+        <v>45.4</v>
       </c>
       <c r="G7" t="n">
         <v>4.6</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1497</v>
+        <v>1540</v>
       </c>
       <c r="D8" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E8" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F8" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1528</v>
+        <v>1571</v>
       </c>
       <c r="D9" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="E9" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="F9" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1500</v>
+        <v>1541</v>
       </c>
       <c r="D10" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1503</v>
+        <v>1543</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="E11" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="F11" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="G11" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1508</v>
+        <v>1549</v>
       </c>
       <c r="D12" t="n">
-        <v>49.2</v>
+        <v>49.6</v>
       </c>
       <c r="E12" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="F12" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="G12" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1527</v>
+        <v>1570</v>
       </c>
       <c r="D13" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E13" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F13" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G13" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1511</v>
+        <v>1554</v>
       </c>
       <c r="D14" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E14" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1511</v>
+        <v>1552</v>
       </c>
       <c r="D15" t="n">
         <v>50</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1506</v>
+        <v>1548</v>
       </c>
       <c r="D16" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E16" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F16" t="n">
         <v>65.3</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1491</v>
+        <v>1530</v>
       </c>
       <c r="D17" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E17" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F17" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1534</v>
+        <v>1576</v>
       </c>
       <c r="D18" t="n">
         <v>47.1</v>
@@ -1129,10 +1129,10 @@
         <v>52.9</v>
       </c>
       <c r="F18" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1482</v>
+        <v>1525</v>
       </c>
       <c r="D19" t="n">
         <v>49.7</v>
@@ -1168,10 +1168,10 @@
         <v>50.3</v>
       </c>
       <c r="F19" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1391</v>
+        <v>1426</v>
       </c>
       <c r="D20" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E20" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F20" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="D21" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="E21" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="F21" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1523</v>
+        <v>1566</v>
       </c>
       <c r="D22" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="E22" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="F22" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1315,19 +1315,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1504</v>
+        <v>1547</v>
       </c>
       <c r="D23" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="E23" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="F23" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1499</v>
+        <v>1541</v>
       </c>
       <c r="D24" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E24" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F24" t="n">
-        <v>54.7</v>
+        <v>54.4</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1516</v>
+        <v>1558</v>
       </c>
       <c r="D25" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E25" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F25" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="G25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1534</v>
+        <v>1567</v>
       </c>
       <c r="D26" t="n">
-        <v>48.2</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1467,20 +1467,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1524</v>
+        <v>1539</v>
       </c>
       <c r="D27" t="n">
-        <v>50.9</v>
+        <v>45.9</v>
       </c>
       <c r="E27" t="n">
-        <v>49.1</v>
+        <v>54.1</v>
       </c>
       <c r="F27" t="n">
-        <v>44.3</v>
+        <v>55.7</v>
       </c>
       <c r="G27" t="n">
         <v>5.7</v>
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1497</v>
+        <v>1577</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>48.1</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>51.9</v>
       </c>
       <c r="F28" t="n">
-        <v>55.8</v>
+        <v>44.3</v>
       </c>
       <c r="G28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1527</v>
+        <v>1570</v>
       </c>
       <c r="D29" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="E29" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="F29" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="G29" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1523</v>
+        <v>1565</v>
       </c>
       <c r="D30" t="n">
         <v>49.1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1522</v>
+        <v>1565</v>
       </c>
       <c r="D31" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E31" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>56.6</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1514</v>
+        <v>1557</v>
       </c>
       <c r="D32" t="n">
         <v>47.8</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1393</v>
+        <v>1428</v>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="E33" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F33" t="n">
-        <v>42.2</v>
+        <v>41.8</v>
       </c>
       <c r="G33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1519</v>
+        <v>1560</v>
       </c>
       <c r="D34" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E34" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F34" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1519</v>
+        <v>1561</v>
       </c>
       <c r="D35" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E35" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="F35" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="G35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36">
@@ -1818,23 +1818,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1527</v>
+        <v>1415</v>
       </c>
       <c r="D36" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="E36" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="F36" t="n">
-        <v>40.2</v>
+        <v>59.6</v>
       </c>
       <c r="G36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1373</v>
+        <v>1570</v>
       </c>
       <c r="D37" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="E37" t="n">
-        <v>51.4</v>
+        <v>51.8</v>
       </c>
       <c r="F37" t="n">
-        <v>59.8</v>
+        <v>40.3</v>
       </c>
       <c r="G37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1505</v>
+        <v>1548</v>
       </c>
       <c r="D38" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="E38" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="F38" t="n">
         <v>60.1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1511</v>
+        <v>1553</v>
       </c>
       <c r="D39" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E39" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="F39" t="n">
-        <v>61</v>
+        <v>60.8</v>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
@@ -1974,23 +1974,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1496</v>
+        <v>1576</v>
       </c>
       <c r="D40" t="n">
-        <v>50.9</v>
+        <v>49.7</v>
       </c>
       <c r="E40" t="n">
-        <v>49.1</v>
+        <v>50.3</v>
       </c>
       <c r="F40" t="n">
-        <v>61.6</v>
+        <v>38.5</v>
       </c>
       <c r="G40" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="D41" t="n">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
       <c r="E41" t="n">
-        <v>50.3</v>
+        <v>49.2</v>
       </c>
       <c r="F41" t="n">
-        <v>38.4</v>
+        <v>61.8</v>
       </c>
       <c r="G41" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1539</v>
+        <v>1582</v>
       </c>
       <c r="D42" t="n">
         <v>50.1</v>
@@ -2065,10 +2065,10 @@
         <v>49.9</v>
       </c>
       <c r="F42" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="G42" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1523</v>
+        <v>1566</v>
       </c>
       <c r="D43" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E43" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F43" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="G43" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1538</v>
+        <v>1581</v>
       </c>
       <c r="D44" t="n">
         <v>51.2</v>
@@ -2143,10 +2143,10 @@
         <v>48.8</v>
       </c>
       <c r="F44" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="G44" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D45" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E45" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F45" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="G45" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1537</v>
+        <v>1580</v>
       </c>
       <c r="D46" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="E46" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="F46" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="G46" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1525</v>
+        <v>1568</v>
       </c>
       <c r="D47" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E47" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F47" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="G47" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1388</v>
+        <v>1422</v>
       </c>
       <c r="D48" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F48" t="n">
         <v>35.2</v>
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1505</v>
+        <v>1544</v>
       </c>
       <c r="D49" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="E49" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50">
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1510</v>
+        <v>1580</v>
       </c>
       <c r="D50" t="n">
-        <v>49.7</v>
+        <v>48.1</v>
       </c>
       <c r="E50" t="n">
-        <v>50.3</v>
+        <v>51.9</v>
       </c>
       <c r="F50" t="n">
-        <v>66</v>
+        <v>33.9</v>
       </c>
       <c r="G50" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>91</v>
@@ -2403,20 +2403,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1537</v>
+        <v>1552</v>
       </c>
       <c r="D51" t="n">
-        <v>48.2</v>
+        <v>49.7</v>
       </c>
       <c r="E51" t="n">
-        <v>51.8</v>
+        <v>50.3</v>
       </c>
       <c r="F51" t="n">
-        <v>33.8</v>
+        <v>66.2</v>
       </c>
       <c r="G51" t="n">
         <v>16.2</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="J51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>92</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1511</v>
+        <v>1553</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E52" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F52" t="n">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="G52" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1538</v>
+        <v>1581</v>
       </c>
       <c r="D53" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E53" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F53" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="G53" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1426</v>
+        <v>1465</v>
       </c>
       <c r="D54" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="G54" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1531</v>
+        <v>1573</v>
       </c>
       <c r="D55" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E55" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F55" t="n">
-        <v>70.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1517</v>
+        <v>1560</v>
       </c>
       <c r="D56" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E56" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="F56" t="n">
         <v>75.3</v>
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D57" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E57" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F57" t="n">
         <v>81.90000000000001</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D58" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E58" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F58" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1534</v>
+        <v>1577</v>
       </c>
       <c r="D59" t="n">
         <v>49.1</v>
@@ -2728,10 +2728,10 @@
         <v>50.9</v>
       </c>
       <c r="F59" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="G59" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1528</v>
+        <v>1450</v>
       </c>
       <c r="D60" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E60" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F60" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="G60" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1411</v>
+        <v>1613</v>
       </c>
       <c r="D61" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="E61" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="F61" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="G61" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="D62" t="n">
         <v>48.4</v>
@@ -2845,10 +2845,10 @@
         <v>51.6</v>
       </c>
       <c r="F62" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="G62" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>966</v>
+        <v>996</v>
       </c>
       <c r="D63" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="E63" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="F63" t="n">
-        <v>57.8</v>
+        <v>58.1</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1387</v>
+        <v>1429</v>
       </c>
       <c r="D64" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E64" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="F64" t="n">
         <v>59.1</v>
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>946</v>
+        <v>977</v>
       </c>
       <c r="D65" t="n">
-        <v>50.5</v>
+        <v>47.4</v>
       </c>
       <c r="E65" t="n">
-        <v>49.5</v>
+        <v>52.6</v>
       </c>
       <c r="F65" t="n">
-        <v>59.3</v>
+        <v>59.5</v>
       </c>
       <c r="G65" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>948</v>
+        <v>976</v>
       </c>
       <c r="D66" t="n">
-        <v>47.7</v>
+        <v>50.3</v>
       </c>
       <c r="E66" t="n">
-        <v>52.3</v>
+        <v>49.7</v>
       </c>
       <c r="F66" t="n">
-        <v>59.7</v>
+        <v>59.5</v>
       </c>
       <c r="G66" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1497</v>
+        <v>1540</v>
       </c>
       <c r="D67" t="n">
         <v>48.6</v>
@@ -3040,10 +3040,10 @@
         <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
       <c r="G67" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1512</v>
+        <v>1363</v>
       </c>
       <c r="D68" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="E68" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G68" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1331</v>
+        <v>1554</v>
       </c>
       <c r="D69" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E69" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F69" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="G69" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70">
@@ -3148,19 +3148,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1528</v>
+        <v>1571</v>
       </c>
       <c r="D70" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="E70" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
       <c r="F70" t="n">
-        <v>62.2</v>
+        <v>61.7</v>
       </c>
       <c r="G70" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1112</v>
+        <v>1614</v>
       </c>
       <c r="D71" t="n">
-        <v>49.6</v>
+        <v>48.2</v>
       </c>
       <c r="E71" t="n">
-        <v>50.4</v>
+        <v>51.8</v>
       </c>
       <c r="F71" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G71" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1528</v>
+        <v>1138</v>
       </c>
       <c r="D72" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="E72" t="n">
-        <v>51.9</v>
+        <v>50.3</v>
       </c>
       <c r="F72" t="n">
-        <v>62.8</v>
+        <v>62.7</v>
       </c>
       <c r="G72" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1339</v>
+        <v>1372</v>
       </c>
       <c r="D73" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="E73" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="F73" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G73" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D74" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E74" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F74" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="D75" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E75" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F75" t="n">
-        <v>52.9</v>
+        <v>52.4</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="D76" t="n">
-        <v>52.7</v>
+        <v>53.1</v>
       </c>
       <c r="E76" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="F76" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1128</v>
+        <v>1153</v>
       </c>
       <c r="D77" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="E77" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="F77" t="n">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="G77" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1434</v>
+        <v>1474</v>
       </c>
       <c r="D78" t="n">
         <v>48.6</v>
@@ -3469,10 +3469,10 @@
         <v>51.4</v>
       </c>
       <c r="F78" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="D79" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="E79" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="F79" t="n">
-        <v>57.1</v>
+        <v>57.6</v>
       </c>
       <c r="G79" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1152</v>
+        <v>1182</v>
       </c>
       <c r="D80" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="E80" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="F80" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1078</v>
+        <v>1113</v>
       </c>
       <c r="D81" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="E81" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="F81" t="n">
         <v>63.9</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="D82" t="n">
-        <v>49.5</v>
+        <v>48.3</v>
       </c>
       <c r="E82" t="n">
-        <v>50.5</v>
+        <v>51.7</v>
       </c>
       <c r="F82" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3655,19 +3655,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="D83" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="E83" t="n">
-        <v>53.3</v>
+        <v>53</v>
       </c>
       <c r="F83" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="D84" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="E84" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="F84" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="G84" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="D85" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E85" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F85" t="n">
-        <v>53.1</v>
+        <v>53.7</v>
       </c>
       <c r="G85" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="D86" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E86" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="F86" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="G86" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="D87" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="E87" t="n">
-        <v>51.2</v>
+        <v>51.8</v>
       </c>
       <c r="F87" t="n">
-        <v>56.2</v>
+        <v>56.7</v>
       </c>
       <c r="G87" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -3846,23 +3846,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="D88" t="n">
-        <v>47.8</v>
+        <v>51.2</v>
       </c>
       <c r="E88" t="n">
-        <v>52.2</v>
+        <v>48.8</v>
       </c>
       <c r="F88" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="G88" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89">
@@ -3885,23 +3885,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D89" t="n">
-        <v>51.8</v>
+        <v>47</v>
       </c>
       <c r="E89" t="n">
-        <v>48.2</v>
+        <v>53</v>
       </c>
       <c r="F89" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="G89" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90">
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="D90" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E90" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F90" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="G90" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="D91" t="n">
-        <v>49.3</v>
+        <v>52.7</v>
       </c>
       <c r="E91" t="n">
-        <v>50.7</v>
+        <v>47.3</v>
       </c>
       <c r="F91" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="G91" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92">
@@ -4002,23 +4002,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="D92" t="n">
-        <v>52.6</v>
+        <v>49.1</v>
       </c>
       <c r="E92" t="n">
-        <v>47.4</v>
+        <v>50.9</v>
       </c>
       <c r="F92" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="G92" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="D93" t="n">
-        <v>49.7</v>
+        <v>48.8</v>
       </c>
       <c r="E93" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
       <c r="F93" t="n">
-        <v>73.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4084,13 +4084,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1483</v>
+        <v>1523</v>
       </c>
       <c r="D94" t="n">
-        <v>51.7</v>
+        <v>51.5</v>
       </c>
       <c r="E94" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="F94" t="n">
         <v>57.5</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95">
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1321</v>
+        <v>1360</v>
       </c>
       <c r="D95" t="n">
-        <v>51.6</v>
+        <v>51.2</v>
       </c>
       <c r="E95" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="F95" t="n">
-        <v>58</v>
+        <v>57.6</v>
       </c>
       <c r="G95" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96">
@@ -4162,19 +4162,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1534</v>
+        <v>1577</v>
       </c>
       <c r="D96" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E96" t="n">
         <v>49.9</v>
       </c>
-      <c r="E96" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F96" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="G96" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1465</v>
+        <v>1582</v>
       </c>
       <c r="D97" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E97" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F97" t="n">
         <v>58.2</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1539</v>
+        <v>1507</v>
       </c>
       <c r="D98" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E98" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F98" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G98" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99">
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1539</v>
+        <v>1582</v>
       </c>
       <c r="D99" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E99" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F99" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="G99" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100">
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1538</v>
+        <v>1581</v>
       </c>
       <c r="D100" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E100" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G100" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101">
@@ -4353,23 +4353,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1530</v>
+        <v>1561</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="F101" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102">
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1519</v>
+        <v>1573</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="E102" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="F102" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="G102" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103">
@@ -4435,33 +4435,33 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E103" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="F103" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>60</v>
-      </c>
-      <c r="G103" t="n">
-        <v>10</v>
-      </c>
-      <c r="H103" t="b">
-        <v>1</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="J103" t="b">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37403</v>
+        <v>37446</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36950</v>
+        <v>36993</v>
       </c>
       <c r="D3" t="n">
         <v>48.9</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37122</v>
+        <v>37162</v>
       </c>
       <c r="D4" t="n">
         <v>49.9</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37676</v>
+        <v>37718</v>
       </c>
       <c r="D5" t="n">
         <v>51</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37728</v>
+        <v>37771</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37592</v>
+        <v>37634</v>
       </c>
       <c r="D7" t="n">
         <v>50.6</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37741</v>
+        <v>37784</v>
       </c>
       <c r="D8" t="n">
         <v>51.3</v>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37135</v>
+        <v>37176</v>
       </c>
       <c r="D9" t="n">
         <v>49.5</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37567</v>
+        <v>37610</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4866,10 +4866,10 @@
         <v>50.5</v>
       </c>
       <c r="F10" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37627</v>
+        <v>37670</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37651</v>
+        <v>37694</v>
       </c>
       <c r="D12" t="n">
         <v>51.1</v>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37458</v>
+        <v>37499</v>
       </c>
       <c r="D13" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E13" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F13" t="n">
         <v>40.6</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37408</v>
+        <v>37451</v>
       </c>
       <c r="D14" t="n">
         <v>49.9</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37536</v>
+        <v>37577</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37551</v>
+        <v>37593</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37679</v>
+        <v>37721</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8320</v>
+        <v>8329</v>
       </c>
       <c r="D18" t="n">
         <v>51</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37351</v>
+        <v>37394</v>
       </c>
       <c r="D19" t="n">
         <v>49.9</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36890</v>
+        <v>36929</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37513</v>
+        <v>37555</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34564</v>
+        <v>34599</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37676</v>
+        <v>37719</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37417</v>
+        <v>37459</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37445</v>
+        <v>37487</v>
       </c>
       <c r="D25" t="n">
         <v>48.9</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37688</v>
+        <v>37731</v>
       </c>
       <c r="D26" t="n">
         <v>49.1</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37370</v>
+        <v>37413</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,13 +5559,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37037</v>
+        <v>37079</v>
       </c>
       <c r="D28" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E28" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F28" t="n">
         <v>54.5</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37182</v>
+        <v>37225</v>
       </c>
       <c r="D29" t="n">
         <v>49.9</v>
@@ -5607,10 +5607,10 @@
         <v>50.1</v>
       </c>
       <c r="F29" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="G29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37735</v>
+        <v>37777</v>
       </c>
       <c r="D30" t="n">
         <v>49.5</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37548</v>
+        <v>37591</v>
       </c>
       <c r="D31" t="n">
         <v>50.5</v>
@@ -5685,10 +5685,10 @@
         <v>49.5</v>
       </c>
       <c r="F31" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="G31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -5715,13 +5715,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37593</v>
+        <v>37636</v>
       </c>
       <c r="D32" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E32" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F32" t="n">
         <v>55.4</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37708</v>
+        <v>37751</v>
       </c>
       <c r="D33" t="n">
         <v>49.3</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37709</v>
+        <v>37752</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37675</v>
+        <v>37716</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37956</v>
+        <v>37999</v>
       </c>
       <c r="D36" t="n">
         <v>48.9</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37946</v>
+        <v>37989</v>
       </c>
       <c r="D37" t="n">
         <v>49</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35029</v>
+        <v>35071</v>
       </c>
       <c r="D38" t="n">
         <v>50.2</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34678</v>
+        <v>34713</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37304</v>
+        <v>37475</v>
       </c>
       <c r="D40" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="E40" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F40" t="n">
         <v>58.3</v>
@@ -6062,23 +6062,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37432</v>
+        <v>37346</v>
       </c>
       <c r="D41" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="E41" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="F41" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G41" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37478</v>
+        <v>37520</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37868</v>
+        <v>37911</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37921</v>
+        <v>37964</v>
       </c>
       <c r="D44" t="n">
         <v>49.1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37916</v>
+        <v>37959</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37739</v>
+        <v>37782</v>
       </c>
       <c r="D46" t="n">
         <v>49.5</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37690</v>
+        <v>37733</v>
       </c>
       <c r="D47" t="n">
         <v>49.4</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37863</v>
+        <v>37906</v>
       </c>
       <c r="D48" t="n">
         <v>49.8</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34512</v>
+        <v>34546</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37350</v>
+        <v>37392</v>
       </c>
       <c r="D50" t="n">
         <v>49.6</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37391</v>
+        <v>37433</v>
       </c>
       <c r="D51" t="n">
         <v>49.9</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37348</v>
+        <v>37387</v>
       </c>
       <c r="D52" t="n">
         <v>50.2</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37813</v>
+        <v>37856</v>
       </c>
       <c r="D53" t="n">
         <v>49</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35859</v>
+        <v>35898</v>
       </c>
       <c r="D54" t="n">
         <v>48.8</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37567</v>
+        <v>37609</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6621,10 +6621,10 @@
         <v>49.9</v>
       </c>
       <c r="F55" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37277</v>
+        <v>37320</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37630</v>
+        <v>37673</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37703</v>
+        <v>37746</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37905</v>
+        <v>37948</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36269</v>
+        <v>36354</v>
       </c>
       <c r="D60" t="n">
         <v>50.3</v>
@@ -6816,10 +6816,10 @@
         <v>49.7</v>
       </c>
       <c r="F60" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34738</v>
+        <v>34777</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36732</v>
+        <v>36775</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6894,10 +6894,10 @@
         <v>49.2</v>
       </c>
       <c r="F62" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G62" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23213</v>
+        <v>23243</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23638</v>
+        <v>23668</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23588</v>
+        <v>23617</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37612</v>
+        <v>37655</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20956</v>
+        <v>20986</v>
       </c>
       <c r="D67" t="n">
         <v>51.8</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37119</v>
+        <v>37161</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30206</v>
+        <v>30238</v>
       </c>
       <c r="D69" t="n">
         <v>50.9</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35478</v>
+        <v>35520</v>
       </c>
       <c r="D70" t="n">
         <v>50.4</v>
@@ -7236,13 +7236,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36782</v>
+        <v>36868</v>
       </c>
       <c r="D71" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E71" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
         <v>56.7</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32849</v>
+        <v>32882</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25768</v>
+        <v>25794</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14114</v>
+        <v>14134</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13922</v>
+        <v>13940</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7401,10 +7401,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14976</v>
+        <v>14995</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -7440,10 +7440,10 @@
         <v>49.4</v>
       </c>
       <c r="F76" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -7470,13 +7470,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26346</v>
+        <v>26371</v>
       </c>
       <c r="D77" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E77" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F77" t="n">
         <v>53.1</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35152</v>
+        <v>35192</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28381</v>
+        <v>28411</v>
       </c>
       <c r="D79" t="n">
         <v>49.4</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15589</v>
+        <v>15607</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27242</v>
+        <v>27277</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10323</v>
+        <v>10349</v>
       </c>
       <c r="D82" t="n">
         <v>51.6</v>
@@ -7674,10 +7674,10 @@
         <v>48.4</v>
       </c>
       <c r="F82" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10326</v>
+        <v>10351</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,13 +7743,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10107</v>
+        <v>10131</v>
       </c>
       <c r="D84" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E84" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F84" t="n">
         <v>54</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10621</v>
+        <v>10647</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7808,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86">
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10109</v>
+        <v>10134</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10577</v>
+        <v>10600</v>
       </c>
       <c r="D87" t="n">
         <v>50.9</v>
@@ -7899,19 +7899,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10683</v>
+        <v>10708</v>
       </c>
       <c r="D88" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="E88" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="F88" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="G88" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10815</v>
+        <v>10841</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10819</v>
+        <v>10845</v>
       </c>
       <c r="D90" t="n">
         <v>51.6</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10747</v>
+        <v>10771</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10172</v>
+        <v>10194</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,13 +8094,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10103</v>
+        <v>10125</v>
       </c>
       <c r="D93" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="E93" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="F93" t="n">
         <v>65.40000000000001</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37155</v>
+        <v>37195</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37748</v>
+        <v>37791</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35403</v>
+        <v>35442</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -8220,10 +8220,10 @@
         <v>51.2</v>
       </c>
       <c r="F96" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="G96" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -8237,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37090</v>
+        <v>37132</v>
       </c>
       <c r="D97" t="n">
         <v>49.2</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37865</v>
+        <v>37908</v>
       </c>
       <c r="D98" t="n">
         <v>50.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37662</v>
+        <v>37704</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37262</v>
+        <v>37305</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8406,13 +8406,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37526</v>
+        <v>37567</v>
       </c>
       <c r="D101" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E101" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F101" t="n">
         <v>54.4</v>
@@ -8432,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37942</v>
+        <v>37985</v>
       </c>
       <c r="D102" t="n">
         <v>50</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>37962</v>
+        <v>38005</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1511</v>
+        <v>1554</v>
       </c>
       <c r="D2" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E2" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1527</v>
+        <v>1570</v>
       </c>
       <c r="D3" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E3" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G3" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1508</v>
+        <v>1549</v>
       </c>
       <c r="D4" t="n">
-        <v>49.2</v>
+        <v>49.6</v>
       </c>
       <c r="E4" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="F4" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="G4" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1503</v>
+        <v>1543</v>
       </c>
       <c r="D5" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="E5" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="F5" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1500</v>
+        <v>1541</v>
       </c>
       <c r="D6" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1528</v>
+        <v>1570</v>
       </c>
       <c r="D7" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1517</v>
+        <v>1560</v>
       </c>
       <c r="D8" t="n">
         <v>49.2</v>
@@ -8837,10 +8837,10 @@
         <v>50.8</v>
       </c>
       <c r="F8" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1467</v>
+        <v>1510</v>
       </c>
       <c r="D9" t="n">
         <v>51.2</v>
@@ -8876,10 +8876,10 @@
         <v>48.8</v>
       </c>
       <c r="F9" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1528</v>
+        <v>1570</v>
       </c>
       <c r="D10" t="n">
         <v>48.8</v>
@@ -8915,10 +8915,10 @@
         <v>51.2</v>
       </c>
       <c r="F10" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1531</v>
+        <v>1574</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="F11" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1531</v>
+        <v>1574</v>
       </c>
       <c r="D12" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="E12" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="F12" t="n">
-        <v>54.6</v>
+        <v>54.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1497</v>
+        <v>1540</v>
       </c>
       <c r="D13" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E13" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F13" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1528</v>
+        <v>1571</v>
       </c>
       <c r="D14" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="E14" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="F14" t="n">
-        <v>57.5</v>
+        <v>57.4</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1511</v>
+        <v>1552</v>
       </c>
       <c r="D15" t="n">
         <v>50</v>
@@ -9140,13 +9140,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1506</v>
+        <v>1548</v>
       </c>
       <c r="D16" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E16" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F16" t="n">
         <v>65.3</v>
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1426</v>
+        <v>1465</v>
       </c>
       <c r="D17" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1538</v>
+        <v>1581</v>
       </c>
       <c r="D18" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E18" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F18" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="G18" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,19 +9257,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1537</v>
+        <v>1580</v>
       </c>
       <c r="D19" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E19" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F19" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="G19" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1505</v>
+        <v>1544</v>
       </c>
       <c r="D20" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="E20" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1388</v>
+        <v>1422</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F21" t="n">
         <v>35.2</v>
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1525</v>
+        <v>1568</v>
       </c>
       <c r="D22" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E22" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F22" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="G22" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9400,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -9413,19 +9413,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1537</v>
+        <v>1580</v>
       </c>
       <c r="D23" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="E23" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9452,19 +9452,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D24" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E24" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F24" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="G24" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1538</v>
+        <v>1581</v>
       </c>
       <c r="D25" t="n">
         <v>51.2</v>
@@ -9500,10 +9500,10 @@
         <v>48.8</v>
       </c>
       <c r="F25" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1523</v>
+        <v>1566</v>
       </c>
       <c r="D26" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E26" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F26" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="G26" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1539</v>
+        <v>1582</v>
       </c>
       <c r="D27" t="n">
         <v>50.1</v>
@@ -9578,10 +9578,10 @@
         <v>49.9</v>
       </c>
       <c r="F27" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="G27" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D28" t="n">
         <v>49.7</v>
@@ -9617,10 +9617,10 @@
         <v>50.3</v>
       </c>
       <c r="F28" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="G28" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1527</v>
+        <v>1570</v>
       </c>
       <c r="D29" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="E29" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="F29" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="G29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1519</v>
+        <v>1560</v>
       </c>
       <c r="D30" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E30" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1393</v>
+        <v>1428</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="E31" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="F31" t="n">
-        <v>42.2</v>
+        <v>41.8</v>
       </c>
       <c r="G31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1523</v>
+        <v>1565</v>
       </c>
       <c r="D32" t="n">
         <v>49.1</v>
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1527</v>
+        <v>1570</v>
       </c>
       <c r="D33" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="E33" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="F33" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="G33" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9838,17 +9838,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1524</v>
+        <v>1577</v>
       </c>
       <c r="D34" t="n">
-        <v>50.9</v>
+        <v>48.1</v>
       </c>
       <c r="E34" t="n">
-        <v>49.1</v>
+        <v>51.9</v>
       </c>
       <c r="F34" t="n">
         <v>44.3</v>
@@ -9877,23 +9877,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1534</v>
+        <v>1567</v>
       </c>
       <c r="D35" t="n">
-        <v>48.2</v>
+        <v>51</v>
       </c>
       <c r="E35" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="G35" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1516</v>
+        <v>1558</v>
       </c>
       <c r="D36" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E36" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F36" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="G36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1504</v>
+        <v>1547</v>
       </c>
       <c r="D37" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="E37" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="F37" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
       <c r="G37" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1391</v>
+        <v>1426</v>
       </c>
       <c r="D38" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E38" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F38" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="G38" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1491</v>
+        <v>1530</v>
       </c>
       <c r="D39" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E39" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F39" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10063,7 +10063,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1534</v>
+        <v>1576</v>
       </c>
       <c r="D40" t="n">
         <v>47.1</v>
@@ -10085,10 +10085,10 @@
         <v>52.9</v>
       </c>
       <c r="F40" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10102,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1482</v>
+        <v>1525</v>
       </c>
       <c r="D41" t="n">
         <v>49.7</v>
@@ -10124,10 +10124,10 @@
         <v>50.3</v>
       </c>
       <c r="F41" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="G41" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="D42" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="E42" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="F42" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="G42" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10180,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
@@ -10193,19 +10193,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1523</v>
+        <v>1566</v>
       </c>
       <c r="D43" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="E43" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="F43" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="G43" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10232,19 +10232,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1499</v>
+        <v>1541</v>
       </c>
       <c r="D44" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E44" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F44" t="n">
-        <v>54.7</v>
+        <v>54.4</v>
       </c>
       <c r="G44" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1497</v>
+        <v>1539</v>
       </c>
       <c r="D45" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="E45" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="F45" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="G45" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1522</v>
+        <v>1565</v>
       </c>
       <c r="D46" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E46" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F46" t="n">
-        <v>57</v>
+        <v>56.6</v>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1514</v>
+        <v>1557</v>
       </c>
       <c r="D47" t="n">
         <v>47.8</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1519</v>
+        <v>1561</v>
       </c>
       <c r="D48" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E48" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="F48" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="G48" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1373</v>
+        <v>1415</v>
       </c>
       <c r="D49" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E49" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F49" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="G49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
@@ -10466,13 +10466,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1505</v>
+        <v>1548</v>
       </c>
       <c r="D50" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="E50" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="F50" t="n">
         <v>60.1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1511</v>
+        <v>1553</v>
       </c>
       <c r="D51" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E51" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="F51" t="n">
-        <v>61</v>
+        <v>60.8</v>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1496</v>
+        <v>1538</v>
       </c>
       <c r="D52" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E52" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F52" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="G52" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1510</v>
+        <v>1552</v>
       </c>
       <c r="D53" t="n">
         <v>49.7</v>
@@ -10592,10 +10592,10 @@
         <v>50.3</v>
       </c>
       <c r="F53" t="n">
-        <v>66</v>
+        <v>66.2</v>
       </c>
       <c r="G53" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1511</v>
+        <v>1553</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E54" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F54" t="n">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="G54" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1531</v>
+        <v>1573</v>
       </c>
       <c r="D55" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E55" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F55" t="n">
-        <v>70.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1517</v>
+        <v>1560</v>
       </c>
       <c r="D56" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E56" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="F56" t="n">
         <v>75.3</v>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D57" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E57" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F57" t="n">
         <v>81.90000000000001</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1533</v>
+        <v>1576</v>
       </c>
       <c r="D58" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E58" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F58" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1534</v>
+        <v>1577</v>
       </c>
       <c r="D59" t="n">
         <v>49.1</v>
@@ -10826,10 +10826,10 @@
         <v>50.9</v>
       </c>
       <c r="F59" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="G59" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10856,19 +10856,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1411</v>
+        <v>1450</v>
       </c>
       <c r="D60" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="E60" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="F60" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="G60" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10895,19 +10895,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1528</v>
+        <v>1613</v>
       </c>
       <c r="D61" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E61" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F61" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="G61" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="D62" t="n">
         <v>48.4</v>
@@ -10943,10 +10943,10 @@
         <v>51.6</v>
       </c>
       <c r="F62" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="G62" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>966</v>
+        <v>996</v>
       </c>
       <c r="D63" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="E63" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="F63" t="n">
-        <v>57.8</v>
+        <v>58.1</v>
       </c>
       <c r="G63" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1387</v>
+        <v>1429</v>
       </c>
       <c r="D64" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E64" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="F64" t="n">
         <v>59.1</v>
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>946</v>
+        <v>977</v>
       </c>
       <c r="D65" t="n">
-        <v>50.5</v>
+        <v>47.4</v>
       </c>
       <c r="E65" t="n">
-        <v>49.5</v>
+        <v>52.6</v>
       </c>
       <c r="F65" t="n">
-        <v>59.3</v>
+        <v>59.5</v>
       </c>
       <c r="G65" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11086,23 +11086,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>948</v>
+        <v>976</v>
       </c>
       <c r="D66" t="n">
-        <v>47.7</v>
+        <v>50.3</v>
       </c>
       <c r="E66" t="n">
-        <v>52.3</v>
+        <v>49.7</v>
       </c>
       <c r="F66" t="n">
-        <v>59.7</v>
+        <v>59.5</v>
       </c>
       <c r="G66" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1497</v>
+        <v>1540</v>
       </c>
       <c r="D67" t="n">
         <v>48.6</v>
@@ -11138,10 +11138,10 @@
         <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
       <c r="G67" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1512</v>
+        <v>1363</v>
       </c>
       <c r="D68" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="E68" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G68" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1331</v>
+        <v>1554</v>
       </c>
       <c r="D69" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E69" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F69" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="G69" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11246,19 +11246,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1528</v>
+        <v>1571</v>
       </c>
       <c r="D70" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="E70" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
       <c r="F70" t="n">
-        <v>62.2</v>
+        <v>61.7</v>
       </c>
       <c r="G70" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71">
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1112</v>
+        <v>1614</v>
       </c>
       <c r="D71" t="n">
-        <v>49.6</v>
+        <v>48.2</v>
       </c>
       <c r="E71" t="n">
-        <v>50.4</v>
+        <v>51.8</v>
       </c>
       <c r="F71" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G71" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72">
@@ -11320,23 +11320,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1528</v>
+        <v>1138</v>
       </c>
       <c r="D72" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="E72" t="n">
-        <v>51.9</v>
+        <v>50.3</v>
       </c>
       <c r="F72" t="n">
-        <v>62.8</v>
+        <v>62.7</v>
       </c>
       <c r="G72" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73">
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1339</v>
+        <v>1372</v>
       </c>
       <c r="D73" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="E73" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="F73" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G73" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D74" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E74" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F74" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="D75" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E75" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F75" t="n">
-        <v>52.9</v>
+        <v>52.4</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="D76" t="n">
-        <v>52.7</v>
+        <v>53.1</v>
       </c>
       <c r="E76" t="n">
-        <v>47.3</v>
+        <v>46.9</v>
       </c>
       <c r="F76" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1128</v>
+        <v>1153</v>
       </c>
       <c r="D77" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="E77" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="F77" t="n">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="G77" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1434</v>
+        <v>1474</v>
       </c>
       <c r="D78" t="n">
         <v>48.6</v>
@@ -11567,10 +11567,10 @@
         <v>51.4</v>
       </c>
       <c r="F78" t="n">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="D79" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="E79" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="F79" t="n">
-        <v>57.1</v>
+        <v>57.6</v>
       </c>
       <c r="G79" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1152</v>
+        <v>1182</v>
       </c>
       <c r="D80" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="E80" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="F80" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1078</v>
+        <v>1113</v>
       </c>
       <c r="D81" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="E81" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="F81" t="n">
         <v>63.9</v>
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="D82" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="E82" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="F82" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="G82" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -11753,19 +11753,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="D83" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="E83" t="n">
-        <v>53.3</v>
+        <v>53</v>
       </c>
       <c r="F83" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="D84" t="n">
-        <v>49.5</v>
+        <v>48.3</v>
       </c>
       <c r="E84" t="n">
-        <v>50.5</v>
+        <v>51.7</v>
       </c>
       <c r="F84" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="D85" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E85" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F85" t="n">
-        <v>53.1</v>
+        <v>53.7</v>
       </c>
       <c r="G85" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11870,19 +11870,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="D86" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E86" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="F86" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="G86" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87">
@@ -11909,19 +11909,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="D87" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="E87" t="n">
-        <v>51.2</v>
+        <v>51.8</v>
       </c>
       <c r="F87" t="n">
-        <v>56.2</v>
+        <v>56.7</v>
       </c>
       <c r="G87" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88">
@@ -11944,23 +11944,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="D88" t="n">
-        <v>47.8</v>
+        <v>51.2</v>
       </c>
       <c r="E88" t="n">
-        <v>52.2</v>
+        <v>48.8</v>
       </c>
       <c r="F88" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="G88" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89">
@@ -11983,23 +11983,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D89" t="n">
-        <v>51.8</v>
+        <v>47</v>
       </c>
       <c r="E89" t="n">
-        <v>48.2</v>
+        <v>53</v>
       </c>
       <c r="F89" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="G89" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90">
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="D90" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E90" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F90" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="G90" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="D91" t="n">
-        <v>49.3</v>
+        <v>52.7</v>
       </c>
       <c r="E91" t="n">
-        <v>50.7</v>
+        <v>47.3</v>
       </c>
       <c r="F91" t="n">
-        <v>62.7</v>
+        <v>62.4</v>
       </c>
       <c r="G91" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92">
@@ -12100,23 +12100,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="D92" t="n">
-        <v>52.6</v>
+        <v>49.1</v>
       </c>
       <c r="E92" t="n">
-        <v>47.4</v>
+        <v>50.9</v>
       </c>
       <c r="F92" t="n">
-        <v>63.2</v>
+        <v>62.5</v>
       </c>
       <c r="G92" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="D93" t="n">
-        <v>49.7</v>
+        <v>48.8</v>
       </c>
       <c r="E93" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
       <c r="F93" t="n">
-        <v>73.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12182,13 +12182,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1483</v>
+        <v>1523</v>
       </c>
       <c r="D94" t="n">
-        <v>51.7</v>
+        <v>51.5</v>
       </c>
       <c r="E94" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="F94" t="n">
         <v>57.5</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95">
@@ -12221,19 +12221,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1321</v>
+        <v>1360</v>
       </c>
       <c r="D95" t="n">
-        <v>51.6</v>
+        <v>51.2</v>
       </c>
       <c r="E95" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="F95" t="n">
-        <v>58</v>
+        <v>57.6</v>
       </c>
       <c r="G95" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96">
@@ -12260,19 +12260,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1534</v>
+        <v>1577</v>
       </c>
       <c r="D96" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E96" t="n">
         <v>49.9</v>
       </c>
-      <c r="E96" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F96" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="G96" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1465</v>
+        <v>1582</v>
       </c>
       <c r="D97" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E97" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F97" t="n">
         <v>58.2</v>
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1539</v>
+        <v>1507</v>
       </c>
       <c r="D98" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E98" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F98" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G98" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12377,19 +12377,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1539</v>
+        <v>1582</v>
       </c>
       <c r="D99" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E99" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F99" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="G99" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12416,19 +12416,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1538</v>
+        <v>1581</v>
       </c>
       <c r="D100" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E100" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G100" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101">
@@ -12451,23 +12451,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1530</v>
+        <v>1561</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="F101" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102">
@@ -12490,23 +12490,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1519</v>
+        <v>1573</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="E102" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="F102" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="G102" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E103" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="F103" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37408</v>
+        <v>37451</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -12682,13 +12682,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37458</v>
+        <v>37499</v>
       </c>
       <c r="D3" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E3" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F3" t="n">
         <v>40.6</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37651</v>
+        <v>37694</v>
       </c>
       <c r="D4" t="n">
         <v>51.1</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37135</v>
+        <v>37176</v>
       </c>
       <c r="D5" t="n">
         <v>49.5</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37592</v>
+        <v>37634</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37122</v>
+        <v>37162</v>
       </c>
       <c r="D7" t="n">
         <v>49.9</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36950</v>
+        <v>36993</v>
       </c>
       <c r="D8" t="n">
         <v>48.9</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37403</v>
+        <v>37446</v>
       </c>
       <c r="D9" t="n">
         <v>49.9</v>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37676</v>
+        <v>37718</v>
       </c>
       <c r="D10" t="n">
         <v>51</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37728</v>
+        <v>37771</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37741</v>
+        <v>37784</v>
       </c>
       <c r="D12" t="n">
         <v>51.3</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37567</v>
+        <v>37610</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13081,10 +13081,10 @@
         <v>50.5</v>
       </c>
       <c r="F13" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -13098,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37627</v>
+        <v>37670</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13137,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37536</v>
+        <v>37577</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37551</v>
+        <v>37593</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35859</v>
+        <v>35898</v>
       </c>
       <c r="D17" t="n">
         <v>48.8</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37813</v>
+        <v>37856</v>
       </c>
       <c r="D18" t="n">
         <v>49</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37348</v>
+        <v>37387</v>
       </c>
       <c r="D19" t="n">
         <v>50.2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34512</v>
+        <v>34546</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37863</v>
+        <v>37906</v>
       </c>
       <c r="D21" t="n">
         <v>49.8</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37690</v>
+        <v>37733</v>
       </c>
       <c r="D22" t="n">
         <v>49.4</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37739</v>
+        <v>37782</v>
       </c>
       <c r="D23" t="n">
         <v>49.5</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37916</v>
+        <v>37959</v>
       </c>
       <c r="D24" t="n">
         <v>49.3</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37921</v>
+        <v>37964</v>
       </c>
       <c r="D25" t="n">
         <v>49.1</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37868</v>
+        <v>37911</v>
       </c>
       <c r="D26" t="n">
         <v>49.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34678</v>
+        <v>34713</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37946</v>
+        <v>37989</v>
       </c>
       <c r="D28" t="n">
         <v>49</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37956</v>
+        <v>37999</v>
       </c>
       <c r="D29" t="n">
         <v>48.9</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37675</v>
+        <v>37716</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37709</v>
+        <v>37752</v>
       </c>
       <c r="D31" t="n">
         <v>49.1</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37708</v>
+        <v>37751</v>
       </c>
       <c r="D32" t="n">
         <v>49.3</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37735</v>
+        <v>37777</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37688</v>
+        <v>37731</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37676</v>
+        <v>37719</v>
       </c>
       <c r="D35" t="n">
         <v>49.6</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34564</v>
+        <v>34599</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37513</v>
+        <v>37555</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36890</v>
+        <v>36929</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37679</v>
+        <v>37721</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8320</v>
+        <v>8329</v>
       </c>
       <c r="D40" t="n">
         <v>51</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37351</v>
+        <v>37394</v>
       </c>
       <c r="D41" t="n">
         <v>49.9</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37417</v>
+        <v>37459</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14229,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37445</v>
+        <v>37487</v>
       </c>
       <c r="D43" t="n">
         <v>48.9</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37370</v>
+        <v>37413</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37037</v>
+        <v>37079</v>
       </c>
       <c r="D45" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E45" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F45" t="n">
         <v>54.5</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37182</v>
+        <v>37225</v>
       </c>
       <c r="D46" t="n">
         <v>49.9</v>
@@ -14368,10 +14368,10 @@
         <v>50.1</v>
       </c>
       <c r="F46" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="G46" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37548</v>
+        <v>37591</v>
       </c>
       <c r="D47" t="n">
         <v>50.5</v>
@@ -14407,10 +14407,10 @@
         <v>49.5</v>
       </c>
       <c r="F47" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="G47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -14424,7 +14424,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48">
@@ -14437,13 +14437,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37593</v>
+        <v>37636</v>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F48" t="n">
         <v>55.4</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35029</v>
+        <v>35071</v>
       </c>
       <c r="D49" t="n">
         <v>50.2</v>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37304</v>
+        <v>37475</v>
       </c>
       <c r="D50" t="n">
-        <v>50.3</v>
+        <v>49.3</v>
       </c>
       <c r="E50" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="F50" t="n">
         <v>58.3</v>
@@ -14550,23 +14550,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37432</v>
+        <v>37346</v>
       </c>
       <c r="D51" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="E51" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="F51" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G51" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -14580,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37478</v>
+        <v>37520</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37350</v>
+        <v>37392</v>
       </c>
       <c r="D53" t="n">
         <v>49.6</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37391</v>
+        <v>37433</v>
       </c>
       <c r="D54" t="n">
         <v>49.9</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37567</v>
+        <v>37609</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14719,10 +14719,10 @@
         <v>49.9</v>
       </c>
       <c r="F55" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37277</v>
+        <v>37320</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37630</v>
+        <v>37673</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37703</v>
+        <v>37746</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37905</v>
+        <v>37948</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34738</v>
+        <v>34777</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36269</v>
+        <v>36354</v>
       </c>
       <c r="D61" t="n">
         <v>50.3</v>
@@ -14953,10 +14953,10 @@
         <v>49.7</v>
       </c>
       <c r="F61" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36732</v>
+        <v>36775</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -14992,10 +14992,10 @@
         <v>49.2</v>
       </c>
       <c r="F62" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G62" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -15009,7 +15009,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63">
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23213</v>
+        <v>23243</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23638</v>
+        <v>23668</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23588</v>
+        <v>23617</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37612</v>
+        <v>37655</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20956</v>
+        <v>20986</v>
       </c>
       <c r="D67" t="n">
         <v>51.8</v>
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37119</v>
+        <v>37161</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30206</v>
+        <v>30238</v>
       </c>
       <c r="D69" t="n">
         <v>50.9</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35478</v>
+        <v>35520</v>
       </c>
       <c r="D70" t="n">
         <v>50.4</v>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36782</v>
+        <v>36868</v>
       </c>
       <c r="D71" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E71" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
         <v>56.7</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32849</v>
+        <v>32882</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25768</v>
+        <v>25794</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14114</v>
+        <v>14134</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13922</v>
+        <v>13940</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15499,10 +15499,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14976</v>
+        <v>14995</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -15538,10 +15538,10 @@
         <v>49.4</v>
       </c>
       <c r="F76" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -15568,13 +15568,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26346</v>
+        <v>26371</v>
       </c>
       <c r="D77" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E77" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F77" t="n">
         <v>53.1</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35152</v>
+        <v>35192</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28381</v>
+        <v>28411</v>
       </c>
       <c r="D79" t="n">
         <v>49.4</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15589</v>
+        <v>15607</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27242</v>
+        <v>27277</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10323</v>
+        <v>10349</v>
       </c>
       <c r="D82" t="n">
         <v>51.6</v>
@@ -15772,10 +15772,10 @@
         <v>48.4</v>
       </c>
       <c r="F82" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10326</v>
+        <v>10351</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,13 +15841,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10107</v>
+        <v>10131</v>
       </c>
       <c r="D84" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E84" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F84" t="n">
         <v>54</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10621</v>
+        <v>10647</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15906,7 +15906,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86">
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10109</v>
+        <v>10134</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10577</v>
+        <v>10600</v>
       </c>
       <c r="D87" t="n">
         <v>50.9</v>
@@ -15997,19 +15997,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10683</v>
+        <v>10708</v>
       </c>
       <c r="D88" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="E88" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="F88" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="G88" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10815</v>
+        <v>10841</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -16062,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90">
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10819</v>
+        <v>10845</v>
       </c>
       <c r="D90" t="n">
         <v>51.6</v>
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10747</v>
+        <v>10771</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10172</v>
+        <v>10194</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,13 +16192,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10103</v>
+        <v>10125</v>
       </c>
       <c r="D93" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="E93" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="F93" t="n">
         <v>65.40000000000001</v>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37155</v>
+        <v>37195</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37748</v>
+        <v>37791</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35403</v>
+        <v>35442</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -16318,10 +16318,10 @@
         <v>51.2</v>
       </c>
       <c r="F96" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="G96" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -16335,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37090</v>
+        <v>37132</v>
       </c>
       <c r="D97" t="n">
         <v>49.2</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37865</v>
+        <v>37908</v>
       </c>
       <c r="D98" t="n">
         <v>50.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37662</v>
+        <v>37704</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37262</v>
+        <v>37305</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16504,13 +16504,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37526</v>
+        <v>37567</v>
       </c>
       <c r="D101" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E101" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F101" t="n">
         <v>54.4</v>
@@ -16530,7 +16530,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102">
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37942</v>
+        <v>37985</v>
       </c>
       <c r="D102" t="n">
         <v>50</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>37962</v>
+        <v>38005</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -16608,7 +16608,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1574</v>
+        <v>1614</v>
       </c>
       <c r="D2" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E2" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F2" t="n">
         <v>50.3</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1570</v>
+        <v>1610</v>
       </c>
       <c r="D3" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="E3" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="F3" t="n">
         <v>47.5</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1510</v>
+        <v>1552</v>
       </c>
       <c r="D4" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1574</v>
+        <v>1614</v>
       </c>
       <c r="D5" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="E5" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="F5" t="n">
-        <v>54.2</v>
+        <v>53.8</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1560</v>
+        <v>1612</v>
       </c>
       <c r="D6" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="E6" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="F6" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -687,11 +687,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1570</v>
+        <v>1585</v>
       </c>
       <c r="D7" t="n">
         <v>49</v>
@@ -700,7 +700,7 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>45.4</v>
+        <v>54.6</v>
       </c>
       <c r="G7" t="n">
         <v>4.6</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -726,23 +726,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURCAD</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1540</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>49.1</v>
+        <v>50.1</v>
       </c>
       <c r="E8" t="n">
-        <v>50.9</v>
+        <v>49.9</v>
       </c>
       <c r="F8" t="n">
-        <v>55.5</v>
+        <v>45.4</v>
       </c>
       <c r="G8" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1571</v>
+        <v>1611</v>
       </c>
       <c r="D9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="F9" t="n">
-        <v>57.4</v>
+        <v>56.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1541</v>
+        <v>1585</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="F10" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="D11" t="n">
-        <v>50.8</v>
+        <v>51.4</v>
       </c>
       <c r="E11" t="n">
-        <v>49.2</v>
+        <v>48.6</v>
       </c>
       <c r="F11" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="G11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1549</v>
+        <v>1587</v>
       </c>
       <c r="D12" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
       <c r="E12" t="n">
-        <v>50.4</v>
+        <v>49.7</v>
       </c>
       <c r="F12" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1570</v>
+        <v>1612</v>
       </c>
       <c r="D13" t="n">
         <v>49.7</v>
@@ -934,10 +934,10 @@
         <v>50.3</v>
       </c>
       <c r="F13" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="G13" t="n">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1554</v>
+        <v>1595</v>
       </c>
       <c r="D14" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="E14" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="F14" t="n">
         <v>35.8</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1552</v>
+        <v>1592</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F15" t="n">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="G15" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1548</v>
+        <v>1589</v>
       </c>
       <c r="D16" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="E16" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="F16" t="n">
-        <v>65.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1530</v>
+        <v>1568</v>
       </c>
       <c r="D17" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="E17" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="F17" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D18" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1525</v>
+        <v>1569</v>
       </c>
       <c r="D19" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="E19" t="n">
-        <v>50.3</v>
+        <v>49.5</v>
       </c>
       <c r="F19" t="n">
         <v>50.8</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1426</v>
+        <v>1505</v>
       </c>
       <c r="D20" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E20" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F20" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="D21" t="n">
         <v>48.5</v>
@@ -1246,10 +1246,10 @@
         <v>51.5</v>
       </c>
       <c r="F21" t="n">
-        <v>52.9</v>
+        <v>51.9</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1566</v>
+        <v>1589</v>
       </c>
       <c r="D22" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="E22" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="F22" t="n">
-        <v>54.1</v>
+        <v>45.7</v>
       </c>
       <c r="G22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1311,20 +1311,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1547</v>
+        <v>1608</v>
       </c>
       <c r="D23" t="n">
-        <v>51.8</v>
+        <v>50.5</v>
       </c>
       <c r="E23" t="n">
-        <v>48.2</v>
+        <v>49.5</v>
       </c>
       <c r="F23" t="n">
-        <v>45.6</v>
+        <v>54.4</v>
       </c>
       <c r="G23" t="n">
         <v>4.4</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1541</v>
+        <v>1599</v>
       </c>
       <c r="D24" t="n">
-        <v>51.1</v>
+        <v>49.3</v>
       </c>
       <c r="E24" t="n">
-        <v>48.9</v>
+        <v>50.7</v>
       </c>
       <c r="F24" t="n">
-        <v>54.4</v>
+        <v>45.4</v>
       </c>
       <c r="G24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1558</v>
+        <v>1580</v>
       </c>
       <c r="D25" t="n">
-        <v>49.6</v>
+        <v>51.1</v>
       </c>
       <c r="E25" t="n">
-        <v>50.4</v>
+        <v>48.9</v>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>54.8</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1567</v>
+        <v>1609</v>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E26" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F26" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="G26" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1539</v>
+        <v>1581</v>
       </c>
       <c r="D27" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="E27" t="n">
-        <v>54.1</v>
+        <v>53.7</v>
       </c>
       <c r="F27" t="n">
-        <v>55.7</v>
+        <v>55.3</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1577</v>
+        <v>1618</v>
       </c>
       <c r="D28" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="E28" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F28" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="G28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1570</v>
+        <v>1611</v>
       </c>
       <c r="D29" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="E29" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="F29" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="G29" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1565</v>
+        <v>1607</v>
       </c>
       <c r="D30" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="E30" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="F30" t="n">
-        <v>43.6</v>
+        <v>56.3</v>
       </c>
       <c r="G30" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1565</v>
+        <v>1606</v>
       </c>
       <c r="D31" t="n">
-        <v>50.2</v>
+        <v>49.3</v>
       </c>
       <c r="E31" t="n">
-        <v>49.8</v>
+        <v>50.7</v>
       </c>
       <c r="F31" t="n">
-        <v>56.6</v>
+        <v>43.5</v>
       </c>
       <c r="G31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1557</v>
+        <v>1598</v>
       </c>
       <c r="D32" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="G32" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1428</v>
+        <v>1507</v>
       </c>
       <c r="D33" t="n">
-        <v>47.9</v>
+        <v>48.9</v>
       </c>
       <c r="E33" t="n">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="F33" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="G33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
@@ -1740,20 +1740,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EURAUD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1560</v>
+        <v>1456</v>
       </c>
       <c r="D34" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E34" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F34" t="n">
-        <v>41.1</v>
+        <v>58.9</v>
       </c>
       <c r="G34" t="n">
         <v>8.9</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1561</v>
+        <v>1602</v>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>46.4</v>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>53.6</v>
       </c>
       <c r="F35" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="G35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1415</v>
+        <v>1602</v>
       </c>
       <c r="D36" t="n">
         <v>48.3</v>
@@ -1831,10 +1831,10 @@
         <v>51.7</v>
       </c>
       <c r="F36" t="n">
-        <v>59.6</v>
+        <v>40.6</v>
       </c>
       <c r="G36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1570</v>
+        <v>1610</v>
       </c>
       <c r="D37" t="n">
         <v>48.2</v>
@@ -1870,10 +1870,10 @@
         <v>51.8</v>
       </c>
       <c r="F37" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="G37" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1548</v>
+        <v>1589</v>
       </c>
       <c r="D38" t="n">
         <v>49.4</v>
@@ -1909,10 +1909,10 @@
         <v>50.6</v>
       </c>
       <c r="F38" t="n">
-        <v>60.1</v>
+        <v>59.8</v>
       </c>
       <c r="G38" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1553</v>
+        <v>1594</v>
       </c>
       <c r="D39" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E39" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F39" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="G39" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D40" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E40" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F40" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="G40" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1538</v>
+        <v>1623</v>
       </c>
       <c r="D41" t="n">
-        <v>50.8</v>
+        <v>49.9</v>
       </c>
       <c r="E41" t="n">
-        <v>49.2</v>
+        <v>50.1</v>
       </c>
       <c r="F41" t="n">
-        <v>61.8</v>
+        <v>38.6</v>
       </c>
       <c r="G41" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D42" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="E42" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="F42" t="n">
-        <v>38.2</v>
+        <v>62.1</v>
       </c>
       <c r="G42" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1566</v>
+        <v>1636</v>
       </c>
       <c r="D43" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="E43" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="F43" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="G43" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1581</v>
+        <v>1622</v>
       </c>
       <c r="D44" t="n">
         <v>51.2</v>
@@ -2143,10 +2143,10 @@
         <v>48.8</v>
       </c>
       <c r="F44" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D45" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E45" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F45" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G45" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1580</v>
+        <v>1647</v>
       </c>
       <c r="D46" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E46" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="G46" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1568</v>
+        <v>1620</v>
       </c>
       <c r="D47" t="n">
-        <v>49.4</v>
+        <v>50.4</v>
       </c>
       <c r="E47" t="n">
-        <v>50.6</v>
+        <v>49.6</v>
       </c>
       <c r="F47" t="n">
-        <v>35.8</v>
+        <v>36.3</v>
       </c>
       <c r="G47" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1422</v>
+        <v>1501</v>
       </c>
       <c r="D48" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E48" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F48" t="n">
-        <v>35.2</v>
+        <v>36.2</v>
       </c>
       <c r="G48" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49">
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1544</v>
+        <v>1583</v>
       </c>
       <c r="D49" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
       <c r="E49" t="n">
-        <v>52.3</v>
+        <v>51.9</v>
       </c>
       <c r="F49" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="G49" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2368,19 +2368,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1580</v>
+        <v>1621</v>
       </c>
       <c r="D50" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="E50" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="F50" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="G50" t="n">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1552</v>
+        <v>1591</v>
       </c>
       <c r="D51" t="n">
         <v>49.7</v>
@@ -2416,10 +2416,10 @@
         <v>50.3</v>
       </c>
       <c r="F51" t="n">
-        <v>66.2</v>
+        <v>66.5</v>
       </c>
       <c r="G51" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1553</v>
+        <v>1594</v>
       </c>
       <c r="D52" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="E52" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="F52" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1581</v>
+        <v>1622</v>
       </c>
       <c r="D53" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E53" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F53" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="G53" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1465</v>
+        <v>1513</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -2533,10 +2533,10 @@
         <v>50</v>
       </c>
       <c r="F54" t="n">
-        <v>29.8</v>
+        <v>30.6</v>
       </c>
       <c r="G54" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1573</v>
+        <v>1613</v>
       </c>
       <c r="D55" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E55" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F55" t="n">
         <v>70.59999999999999</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1560</v>
+        <v>1600</v>
       </c>
       <c r="D56" t="n">
         <v>48.5</v>
@@ -2611,10 +2611,10 @@
         <v>51.5</v>
       </c>
       <c r="F56" t="n">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D57" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E57" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F57" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="G57" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D58" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E58" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F58" t="n">
         <v>83.09999999999999</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1577</v>
+        <v>1619</v>
       </c>
       <c r="D59" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="E59" t="n">
-        <v>50.9</v>
+        <v>51.3</v>
       </c>
       <c r="F59" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1450</v>
+        <v>1611</v>
       </c>
       <c r="D60" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E60" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F60" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
       <c r="G60" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1613</v>
+        <v>1526</v>
       </c>
       <c r="D61" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="E61" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="F61" t="n">
-        <v>43.2</v>
+        <v>42.3</v>
       </c>
       <c r="G61" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="D62" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="E62" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="F62" t="n">
-        <v>57.7</v>
+        <v>57</v>
       </c>
       <c r="G62" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="D63" t="n">
-        <v>51.6</v>
+        <v>52.6</v>
       </c>
       <c r="E63" t="n">
-        <v>48.4</v>
+        <v>47.4</v>
       </c>
       <c r="F63" t="n">
         <v>58.1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -2910,23 +2910,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1429</v>
+        <v>998</v>
       </c>
       <c r="D64" t="n">
-        <v>48.8</v>
+        <v>50.4</v>
       </c>
       <c r="E64" t="n">
-        <v>51.2</v>
+        <v>49.6</v>
       </c>
       <c r="F64" t="n">
-        <v>59.1</v>
+        <v>58.5</v>
       </c>
       <c r="G64" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -2953,19 +2953,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>977</v>
+        <v>997</v>
       </c>
       <c r="D65" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="E65" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="F65" t="n">
-        <v>59.5</v>
+        <v>58.6</v>
       </c>
       <c r="G65" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
@@ -2988,17 +2988,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>976</v>
+        <v>1502</v>
       </c>
       <c r="D66" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
       <c r="E66" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
       <c r="F66" t="n">
         <v>59.5</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1540</v>
+        <v>1619</v>
       </c>
       <c r="D67" t="n">
         <v>48.6</v>
@@ -3040,10 +3040,10 @@
         <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G67" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1363</v>
+        <v>1646</v>
       </c>
       <c r="D68" t="n">
-        <v>48</v>
+        <v>49.8</v>
       </c>
       <c r="E68" t="n">
-        <v>52</v>
+        <v>50.2</v>
       </c>
       <c r="F68" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
       <c r="G68" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1554</v>
+        <v>1437</v>
       </c>
       <c r="D69" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="E69" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="F69" t="n">
-        <v>61.5</v>
+        <v>62.1</v>
       </c>
       <c r="G69" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70">
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1571</v>
+        <v>1594</v>
       </c>
       <c r="D70" t="n">
-        <v>50.2</v>
+        <v>48.3</v>
       </c>
       <c r="E70" t="n">
-        <v>49.8</v>
+        <v>51.7</v>
       </c>
       <c r="F70" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="G70" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71">
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="D71" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E71" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F71" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="G71" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72">
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="D72" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="E72" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
       <c r="F72" t="n">
-        <v>62.7</v>
+        <v>63.1</v>
       </c>
       <c r="G72" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1372</v>
+        <v>1441</v>
       </c>
       <c r="D73" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="E73" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
       <c r="F73" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74">
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>580</v>
+        <v>616</v>
       </c>
       <c r="D74" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E74" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F74" t="n">
-        <v>52.1</v>
+        <v>53.1</v>
       </c>
       <c r="G74" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -3339,23 +3339,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="D75" t="n">
-        <v>49.9</v>
+        <v>52.8</v>
       </c>
       <c r="E75" t="n">
-        <v>50.1</v>
+        <v>47.2</v>
       </c>
       <c r="F75" t="n">
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
       <c r="G75" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
@@ -3378,23 +3378,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D76" t="n">
-        <v>53.1</v>
+        <v>49.8</v>
       </c>
       <c r="E76" t="n">
-        <v>46.9</v>
+        <v>50.2</v>
       </c>
       <c r="F76" t="n">
-        <v>53.3</v>
+        <v>53.8</v>
       </c>
       <c r="G76" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1153</v>
+        <v>1219</v>
       </c>
       <c r="D77" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="F77" t="n">
-        <v>55.6</v>
+        <v>55.8</v>
       </c>
       <c r="G77" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1474</v>
+        <v>1545</v>
       </c>
       <c r="D78" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E78" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F78" t="n">
-        <v>70.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>571</v>
+        <v>615</v>
       </c>
       <c r="D79" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="E79" t="n">
-        <v>51.8</v>
+        <v>52.5</v>
       </c>
       <c r="F79" t="n">
-        <v>57.6</v>
+        <v>58.7</v>
       </c>
       <c r="G79" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80">
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1182</v>
+        <v>1251</v>
       </c>
       <c r="D80" t="n">
-        <v>47.4</v>
+        <v>47</v>
       </c>
       <c r="E80" t="n">
-        <v>52.6</v>
+        <v>53</v>
       </c>
       <c r="F80" t="n">
         <v>60.4</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1113</v>
+        <v>1201</v>
       </c>
       <c r="D81" t="n">
-        <v>47.5</v>
+        <v>47</v>
       </c>
       <c r="E81" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="F81" t="n">
-        <v>63.9</v>
+        <v>63.5</v>
       </c>
       <c r="G81" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="D82" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E82" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F82" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="D83" t="n">
-        <v>47</v>
+        <v>50.3</v>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>49.7</v>
       </c>
       <c r="F83" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -3690,23 +3690,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D84" t="n">
-        <v>51.1</v>
+        <v>47</v>
       </c>
       <c r="E84" t="n">
+        <v>53</v>
+      </c>
+      <c r="F84" t="n">
         <v>48.9</v>
       </c>
-      <c r="F84" t="n">
-        <v>48</v>
-      </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="D85" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="E85" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="F85" t="n">
-        <v>53.7</v>
+        <v>54.1</v>
       </c>
       <c r="G85" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D86" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E86" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F86" t="n">
-        <v>55.7</v>
+        <v>54.7</v>
       </c>
       <c r="G86" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
@@ -3814,16 +3814,16 @@
         <v>423</v>
       </c>
       <c r="D87" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E87" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F87" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D88" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
       <c r="E88" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="F88" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="G88" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
@@ -3892,16 +3892,16 @@
         <v>415</v>
       </c>
       <c r="D89" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="F89" t="n">
-        <v>60.7</v>
+        <v>61.7</v>
       </c>
       <c r="G89" t="n">
-        <v>10.7</v>
+        <v>11.7</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90">
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="D90" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="E90" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F90" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="G90" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D91" t="n">
-        <v>52.7</v>
+        <v>49.4</v>
       </c>
       <c r="E91" t="n">
-        <v>47.3</v>
+        <v>50.6</v>
       </c>
       <c r="F91" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="G91" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92">
@@ -4002,23 +4002,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="D92" t="n">
-        <v>49.1</v>
+        <v>51.1</v>
       </c>
       <c r="E92" t="n">
-        <v>50.9</v>
+        <v>48.9</v>
       </c>
       <c r="F92" t="n">
-        <v>62.5</v>
+        <v>62.8</v>
       </c>
       <c r="G92" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93">
@@ -4048,16 +4048,16 @@
         <v>406</v>
       </c>
       <c r="D93" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="E93" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="F93" t="n">
-        <v>72.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4080,23 +4080,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1523</v>
+        <v>1620</v>
       </c>
       <c r="D94" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="E94" t="n">
-        <v>48.5</v>
+        <v>50.7</v>
       </c>
       <c r="F94" t="n">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="G94" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95">
@@ -4119,23 +4119,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1360</v>
+        <v>1568</v>
       </c>
       <c r="D95" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E95" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F95" t="n">
-        <v>57.6</v>
+        <v>58.1</v>
       </c>
       <c r="G95" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1577</v>
+        <v>1417</v>
       </c>
       <c r="D96" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
       <c r="E96" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="G96" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1582</v>
+        <v>1623</v>
       </c>
       <c r="D97" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="E97" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="F97" t="n">
-        <v>58.2</v>
+        <v>58.9</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1507</v>
+        <v>1622</v>
       </c>
       <c r="D98" t="n">
-        <v>49.3</v>
+        <v>49.9</v>
       </c>
       <c r="E98" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="F98" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="G98" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99">
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1582</v>
+        <v>1623</v>
       </c>
       <c r="D99" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E99" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F99" t="n">
-        <v>58.5</v>
+        <v>59.2</v>
       </c>
       <c r="G99" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100">
@@ -4314,11 +4314,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1581</v>
+        <v>1558</v>
       </c>
       <c r="D100" t="n">
         <v>50</v>
@@ -4327,10 +4327,10 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>59.1</v>
+        <v>59.3</v>
       </c>
       <c r="G100" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1561</v>
+        <v>1602</v>
       </c>
       <c r="D101" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E101" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="G101" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102">
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1573</v>
+        <v>1615</v>
       </c>
       <c r="D102" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E102" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>59.8</v>
+        <v>60.3</v>
       </c>
       <c r="G102" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1558</v>
+        <v>1602</v>
       </c>
       <c r="D103" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="E103" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="G103" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37446</v>
+        <v>37573</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -4584,13 +4584,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36993</v>
+        <v>37118</v>
       </c>
       <c r="D3" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>49.1</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37162</v>
+        <v>37288</v>
       </c>
       <c r="D4" t="n">
         <v>49.9</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37718</v>
+        <v>37846</v>
       </c>
       <c r="D5" t="n">
         <v>51</v>
@@ -4671,10 +4671,10 @@
         <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37771</v>
+        <v>37899</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37634</v>
+        <v>37763</v>
       </c>
       <c r="D7" t="n">
         <v>50.6</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37784</v>
+        <v>37912</v>
       </c>
       <c r="D8" t="n">
         <v>51.3</v>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37176</v>
+        <v>37303</v>
       </c>
       <c r="D9" t="n">
         <v>49.5</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37610</v>
+        <v>37739</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4866,10 +4866,10 @@
         <v>50.5</v>
       </c>
       <c r="F10" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37670</v>
+        <v>37797</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37694</v>
+        <v>37823</v>
       </c>
       <c r="D12" t="n">
         <v>51.1</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37499</v>
+        <v>37624</v>
       </c>
       <c r="D13" t="n">
         <v>50.2</v>
@@ -5013,13 +5013,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37451</v>
+        <v>37578</v>
       </c>
       <c r="D14" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>40.2</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37577</v>
+        <v>37703</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,13 +5091,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37593</v>
+        <v>37719</v>
       </c>
       <c r="D16" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E16" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F16" t="n">
         <v>60.9</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37721</v>
+        <v>37850</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8329</v>
+        <v>8371</v>
       </c>
       <c r="D18" t="n">
         <v>51</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37394</v>
+        <v>37519</v>
       </c>
       <c r="D19" t="n">
         <v>49.9</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36929</v>
+        <v>37052</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37555</v>
+        <v>37684</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34599</v>
+        <v>34758</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37719</v>
+        <v>37848</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37459</v>
+        <v>37587</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5412,10 +5412,10 @@
         <v>50.2</v>
       </c>
       <c r="F24" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37487</v>
+        <v>37615</v>
       </c>
       <c r="D25" t="n">
         <v>48.9</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37731</v>
+        <v>37859</v>
       </c>
       <c r="D26" t="n">
         <v>49.1</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37413</v>
+        <v>37541</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37079</v>
+        <v>37204</v>
       </c>
       <c r="D28" t="n">
         <v>49.3</v>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37225</v>
+        <v>37351</v>
       </c>
       <c r="D29" t="n">
         <v>49.9</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37777</v>
+        <v>37905</v>
       </c>
       <c r="D30" t="n">
         <v>49.5</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37591</v>
+        <v>37719</v>
       </c>
       <c r="D31" t="n">
         <v>50.5</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37636</v>
+        <v>37765</v>
       </c>
       <c r="D32" t="n">
         <v>50.9</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37751</v>
+        <v>37879</v>
       </c>
       <c r="D33" t="n">
         <v>49.3</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37752</v>
+        <v>37881</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -5819,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37716</v>
+        <v>37844</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37999</v>
+        <v>38128</v>
       </c>
       <c r="D36" t="n">
         <v>48.9</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37989</v>
+        <v>38118</v>
       </c>
       <c r="D37" t="n">
         <v>49</v>
@@ -5919,10 +5919,10 @@
         <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35071</v>
+        <v>35190</v>
       </c>
       <c r="D38" t="n">
         <v>50.2</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34713</v>
+        <v>34872</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37475</v>
+        <v>37603</v>
       </c>
       <c r="D40" t="n">
         <v>49.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37346</v>
+        <v>37472</v>
       </c>
       <c r="D41" t="n">
         <v>50.3</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37520</v>
+        <v>37647</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37911</v>
+        <v>38040</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37964</v>
+        <v>38093</v>
       </c>
       <c r="D44" t="n">
         <v>49.1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37959</v>
+        <v>38087</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37782</v>
+        <v>37939</v>
       </c>
       <c r="D46" t="n">
         <v>49.5</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37733</v>
+        <v>37898</v>
       </c>
       <c r="D47" t="n">
         <v>49.4</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37906</v>
+        <v>38035</v>
       </c>
       <c r="D48" t="n">
         <v>49.8</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34546</v>
+        <v>34704</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37392</v>
+        <v>37518</v>
       </c>
       <c r="D50" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E50" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F50" t="n">
         <v>61.5</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37433</v>
+        <v>37559</v>
       </c>
       <c r="D51" t="n">
         <v>49.9</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37387</v>
+        <v>37511</v>
       </c>
       <c r="D52" t="n">
         <v>50.2</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37856</v>
+        <v>37985</v>
       </c>
       <c r="D53" t="n">
         <v>49</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35898</v>
+        <v>36021</v>
       </c>
       <c r="D54" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E54" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F54" t="n">
         <v>32.5</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37609</v>
+        <v>37737</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37320</v>
+        <v>37448</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,13 +6690,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37673</v>
+        <v>37802</v>
       </c>
       <c r="D57" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E57" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F57" t="n">
         <v>73.90000000000001</v>
@@ -6729,13 +6729,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37746</v>
+        <v>37875</v>
       </c>
       <c r="D58" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E58" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F58" t="n">
         <v>76.3</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37948</v>
+        <v>38077</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6777,10 +6777,10 @@
         <v>48.7</v>
       </c>
       <c r="F59" t="n">
-        <v>87.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="G59" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36354</v>
+        <v>36438</v>
       </c>
       <c r="D60" t="n">
         <v>50.3</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34777</v>
+        <v>34936</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6855,10 +6855,10 @@
         <v>49.2</v>
       </c>
       <c r="F61" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36775</v>
+        <v>36937</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23243</v>
+        <v>23320</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23668</v>
+        <v>23746</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23617</v>
+        <v>23691</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37655</v>
+        <v>37816</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -7080,19 +7080,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20986</v>
+        <v>21064</v>
       </c>
       <c r="D67" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E67" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F67" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37161</v>
+        <v>37288</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -7128,10 +7128,10 @@
         <v>49.5</v>
       </c>
       <c r="F68" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69">
@@ -7154,17 +7154,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30238</v>
+        <v>35676</v>
       </c>
       <c r="D69" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -7193,23 +7193,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35520</v>
+        <v>30386</v>
       </c>
       <c r="D70" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="E70" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="F70" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="G70" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71">
@@ -7236,13 +7236,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36868</v>
+        <v>36954</v>
       </c>
       <c r="D71" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E71" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F71" t="n">
         <v>56.7</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32882</v>
+        <v>33027</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25794</v>
+        <v>25889</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7323,10 +7323,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G73" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14134</v>
+        <v>14204</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13940</v>
+        <v>14009</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7401,10 +7401,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="G75" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14995</v>
+        <v>15065</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -7440,10 +7440,10 @@
         <v>49.4</v>
       </c>
       <c r="F76" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="G76" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26371</v>
+        <v>26507</v>
       </c>
       <c r="D77" t="n">
         <v>50</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35192</v>
+        <v>35348</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7518,10 +7518,10 @@
         <v>49.4</v>
       </c>
       <c r="F78" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G78" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -7548,19 +7548,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28411</v>
+        <v>28543</v>
       </c>
       <c r="D79" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E79" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F79" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="G79" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -7574,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80">
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15607</v>
+        <v>15685</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27277</v>
+        <v>27418</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10349</v>
+        <v>10399</v>
       </c>
       <c r="D82" t="n">
         <v>51.6</v>
@@ -7674,10 +7674,10 @@
         <v>48.4</v>
       </c>
       <c r="F82" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10351</v>
+        <v>10376</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10131</v>
+        <v>10181</v>
       </c>
       <c r="D84" t="n">
         <v>50.7</v>
@@ -7769,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10647</v>
+        <v>10672</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10134</v>
+        <v>10179</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
@@ -7860,13 +7860,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10600</v>
+        <v>10626</v>
       </c>
       <c r="D87" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E87" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F87" t="n">
         <v>57.3</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10708</v>
+        <v>10733</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10841</v>
+        <v>10893</v>
       </c>
       <c r="D89" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E89" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F89" t="n">
         <v>58.3</v>
@@ -7977,13 +7977,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10845</v>
+        <v>10895</v>
       </c>
       <c r="D90" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E90" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F90" t="n">
         <v>59.2</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10771</v>
+        <v>10796</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10194</v>
+        <v>10219</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10125</v>
+        <v>10149</v>
       </c>
       <c r="D93" t="n">
         <v>51.3</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37195</v>
+        <v>37322</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37791</v>
+        <v>37920</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8198,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35442</v>
+        <v>35558</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -8220,10 +8220,10 @@
         <v>51.2</v>
       </c>
       <c r="F96" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G96" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -8237,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97">
@@ -8246,17 +8246,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37132</v>
+        <v>38037</v>
       </c>
       <c r="D97" t="n">
-        <v>49.2</v>
+        <v>50.3</v>
       </c>
       <c r="E97" t="n">
-        <v>50.8</v>
+        <v>49.7</v>
       </c>
       <c r="F97" t="n">
         <v>53.9</v>
@@ -8285,23 +8285,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37908</v>
+        <v>37256</v>
       </c>
       <c r="D98" t="n">
-        <v>50.3</v>
+        <v>49.2</v>
       </c>
       <c r="E98" t="n">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
       <c r="F98" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G98" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99">
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37704</v>
+        <v>37830</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8337,10 +8337,10 @@
         <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37305</v>
+        <v>37434</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8376,10 +8376,10 @@
         <v>50.8</v>
       </c>
       <c r="F100" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="G100" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
@@ -8402,23 +8402,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37567</v>
+        <v>38114</v>
       </c>
       <c r="D101" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E101" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G101" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -8432,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37985</v>
+        <v>37694</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F102" t="n">
         <v>54.5</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38005</v>
+        <v>38134</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1554</v>
+        <v>1595</v>
       </c>
       <c r="D2" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="E2" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="F2" t="n">
         <v>35.8</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1570</v>
+        <v>1612</v>
       </c>
       <c r="D3" t="n">
         <v>49.7</v>
@@ -8642,10 +8642,10 @@
         <v>50.3</v>
       </c>
       <c r="F3" t="n">
-        <v>36.6</v>
+        <v>37.2</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4</v>
+        <v>12.8</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1549</v>
+        <v>1587</v>
       </c>
       <c r="D4" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
       <c r="E4" t="n">
-        <v>50.4</v>
+        <v>49.7</v>
       </c>
       <c r="F4" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1543</v>
+        <v>1581</v>
       </c>
       <c r="D5" t="n">
-        <v>50.8</v>
+        <v>51.4</v>
       </c>
       <c r="E5" t="n">
-        <v>49.2</v>
+        <v>48.6</v>
       </c>
       <c r="F5" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1541</v>
+        <v>1585</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="F6" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8785,17 +8785,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1570</v>
+        <v>1600</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>50.1</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>49.9</v>
       </c>
       <c r="F7" t="n">
         <v>45.4</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1560</v>
+        <v>1612</v>
       </c>
       <c r="D8" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="E8" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="F8" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="G8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8867,19 +8867,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1510</v>
+        <v>1552</v>
       </c>
       <c r="D9" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,13 +8906,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1570</v>
+        <v>1610</v>
       </c>
       <c r="D10" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="E10" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="F10" t="n">
         <v>47.5</v>
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1574</v>
+        <v>1614</v>
       </c>
       <c r="D11" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E11" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F11" t="n">
         <v>50.3</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1574</v>
+        <v>1614</v>
       </c>
       <c r="D12" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="E12" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="F12" t="n">
-        <v>54.2</v>
+        <v>53.8</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1540</v>
+        <v>1585</v>
       </c>
       <c r="D13" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E13" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>55.5</v>
+        <v>54.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1571</v>
+        <v>1611</v>
       </c>
       <c r="D14" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E14" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="F14" t="n">
-        <v>57.4</v>
+        <v>56.7</v>
       </c>
       <c r="G14" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1552</v>
+        <v>1592</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F15" t="n">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="G15" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1548</v>
+        <v>1589</v>
       </c>
       <c r="D16" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="E16" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="F16" t="n">
-        <v>65.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1465</v>
+        <v>1513</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -9188,10 +9188,10 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>29.8</v>
+        <v>30.6</v>
       </c>
       <c r="G17" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1581</v>
+        <v>1622</v>
       </c>
       <c r="D18" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E18" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F18" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="G18" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,19 +9257,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1580</v>
+        <v>1621</v>
       </c>
       <c r="D19" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="E19" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="F19" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="G19" t="n">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1544</v>
+        <v>1583</v>
       </c>
       <c r="D20" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
       <c r="E20" t="n">
-        <v>52.3</v>
+        <v>51.9</v>
       </c>
       <c r="F20" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="G20" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1422</v>
+        <v>1501</v>
       </c>
       <c r="D21" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E21" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F21" t="n">
-        <v>35.2</v>
+        <v>36.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9361,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -9370,23 +9370,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1568</v>
+        <v>1620</v>
       </c>
       <c r="D22" t="n">
-        <v>49.4</v>
+        <v>50.4</v>
       </c>
       <c r="E22" t="n">
-        <v>50.6</v>
+        <v>49.6</v>
       </c>
       <c r="F22" t="n">
-        <v>35.8</v>
+        <v>36.3</v>
       </c>
       <c r="G22" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9409,23 +9409,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1580</v>
+        <v>1647</v>
       </c>
       <c r="D23" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="G23" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9452,19 +9452,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D24" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E24" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F24" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="G24" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1581</v>
+        <v>1622</v>
       </c>
       <c r="D25" t="n">
         <v>51.2</v>
@@ -9500,10 +9500,10 @@
         <v>48.8</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1566</v>
+        <v>1636</v>
       </c>
       <c r="D26" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="E26" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="F26" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="G26" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1582</v>
+        <v>1623</v>
       </c>
       <c r="D27" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E27" t="n">
         <v>50.1</v>
       </c>
-      <c r="E27" t="n">
-        <v>49.9</v>
-      </c>
       <c r="F27" t="n">
-        <v>38.2</v>
+        <v>38.6</v>
       </c>
       <c r="G27" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D28" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="E28" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="F28" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="G28" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1570</v>
+        <v>1610</v>
       </c>
       <c r="D29" t="n">
         <v>48.2</v>
@@ -9656,10 +9656,10 @@
         <v>51.8</v>
       </c>
       <c r="F29" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="G29" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1560</v>
+        <v>1602</v>
       </c>
       <c r="D30" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="E30" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="F30" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="G30" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1428</v>
+        <v>1507</v>
       </c>
       <c r="D31" t="n">
-        <v>47.9</v>
+        <v>48.9</v>
       </c>
       <c r="E31" t="n">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="F31" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9764,19 +9764,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1565</v>
+        <v>1606</v>
       </c>
       <c r="D32" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E32" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F32" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="G32" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1570</v>
+        <v>1611</v>
       </c>
       <c r="D33" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="E33" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="F33" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="G33" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1577</v>
+        <v>1618</v>
       </c>
       <c r="D34" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="E34" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F34" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="G34" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1567</v>
+        <v>1609</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E35" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F35" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="D36" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E36" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F36" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1547</v>
+        <v>1589</v>
       </c>
       <c r="D37" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="E37" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="F37" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="G37" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1426</v>
+        <v>1505</v>
       </c>
       <c r="D38" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E38" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F38" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="G38" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1530</v>
+        <v>1568</v>
       </c>
       <c r="D39" t="n">
-        <v>49.3</v>
+        <v>49.8</v>
       </c>
       <c r="E39" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="F39" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10063,7 +10063,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -10076,19 +10076,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D40" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="E40" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="F40" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10102,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -10115,13 +10115,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1525</v>
+        <v>1569</v>
       </c>
       <c r="D41" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="E41" t="n">
-        <v>50.3</v>
+        <v>49.5</v>
       </c>
       <c r="F41" t="n">
         <v>50.8</v>
@@ -10141,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="D42" t="n">
         <v>48.5</v>
@@ -10163,10 +10163,10 @@
         <v>51.5</v>
       </c>
       <c r="F42" t="n">
-        <v>52.9</v>
+        <v>51.9</v>
       </c>
       <c r="G42" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10180,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -10193,19 +10193,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="D43" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E43" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F43" t="n">
-        <v>54.1</v>
+        <v>54.4</v>
       </c>
       <c r="G43" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
@@ -10232,7 +10232,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1541</v>
+        <v>1580</v>
       </c>
       <c r="D44" t="n">
         <v>51.1</v>
@@ -10241,10 +10241,10 @@
         <v>48.9</v>
       </c>
       <c r="F44" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="G44" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10258,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1539</v>
+        <v>1581</v>
       </c>
       <c r="D45" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="E45" t="n">
-        <v>54.1</v>
+        <v>53.7</v>
       </c>
       <c r="F45" t="n">
-        <v>55.7</v>
+        <v>55.3</v>
       </c>
       <c r="G45" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1565</v>
+        <v>1607</v>
       </c>
       <c r="D46" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="E46" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
       <c r="F46" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="G46" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1557</v>
+        <v>1598</v>
       </c>
       <c r="D47" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="E47" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="F47" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="G47" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10384,23 +10384,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1561</v>
+        <v>1456</v>
       </c>
       <c r="D48" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>51.9</v>
       </c>
       <c r="F48" t="n">
-        <v>59.4</v>
+        <v>58.9</v>
       </c>
       <c r="G48" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
@@ -10423,23 +10423,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1415</v>
+        <v>1602</v>
       </c>
       <c r="D49" t="n">
-        <v>48.3</v>
+        <v>46.4</v>
       </c>
       <c r="E49" t="n">
-        <v>51.7</v>
+        <v>53.6</v>
       </c>
       <c r="F49" t="n">
-        <v>59.6</v>
+        <v>59.2</v>
       </c>
       <c r="G49" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50">
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1548</v>
+        <v>1589</v>
       </c>
       <c r="D50" t="n">
         <v>49.4</v>
@@ -10475,10 +10475,10 @@
         <v>50.6</v>
       </c>
       <c r="F50" t="n">
-        <v>60.1</v>
+        <v>59.8</v>
       </c>
       <c r="G50" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1553</v>
+        <v>1594</v>
       </c>
       <c r="D51" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E51" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F51" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="G51" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1538</v>
+        <v>1580</v>
       </c>
       <c r="D52" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="E52" t="n">
-        <v>49.2</v>
+        <v>49.5</v>
       </c>
       <c r="F52" t="n">
-        <v>61.8</v>
+        <v>62.1</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1552</v>
+        <v>1591</v>
       </c>
       <c r="D53" t="n">
         <v>49.7</v>
@@ -10592,10 +10592,10 @@
         <v>50.3</v>
       </c>
       <c r="F53" t="n">
-        <v>66.2</v>
+        <v>66.5</v>
       </c>
       <c r="G53" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1553</v>
+        <v>1594</v>
       </c>
       <c r="D54" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="E54" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="F54" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,13 +10661,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1573</v>
+        <v>1613</v>
       </c>
       <c r="D55" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E55" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F55" t="n">
         <v>70.59999999999999</v>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1560</v>
+        <v>1600</v>
       </c>
       <c r="D56" t="n">
         <v>48.5</v>
@@ -10709,10 +10709,10 @@
         <v>51.5</v>
       </c>
       <c r="F56" t="n">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D57" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E57" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F57" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="G57" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1576</v>
+        <v>1617</v>
       </c>
       <c r="D58" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E58" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F58" t="n">
         <v>83.09999999999999</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1577</v>
+        <v>1619</v>
       </c>
       <c r="D59" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="E59" t="n">
-        <v>50.9</v>
+        <v>51.3</v>
       </c>
       <c r="F59" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10856,19 +10856,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1450</v>
+        <v>1526</v>
       </c>
       <c r="D60" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="E60" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="F60" t="n">
-        <v>43.2</v>
+        <v>42.3</v>
       </c>
       <c r="G60" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10895,19 +10895,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="D61" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="E61" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="F61" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
       <c r="G61" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="D62" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="E62" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="F62" t="n">
-        <v>57.7</v>
+        <v>57</v>
       </c>
       <c r="G62" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="D63" t="n">
-        <v>51.6</v>
+        <v>52.6</v>
       </c>
       <c r="E63" t="n">
-        <v>48.4</v>
+        <v>47.4</v>
       </c>
       <c r="F63" t="n">
         <v>58.1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
@@ -11008,23 +11008,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1429</v>
+        <v>998</v>
       </c>
       <c r="D64" t="n">
-        <v>48.8</v>
+        <v>50.4</v>
       </c>
       <c r="E64" t="n">
-        <v>51.2</v>
+        <v>49.6</v>
       </c>
       <c r="F64" t="n">
-        <v>59.1</v>
+        <v>58.5</v>
       </c>
       <c r="G64" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65">
@@ -11051,19 +11051,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>977</v>
+        <v>997</v>
       </c>
       <c r="D65" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="E65" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="F65" t="n">
-        <v>59.5</v>
+        <v>58.6</v>
       </c>
       <c r="G65" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
@@ -11086,17 +11086,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>976</v>
+        <v>1502</v>
       </c>
       <c r="D66" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
       <c r="E66" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
       <c r="F66" t="n">
         <v>59.5</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67">
@@ -11129,7 +11129,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1540</v>
+        <v>1619</v>
       </c>
       <c r="D67" t="n">
         <v>48.6</v>
@@ -11138,10 +11138,10 @@
         <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G67" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1363</v>
+        <v>1646</v>
       </c>
       <c r="D68" t="n">
-        <v>48</v>
+        <v>49.8</v>
       </c>
       <c r="E68" t="n">
-        <v>52</v>
+        <v>50.2</v>
       </c>
       <c r="F68" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
       <c r="G68" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1554</v>
+        <v>1437</v>
       </c>
       <c r="D69" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="E69" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="F69" t="n">
-        <v>61.5</v>
+        <v>62.1</v>
       </c>
       <c r="G69" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70">
@@ -11242,23 +11242,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1571</v>
+        <v>1594</v>
       </c>
       <c r="D70" t="n">
-        <v>50.2</v>
+        <v>48.3</v>
       </c>
       <c r="E70" t="n">
-        <v>49.8</v>
+        <v>51.7</v>
       </c>
       <c r="F70" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="G70" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71">
@@ -11285,19 +11285,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="D71" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E71" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F71" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="G71" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72">
@@ -11324,19 +11324,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1138</v>
+        <v>1169</v>
       </c>
       <c r="D72" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="E72" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
       <c r="F72" t="n">
-        <v>62.7</v>
+        <v>63.1</v>
       </c>
       <c r="G72" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1372</v>
+        <v>1441</v>
       </c>
       <c r="D73" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="E73" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
       <c r="F73" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>580</v>
+        <v>616</v>
       </c>
       <c r="D74" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E74" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F74" t="n">
-        <v>52.1</v>
+        <v>53.1</v>
       </c>
       <c r="G74" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
@@ -11437,23 +11437,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="D75" t="n">
-        <v>49.9</v>
+        <v>52.8</v>
       </c>
       <c r="E75" t="n">
-        <v>50.1</v>
+        <v>47.2</v>
       </c>
       <c r="F75" t="n">
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
       <c r="G75" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76">
@@ -11476,23 +11476,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="D76" t="n">
-        <v>53.1</v>
+        <v>49.8</v>
       </c>
       <c r="E76" t="n">
-        <v>46.9</v>
+        <v>50.2</v>
       </c>
       <c r="F76" t="n">
-        <v>53.3</v>
+        <v>53.8</v>
       </c>
       <c r="G76" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77">
@@ -11519,33 +11519,33 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1153</v>
+        <v>1219</v>
       </c>
       <c r="D77" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>52</v>
-      </c>
-      <c r="E77" t="n">
-        <v>48</v>
-      </c>
-      <c r="F77" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="G77" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H77" t="b">
-        <v>1</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1474</v>
+        <v>1545</v>
       </c>
       <c r="D78" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E78" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F78" t="n">
-        <v>70.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>571</v>
+        <v>615</v>
       </c>
       <c r="D79" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="E79" t="n">
-        <v>51.8</v>
+        <v>52.5</v>
       </c>
       <c r="F79" t="n">
-        <v>57.6</v>
+        <v>58.7</v>
       </c>
       <c r="G79" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1182</v>
+        <v>1251</v>
       </c>
       <c r="D80" t="n">
-        <v>47.4</v>
+        <v>47</v>
       </c>
       <c r="E80" t="n">
-        <v>52.6</v>
+        <v>53</v>
       </c>
       <c r="F80" t="n">
         <v>60.4</v>
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1113</v>
+        <v>1201</v>
       </c>
       <c r="D81" t="n">
-        <v>47.5</v>
+        <v>47</v>
       </c>
       <c r="E81" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="F81" t="n">
-        <v>63.9</v>
+        <v>63.5</v>
       </c>
       <c r="G81" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11710,23 +11710,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D82" t="n">
-        <v>51.1</v>
+        <v>47</v>
       </c>
       <c r="E82" t="n">
+        <v>53</v>
+      </c>
+      <c r="F82" t="n">
         <v>48.9</v>
       </c>
-      <c r="F82" t="n">
-        <v>48</v>
-      </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
@@ -11749,23 +11749,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="D83" t="n">
-        <v>47</v>
+        <v>50.3</v>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>49.7</v>
       </c>
       <c r="F83" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="D84" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E84" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F84" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="D85" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="E85" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="F85" t="n">
-        <v>53.7</v>
+        <v>54.1</v>
       </c>
       <c r="G85" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86">
@@ -11870,19 +11870,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D86" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E86" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F86" t="n">
-        <v>55.7</v>
+        <v>54.7</v>
       </c>
       <c r="G86" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87">
@@ -11912,16 +11912,16 @@
         <v>423</v>
       </c>
       <c r="D87" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E87" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F87" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D88" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
       <c r="E88" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="F88" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="G88" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89">
@@ -11990,16 +11990,16 @@
         <v>415</v>
       </c>
       <c r="D89" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="F89" t="n">
-        <v>60.7</v>
+        <v>61.7</v>
       </c>
       <c r="G89" t="n">
-        <v>10.7</v>
+        <v>11.7</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="D90" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="E90" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F90" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="G90" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D91" t="n">
-        <v>52.7</v>
+        <v>49.4</v>
       </c>
       <c r="E91" t="n">
-        <v>47.3</v>
+        <v>50.6</v>
       </c>
       <c r="F91" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="G91" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92">
@@ -12100,23 +12100,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="D92" t="n">
-        <v>49.1</v>
+        <v>51.1</v>
       </c>
       <c r="E92" t="n">
-        <v>50.9</v>
+        <v>48.9</v>
       </c>
       <c r="F92" t="n">
-        <v>62.5</v>
+        <v>62.8</v>
       </c>
       <c r="G92" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93">
@@ -12146,16 +12146,16 @@
         <v>406</v>
       </c>
       <c r="D93" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="E93" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="F93" t="n">
-        <v>72.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12178,23 +12178,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1523</v>
+        <v>1620</v>
       </c>
       <c r="D94" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="E94" t="n">
-        <v>48.5</v>
+        <v>50.7</v>
       </c>
       <c r="F94" t="n">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="G94" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95">
@@ -12217,23 +12217,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1360</v>
+        <v>1568</v>
       </c>
       <c r="D95" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E95" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F95" t="n">
-        <v>57.6</v>
+        <v>58.1</v>
       </c>
       <c r="G95" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1577</v>
+        <v>1417</v>
       </c>
       <c r="D96" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
       <c r="E96" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="G96" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1582</v>
+        <v>1623</v>
       </c>
       <c r="D97" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="E97" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="F97" t="n">
-        <v>58.2</v>
+        <v>58.9</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1507</v>
+        <v>1622</v>
       </c>
       <c r="D98" t="n">
-        <v>49.3</v>
+        <v>49.9</v>
       </c>
       <c r="E98" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="F98" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="G98" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1582</v>
+        <v>1623</v>
       </c>
       <c r="D99" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E99" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F99" t="n">
-        <v>58.5</v>
+        <v>59.2</v>
       </c>
       <c r="G99" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100">
@@ -12412,11 +12412,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1581</v>
+        <v>1558</v>
       </c>
       <c r="D100" t="n">
         <v>50</v>
@@ -12425,10 +12425,10 @@
         <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>59.1</v>
+        <v>59.3</v>
       </c>
       <c r="G100" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101">
@@ -12455,19 +12455,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1561</v>
+        <v>1602</v>
       </c>
       <c r="D101" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E101" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="G101" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1573</v>
+        <v>1615</v>
       </c>
       <c r="D102" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E102" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F102" t="n">
-        <v>59.8</v>
+        <v>60.3</v>
       </c>
       <c r="G102" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1558</v>
+        <v>1602</v>
       </c>
       <c r="D103" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="E103" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="G103" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -12643,13 +12643,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37451</v>
+        <v>37578</v>
       </c>
       <c r="D2" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>40.2</v>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37499</v>
+        <v>37624</v>
       </c>
       <c r="D3" t="n">
         <v>50.2</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37694</v>
+        <v>37823</v>
       </c>
       <c r="D4" t="n">
         <v>51.1</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37176</v>
+        <v>37303</v>
       </c>
       <c r="D5" t="n">
         <v>49.5</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37634</v>
+        <v>37763</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37162</v>
+        <v>37288</v>
       </c>
       <c r="D7" t="n">
         <v>49.9</v>
@@ -12877,13 +12877,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36993</v>
+        <v>37118</v>
       </c>
       <c r="D8" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
         <v>49.1</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37446</v>
+        <v>37573</v>
       </c>
       <c r="D9" t="n">
         <v>49.9</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37718</v>
+        <v>37846</v>
       </c>
       <c r="D10" t="n">
         <v>51</v>
@@ -12964,10 +12964,10 @@
         <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37771</v>
+        <v>37899</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37784</v>
+        <v>37912</v>
       </c>
       <c r="D12" t="n">
         <v>51.3</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37610</v>
+        <v>37739</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13081,10 +13081,10 @@
         <v>50.5</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -13098,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37670</v>
+        <v>37797</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37577</v>
+        <v>37703</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,13 +13189,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37593</v>
+        <v>37719</v>
       </c>
       <c r="D16" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E16" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F16" t="n">
         <v>60.9</v>
@@ -13228,13 +13228,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35898</v>
+        <v>36021</v>
       </c>
       <c r="D17" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E17" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F17" t="n">
         <v>32.5</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37856</v>
+        <v>37985</v>
       </c>
       <c r="D18" t="n">
         <v>49</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37387</v>
+        <v>37511</v>
       </c>
       <c r="D19" t="n">
         <v>50.2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34546</v>
+        <v>34704</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37906</v>
+        <v>38035</v>
       </c>
       <c r="D21" t="n">
         <v>49.8</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37733</v>
+        <v>37898</v>
       </c>
       <c r="D22" t="n">
         <v>49.4</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37782</v>
+        <v>37939</v>
       </c>
       <c r="D23" t="n">
         <v>49.5</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37959</v>
+        <v>38087</v>
       </c>
       <c r="D24" t="n">
         <v>49.3</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37964</v>
+        <v>38093</v>
       </c>
       <c r="D25" t="n">
         <v>49.1</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37911</v>
+        <v>38040</v>
       </c>
       <c r="D26" t="n">
         <v>49.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34713</v>
+        <v>34872</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37989</v>
+        <v>38118</v>
       </c>
       <c r="D28" t="n">
         <v>49</v>
@@ -13666,10 +13666,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37999</v>
+        <v>38128</v>
       </c>
       <c r="D29" t="n">
         <v>48.9</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37716</v>
+        <v>37844</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37752</v>
+        <v>37881</v>
       </c>
       <c r="D31" t="n">
         <v>49.1</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37751</v>
+        <v>37879</v>
       </c>
       <c r="D32" t="n">
         <v>49.3</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37777</v>
+        <v>37905</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37731</v>
+        <v>37859</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37719</v>
+        <v>37848</v>
       </c>
       <c r="D35" t="n">
         <v>49.6</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34599</v>
+        <v>34758</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37555</v>
+        <v>37684</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36929</v>
+        <v>37052</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37721</v>
+        <v>37850</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8329</v>
+        <v>8371</v>
       </c>
       <c r="D40" t="n">
         <v>51</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37394</v>
+        <v>37519</v>
       </c>
       <c r="D41" t="n">
         <v>49.9</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37459</v>
+        <v>37587</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14212,10 +14212,10 @@
         <v>50.2</v>
       </c>
       <c r="F42" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -14229,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37487</v>
+        <v>37615</v>
       </c>
       <c r="D43" t="n">
         <v>48.9</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37413</v>
+        <v>37541</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14307,7 +14307,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37079</v>
+        <v>37204</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -14346,7 +14346,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37225</v>
+        <v>37351</v>
       </c>
       <c r="D46" t="n">
         <v>49.9</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37591</v>
+        <v>37719</v>
       </c>
       <c r="D47" t="n">
         <v>50.5</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37636</v>
+        <v>37765</v>
       </c>
       <c r="D48" t="n">
         <v>50.9</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35071</v>
+        <v>35190</v>
       </c>
       <c r="D49" t="n">
         <v>50.2</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37475</v>
+        <v>37603</v>
       </c>
       <c r="D50" t="n">
         <v>49.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37346</v>
+        <v>37472</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37520</v>
+        <v>37647</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37392</v>
+        <v>37518</v>
       </c>
       <c r="D53" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E53" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F53" t="n">
         <v>61.5</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37433</v>
+        <v>37559</v>
       </c>
       <c r="D54" t="n">
         <v>49.9</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37609</v>
+        <v>37737</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37320</v>
+        <v>37448</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37673</v>
+        <v>37802</v>
       </c>
       <c r="D57" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E57" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F57" t="n">
         <v>73.90000000000001</v>
@@ -14827,13 +14827,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37746</v>
+        <v>37875</v>
       </c>
       <c r="D58" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E58" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F58" t="n">
         <v>76.3</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>37948</v>
+        <v>38077</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14875,10 +14875,10 @@
         <v>48.7</v>
       </c>
       <c r="F59" t="n">
-        <v>87.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="G59" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34777</v>
+        <v>34936</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14914,10 +14914,10 @@
         <v>49.2</v>
       </c>
       <c r="F60" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36354</v>
+        <v>36438</v>
       </c>
       <c r="D61" t="n">
         <v>50.3</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36775</v>
+        <v>36937</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23243</v>
+        <v>23320</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23668</v>
+        <v>23746</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23617</v>
+        <v>23691</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37655</v>
+        <v>37816</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -15178,19 +15178,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20986</v>
+        <v>21064</v>
       </c>
       <c r="D67" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E67" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F67" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37161</v>
+        <v>37288</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -15226,10 +15226,10 @@
         <v>49.5</v>
       </c>
       <c r="F68" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -15243,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69">
@@ -15252,17 +15252,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30238</v>
+        <v>35676</v>
       </c>
       <c r="D69" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -15291,23 +15291,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35520</v>
+        <v>30386</v>
       </c>
       <c r="D70" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="E70" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="F70" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="G70" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36868</v>
+        <v>36954</v>
       </c>
       <c r="D71" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E71" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F71" t="n">
         <v>56.7</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32882</v>
+        <v>33027</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25794</v>
+        <v>25889</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15421,10 +15421,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G73" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14134</v>
+        <v>14204</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13940</v>
+        <v>14009</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15499,10 +15499,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="G75" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14995</v>
+        <v>15065</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -15538,10 +15538,10 @@
         <v>49.4</v>
       </c>
       <c r="F76" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="G76" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26371</v>
+        <v>26507</v>
       </c>
       <c r="D77" t="n">
         <v>50</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35192</v>
+        <v>35348</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15616,10 +15616,10 @@
         <v>49.4</v>
       </c>
       <c r="F78" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G78" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
@@ -15646,19 +15646,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28411</v>
+        <v>28543</v>
       </c>
       <c r="D79" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E79" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F79" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="G79" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15607</v>
+        <v>15685</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27277</v>
+        <v>27418</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10349</v>
+        <v>10399</v>
       </c>
       <c r="D82" t="n">
         <v>51.6</v>
@@ -15772,10 +15772,10 @@
         <v>48.4</v>
       </c>
       <c r="F82" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10351</v>
+        <v>10376</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10131</v>
+        <v>10181</v>
       </c>
       <c r="D84" t="n">
         <v>50.7</v>
@@ -15867,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10647</v>
+        <v>10672</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10134</v>
+        <v>10179</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
@@ -15958,13 +15958,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10600</v>
+        <v>10626</v>
       </c>
       <c r="D87" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E87" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F87" t="n">
         <v>57.3</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10708</v>
+        <v>10733</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -16036,13 +16036,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10841</v>
+        <v>10893</v>
       </c>
       <c r="D89" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E89" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F89" t="n">
         <v>58.3</v>
@@ -16075,13 +16075,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10845</v>
+        <v>10895</v>
       </c>
       <c r="D90" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E90" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F90" t="n">
         <v>59.2</v>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10771</v>
+        <v>10796</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10194</v>
+        <v>10219</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10125</v>
+        <v>10149</v>
       </c>
       <c r="D93" t="n">
         <v>51.3</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37195</v>
+        <v>37322</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37791</v>
+        <v>37920</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16296,7 +16296,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96">
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35442</v>
+        <v>35558</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -16318,10 +16318,10 @@
         <v>51.2</v>
       </c>
       <c r="F96" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G96" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -16335,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97">
@@ -16344,17 +16344,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>37132</v>
+        <v>38037</v>
       </c>
       <c r="D97" t="n">
-        <v>49.2</v>
+        <v>50.3</v>
       </c>
       <c r="E97" t="n">
-        <v>50.8</v>
+        <v>49.7</v>
       </c>
       <c r="F97" t="n">
         <v>53.9</v>
@@ -16383,23 +16383,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37908</v>
+        <v>37256</v>
       </c>
       <c r="D98" t="n">
-        <v>50.3</v>
+        <v>49.2</v>
       </c>
       <c r="E98" t="n">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
       <c r="F98" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G98" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -16413,7 +16413,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99">
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37704</v>
+        <v>37830</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16435,10 +16435,10 @@
         <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37305</v>
+        <v>37434</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16474,10 +16474,10 @@
         <v>50.8</v>
       </c>
       <c r="F100" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="G100" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -16491,7 +16491,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101">
@@ -16500,23 +16500,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37567</v>
+        <v>38114</v>
       </c>
       <c r="D101" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E101" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G101" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -16530,7 +16530,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102">
@@ -16539,17 +16539,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37985</v>
+        <v>37694</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F102" t="n">
         <v>54.5</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38005</v>
+        <v>38134</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
